--- a/data/output/workbook/2026-07-07.xlsx
+++ b/data/output/workbook/2026-07-07.xlsx
@@ -400,7 +400,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10677525"/>
+    <ext cx="10125075" cy="11106150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -610,7 +610,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10620375"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07 10:26</t>
+          <t>2026-07-07 15:09</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6726,329 +6726,171 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="28" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>Kansas City Royals offense vs New York Mets defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="29" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="29" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="29" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="29" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="29" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="29" t="inlineStr">
+      <c r="I70" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="29" t="inlineStr">
+      <c r="J70" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="29" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="29" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="29" t="inlineStr">
+      <c r="M70" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="29" t="inlineStr">
+      <c r="N70" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="29" t="inlineStr">
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="29" t="inlineStr">
+      <c r="P70" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="29" t="inlineStr">
+      <c r="Q70" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n">
-        <v>4.235</v>
-      </c>
-      <c r="C69" s="31" t="n">
-        <v>5.033</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F69" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G69" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I69" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J69" s="32" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O69" s="31" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="P69" s="31" t="n">
-        <v>4.771</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="C70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>7.918</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>0.896</v>
-      </c>
-      <c r="C71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.235</v>
+      </c>
+      <c r="C71" s="31" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="32" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O71" s="31" t="n">
+        <v>5.533</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>0.918</v>
+        <v>4.771</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>8.021000000000001</v>
+        <v>7.792</v>
       </c>
       <c r="C72" s="31" t="inlineStr">
         <is>
@@ -7112,396 +6954,396 @@
         </is>
       </c>
       <c r="P72" s="31" t="n">
-        <v>9.061</v>
+        <v>7.918</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="31" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="C73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="31" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="Q73" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>8.021000000000001</v>
+      </c>
+      <c r="C74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>9.061</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="31" t="n">
+      <c r="B75" s="31" t="n">
         <v>0.551</v>
       </c>
-      <c r="C73" s="31" t="n">
+      <c r="C75" s="31" t="n">
         <v>0.967</v>
       </c>
-      <c r="D73" s="31" t="n">
+      <c r="D75" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="E73" s="31" t="n">
+      <c r="E75" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="F73" s="31" t="n">
+      <c r="F75" s="31" t="n">
         <v>1.1</v>
       </c>
-      <c r="G73" s="31" t="n">
+      <c r="G75" s="31" t="n">
         <v>1.8</v>
       </c>
-      <c r="H73" s="33" t="inlineStr">
+      <c r="H75" s="33" t="inlineStr">
         <is>
           <t>4th</t>
         </is>
       </c>
-      <c r="I73" s="31" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J73" s="35" t="inlineStr">
+      <c r="J75" s="35" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
       </c>
-      <c r="K73" s="31" t="n">
+      <c r="K75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="L73" s="31" t="n">
+      <c r="L75" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="M73" s="31" t="n">
+      <c r="M75" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="N73" s="31" t="n">
+      <c r="N75" s="31" t="n">
         <v>0.85</v>
       </c>
-      <c r="O73" s="31" t="n">
+      <c r="O75" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="P73" s="31" t="n">
+      <c r="P75" s="31" t="n">
         <v>0.532</v>
       </c>
-      <c r="Q73" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>New York Mets offense vs Kansas City Royals defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="29" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="29" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="29" t="inlineStr">
+      <c r="F78" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="29" t="inlineStr">
+      <c r="G78" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="29" t="inlineStr">
+      <c r="H78" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="29" t="inlineStr">
+      <c r="I78" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="29" t="inlineStr">
+      <c r="J78" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="29" t="inlineStr">
+      <c r="K78" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="29" t="inlineStr">
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="29" t="inlineStr">
+      <c r="M78" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="29" t="inlineStr">
+      <c r="N78" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="29" t="inlineStr">
+      <c r="O78" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="29" t="inlineStr">
+      <c r="P78" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="29" t="inlineStr">
+      <c r="Q78" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>6.467</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O77" s="31" t="n">
-        <v>5.633</v>
-      </c>
-      <c r="P77" s="31" t="n">
-        <v>5.173</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>7.306</v>
-      </c>
-      <c r="C78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>8.603999999999999</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="C79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.94</v>
+      </c>
+      <c r="C79" s="31" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>6.467</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O79" s="31" t="n">
+        <v>5.633</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>1.25</v>
+        <v>5.173</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.407999999999999</v>
+        <v>7.306</v>
       </c>
       <c r="C80" s="31" t="inlineStr">
         <is>
@@ -7565,68 +7407,226 @@
         </is>
       </c>
       <c r="P80" s="31" t="n">
-        <v>8.208</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B81" s="31" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="C81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q81" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>8.407999999999999</v>
+      </c>
+      <c r="C82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>8.208</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="31" t="n">
+      <c r="B83" s="31" t="n">
         <v>0.519</v>
       </c>
-      <c r="C81" s="31" t="n">
+      <c r="C83" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="D81" s="31" t="n">
+      <c r="D83" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E81" s="31" t="n">
+      <c r="E83" s="31" t="n">
         <v>0.067</v>
       </c>
-      <c r="F81" s="31" t="n">
+      <c r="F83" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="G81" s="31" t="n">
+      <c r="G83" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="H81" s="32" t="inlineStr">
+      <c r="H83" s="32" t="inlineStr">
         <is>
           <t>24th</t>
         </is>
       </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="35" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
       </c>
-      <c r="K81" s="31" t="n">
+      <c r="K83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="L81" s="31" t="n">
+      <c r="L83" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="M81" s="31" t="n">
+      <c r="M83" s="31" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="N81" s="31" t="n">
+      <c r="N83" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="O81" s="31" t="n">
+      <c r="O83" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="P81" s="31" t="n">
+      <c r="P83" s="31" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="Q81" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6713636363636364</v>
+        <v>0.6628671328671327</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-204</v>
+        <v>-197</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>186</v>
@@ -8821,7 +8821,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 67.1% (fair -204). Your call.</t>
+          <t>Model 66.3% (fair -197). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8857,13 +8857,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5728014184397162</v>
+        <v>0.6392657342657342</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-134</v>
+        <v>-177</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 63.9% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8899,17 +8899,17 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8919,17 +8919,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>New York Yankees +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5571111111111111</v>
+        <v>0.6310661764705883</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-126</v>
+        <v>-171</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8965,17 +8965,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -8985,17 +8985,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.743549019607843</v>
+        <v>0.5876119402985075</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-290</v>
+        <v>-142</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-104</v>
+        <v>168</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 74.4% (fair -290). Your call.</t>
+          <t>Model 58.8% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9031,17 +9031,17 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9051,17 +9051,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Atlanta Braves +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5212592592592592</v>
+        <v>0.5682462686567165</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-109</v>
+        <v>-132</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9085,7 +9085,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 56.8% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9102,12 +9102,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9117,14 +9117,14 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4787407407407407</v>
+        <v>0.5571111111111111</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>109</v>
+        <v>-126</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>170</v>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9168,12 +9168,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -9183,17 +9183,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6443411764705882</v>
+        <v>0.5212592592592592</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-181</v>
+        <v>-109</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-104</v>
+        <v>170</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9249,17 +9249,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4429090909090909</v>
+        <v>0.7350906976744187</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>126</v>
+        <v>-277</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>175</v>
+        <v>-115</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 73.5% (fair -277). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9300,12 +9300,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9315,17 +9315,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies -1.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5251528384279476</v>
+        <v>0.4787407407407407</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-111</v>
+        <v>109</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -111). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9381,17 +9381,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins -1.5</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4272142857142857</v>
+        <v>0.5541921397379912</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>134</v>
+        <v>-124</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9432,12 +9432,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9447,17 +9447,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.6156674641148324</v>
+        <v>0.6550186046511628</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-160</v>
+        <v>-190</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-109</v>
+        <v>-115</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 65.5% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9513,17 +9513,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves +1.5</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5612231527093596</v>
+        <v>0.4429090909090909</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-128</v>
+        <v>126</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-103</v>
+        <v>175</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9564,32 +9564,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.3975185185185184</v>
+        <v>0.6147808612440192</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>152</v>
+        <v>-160</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>170</v>
+        <v>-109</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +152). Your call.</t>
+          <t>Model 61.5% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9630,32 +9630,32 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.53015</v>
+        <v>0.4317358490566037</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-113</v>
+        <v>132</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>100</v>
+        <v>165</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 43.2% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9696,12 +9696,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9711,17 +9711,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4944600938967136</v>
+        <v>0.5865639810426539</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>102</v>
+        <v>-142</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>113</v>
+        <v>-111</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9745,7 +9745,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9762,12 +9762,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9777,17 +9777,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5561962264150944</v>
+        <v>0.6745078740157481</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-125</v>
+        <v>-207</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-112</v>
+        <v>-154</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 67.5% (fair -207). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9823,17 +9823,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9843,17 +9843,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4387815126050421</v>
+        <v>0.4123880597014926</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 41.2% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9913,13 +9913,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5364834951456311</v>
+        <v>0.5557882352941176</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-116</v>
+        <v>-125</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-106</v>
+        <v>-104</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9955,17 +9955,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5527450704225352</v>
+        <v>0.3687074829931973</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-124</v>
+        <v>171</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-113</v>
+        <v>194</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10026,32 +10026,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Atlanta Braves +1.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4413191489361701</v>
+        <v>0.560328502415459</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>127</v>
+        <v>-127</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>135</v>
+        <v>-107</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10087,37 +10087,37 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4411587982832618</v>
+        <v>0.4396341463414634</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>127</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10158,12 +10158,12 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -10173,17 +10173,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4625225225225226</v>
+        <v>0.5707826291079813</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>116</v>
+        <v>-133</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>122</v>
+        <v>-113</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10219,37 +10219,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.6246703124999999</v>
+        <v>0.5433365853658536</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-166</v>
+        <v>-119</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-156</v>
+        <v>-105</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -166). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10290,12 +10290,12 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -10305,17 +10305,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4916826923076922</v>
+        <v>0.52615</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>103</v>
+        <v>-111</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10351,17 +10351,17 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -10371,17 +10371,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5424</v>
+        <v>0.5134803921568628</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-119</v>
+        <v>-106</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-113</v>
+        <v>104</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -119). Your call.</t>
+          <t>Model 51.3% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10438,7 +10438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P108"/>
+  <dimension ref="A1:P148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10582,13 +10582,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6253</v>
+        <v>0.6149</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-167</v>
+        <v>-160</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 61.5% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10648,13 +10648,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3747</v>
+        <v>0.3851</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +167). Your call.</t>
+          <t>Model 38.5% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5669</v>
+        <v>0.5689</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-131</v>
+        <v>-132</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>141</v>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10780,13 +10780,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4331</v>
+        <v>0.4311</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10846,10 +10846,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.2564642857142857</v>
+        <v>0.2648928571428572</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>180</v>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 25.6% (fair +290). Your call.</t>
+          <t>Model 26.5% (fair +278). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10912,13 +10912,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.743549019607843</v>
+        <v>0.7350906976744187</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-290</v>
+        <v>-277</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-104</v>
+        <v>-115</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 74.4% (fair -290). Your call.</t>
+          <t>Model 73.5% (fair -277). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -10978,13 +10978,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5194</v>
+        <v>0.5291</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11044,13 +11044,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4805</v>
+        <v>0.4709</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11182,7 +11182,7 @@
         <v>194</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -11242,10 +11242,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3556428571428571</v>
+        <v>0.345</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>180</v>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 34.5% (fair +190). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11308,13 +11308,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6443411764705882</v>
+        <v>0.6550186046511628</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-181</v>
+        <v>-190</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-104</v>
+        <v>-115</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 65.5% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11374,13 +11374,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.517135922330097</v>
+        <v>0.4932862745098039</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-107</v>
+        <v>103</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-106</v>
+        <v>-104</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11440,13 +11440,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4828780487804878</v>
+        <v>0.5067156862745098</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>107</v>
+        <v>-103</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11502,17 +11502,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4036</v>
+        <v>0.4732</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +148). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11568,17 +11568,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5964</v>
+        <v>0.5267999999999999</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-148</v>
+        <v>-111</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -148). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11638,13 +11638,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.3975185185185184</v>
+        <v>0.3687074829931973</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +152). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11704,13 +11704,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6024925925925926</v>
+        <v>0.6312918367346939</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-152</v>
+        <v>-171</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-170</v>
+        <v>-194</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 60.2% (fair -152). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11770,10 +11770,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.618</v>
+        <v>0.6122</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-162</v>
+        <v>-158</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>117</v>
@@ -11800,7 +11800,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -162). Your call.</t>
+          <t>Model 61.2% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11836,13 +11836,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.382</v>
+        <v>0.3878</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 38.2% (fair +162). Your call.</t>
+          <t>Model 38.8% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11902,13 +11902,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4368</v>
+        <v>0.4509047619047619</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11968,13 +11968,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5631638766519824</v>
+        <v>0.5490845070422534</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-129</v>
+        <v>-122</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-127</v>
+        <v>-113</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12034,13 +12034,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4167622950819672</v>
+        <v>0.4057872340425532</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12100,13 +12100,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5832485477178423</v>
+        <v>0.5942117647058823</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-140</v>
+        <v>-146</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-141</v>
+        <v>-138</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12166,13 +12166,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5289</v>
+        <v>0.5373</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-112</v>
+        <v>-116</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12232,10 +12232,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4711</v>
+        <v>0.4627</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>110</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12298,13 +12298,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4387815126050421</v>
+        <v>0.4396341463414634</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12364,13 +12364,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5612231527093596</v>
+        <v>0.560328502415459</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-128</v>
+        <v>-127</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-103</v>
+        <v>-107</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12430,13 +12430,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4576303317535544</v>
+        <v>0.4583870967741936</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +119). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12496,13 +12496,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5424</v>
+        <v>0.5415967741935483</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-119</v>
+        <v>-118</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-113</v>
+        <v>-117</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -119). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12562,13 +12562,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.5262</v>
+        <v>0.5051780487804878</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-111</v>
+        <v>-102</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>106</v>
+        <v>-105</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12592,7 +12592,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12628,13 +12628,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.4738</v>
+        <v>0.4948341232227488</v>
       </c>
       <c r="G36" s="14" t="n">
+        <v>102</v>
+      </c>
+      <c r="H36" s="15" t="n">
         <v>111</v>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>108</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12694,13 +12694,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4272142857142857</v>
+        <v>0.3607342657342657</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 36.1% (fair +177). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12760,13 +12760,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5728014184397162</v>
+        <v>0.6392657342657342</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-134</v>
+        <v>-177</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 63.9% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4944600938967136</v>
+        <v>0.4723943661971831</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>113</v>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12892,10 +12892,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5055291079812206</v>
+        <v>0.5275985915492958</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-102</v>
+        <v>-112</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>-113</v>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12958,13 +12958,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5168</v>
+        <v>0.5077</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-107</v>
+        <v>-103</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12988,7 +12988,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13024,10 +13024,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4832</v>
+        <v>0.4923</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>113</v>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13090,13 +13090,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.3286330935251798</v>
+        <v>0.3371328671328671</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 32.9% (fair +204). Your call.</t>
+          <t>Model 33.7% (fair +197). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13156,10 +13156,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.6713636363636364</v>
+        <v>0.6628671328671327</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-204</v>
+        <v>-197</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>186</v>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 67.1% (fair -204). Your call.</t>
+          <t>Model 66.3% (fair -197). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13222,13 +13222,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4438028169014085</v>
+        <v>0.4134123222748814</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13288,13 +13288,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5561962264150944</v>
+        <v>0.5865639810426539</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-125</v>
+        <v>-142</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-112</v>
+        <v>-111</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13350,17 +13350,17 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.5423</v>
+        <v>0.4703</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>-118</v>
+        <v>113</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13384,7 +13384,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13416,17 +13416,17 @@
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.4577</v>
+        <v>0.5297000000000001</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>118</v>
+        <v>-113</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4413191489361701</v>
+        <v>0.426</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>135</v>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13684,10 +13684,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.558726050420168</v>
+        <v>0.5739756302521009</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-127</v>
+        <v>-135</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>-138</v>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13746,17 +13746,17 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.3966</v>
+        <v>0.5037</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>152</v>
+        <v>-101</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 50.4% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13812,17 +13812,17 @@
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.6033999999999999</v>
+        <v>0.4963</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-152</v>
+        <v>101</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 60.3% (fair -152). Your call.</t>
+          <t>Model 49.6% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.38436</v>
+        <v>0.3852</v>
       </c>
       <c r="G55" s="14" t="n">
         <v>160</v>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +160). Your call.</t>
+          <t>Model 38.5% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.6156674641148324</v>
+        <v>0.6147808612440192</v>
       </c>
       <c r="G56" s="14" t="n">
         <v>-160</v>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 61.5% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14014,13 +14014,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.6246703124999999</v>
+        <v>0.6745078740157481</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>-166</v>
+        <v>-207</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>-156</v>
+        <v>-154</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -166). Your call.</t>
+          <t>Model 67.5% (fair -207). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14080,10 +14080,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.3753125</v>
+        <v>0.32546875</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>156</v>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +166). Your call.</t>
+          <t>Model 32.5% (fair +207). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14142,17 +14142,17 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5562</v>
+        <v>0.5393</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-125</v>
+        <v>-117</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14208,17 +14208,17 @@
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4438</v>
+        <v>0.4607</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14278,10 +14278,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4748313725490196</v>
+        <v>0.4458235294117647</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>-104</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +111). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14344,10 +14344,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5251528384279476</v>
+        <v>0.5541921397379912</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-111</v>
+        <v>-124</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>129</v>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -111). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14410,10 +14410,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.4635294117647059</v>
+        <v>0.4441666666666667</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>104</v>
@@ -14440,7 +14440,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14476,13 +14476,13 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5364834951456311</v>
+        <v>0.5557882352941176</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-116</v>
+        <v>-125</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>-106</v>
+        <v>-104</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4948</v>
+        <v>0.4942</v>
       </c>
       <c r="G69" s="14" t="n">
         <v>102</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14870,7 +14870,7 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5052</v>
+        <v>0.5058</v>
       </c>
       <c r="G70" s="14" t="n">
         <v>-102</v>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -15190,10 +15190,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4426</v>
+        <v>0.4332</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H75" s="15" t="n"/>
       <c r="I75" s="13">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15254,10 +15254,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5574</v>
+        <v>0.5668</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-126</v>
+        <v>-131</v>
       </c>
       <c r="H76" s="15" t="n"/>
       <c r="I76" s="13">
@@ -15282,7 +15282,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15318,10 +15318,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.3855</v>
+        <v>0.381</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H77" s="15" t="n"/>
       <c r="I77" s="13">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15382,10 +15382,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.6145</v>
+        <v>0.619</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-159</v>
+        <v>-162</v>
       </c>
       <c r="H78" s="15" t="n"/>
       <c r="I78" s="13">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -159). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15446,10 +15446,10 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5044</v>
+        <v>0.48395</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-102</v>
+        <v>107</v>
       </c>
       <c r="H79" s="15" t="n">
         <v>100</v>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4955882352941176</v>
+        <v>0.51605</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>102</v>
+        <v>-107</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15559,32 +15559,32 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Over 7</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4916826923076922</v>
+        <v>0.4633</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15625,32 +15625,32 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Under 7</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5083408450704225</v>
+        <v>0.5367</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-103</v>
+        <v>-116</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-113</v>
+        <v>113</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15691,32 +15691,32 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>San Francisco Giants +1.5</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4157</v>
+        <v>0.6359456140350878</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>141</v>
+        <v>-175</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>163</v>
+        <v>-185</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +141). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15757,32 +15757,32 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Toronto Blue Jays -1.5</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5843</v>
+        <v>0.3640530303030303</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-141</v>
+        <v>175</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-133</v>
+        <v>164</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -141). Your call.</t>
+          <t>Model 36.4% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15823,12 +15823,12 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -15838,17 +15838,17 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4441441441441442</v>
+        <v>0.4702884615384615</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15889,12 +15889,12 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -15904,17 +15904,17 @@
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5558348017621146</v>
+        <v>0.5296761904761905</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-125</v>
+        <v>-113</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-127</v>
+        <v>-110</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15938,7 +15938,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15955,32 +15955,32 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.48925</v>
+        <v>0.49125</v>
       </c>
       <c r="G87" s="14" t="n">
         <v>104</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16021,32 +16021,32 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.51075</v>
+        <v>0.5087279069767443</v>
       </c>
       <c r="G88" s="14" t="n">
         <v>-104</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>100</v>
+        <v>-115</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16087,32 +16087,32 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Baltimore Orioles +1.5</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4625225225225226</v>
+        <v>0.6188087719298245</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>116</v>
+        <v>-162</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>122</v>
+        <v>-185</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16153,32 +16153,32 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.537484140969163</v>
+        <v>0.3811627906976744</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-116</v>
+        <v>162</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-127</v>
+        <v>158</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16219,12 +16219,12 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -16234,17 +16234,17 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4552534562211982</v>
+        <v>0.416</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16285,12 +16285,12 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -16300,17 +16300,17 @@
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5447239631336405</v>
+        <v>0.584</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-120</v>
+        <v>-140</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>-117</v>
+        <v>-138</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -16334,7 +16334,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16351,32 +16351,32 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.4411587982832618</v>
+        <v>0.5433365853658536</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>127</v>
+        <v>-119</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>133</v>
+        <v>-105</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16417,32 +16417,32 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5588283261802575</v>
+        <v>0.4566341463414635</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-127</v>
+        <v>119</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-133</v>
+        <v>105</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16466,7 +16466,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16483,32 +16483,32 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Detroit Tigers -1.5</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.53015</v>
+        <v>0.4314583333333334</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-113</v>
+        <v>132</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16549,32 +16549,32 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4698862745098039</v>
+        <v>0.5685183673469387</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>113</v>
+        <v>-132</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>-104</v>
+        <v>-145</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16615,12 +16615,12 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
@@ -16630,11 +16630,11 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4472350230414747</v>
+        <v>0.4464055299539171</v>
       </c>
       <c r="G97" s="14" t="n">
         <v>124</v>
@@ -16664,7 +16664,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16681,12 +16681,12 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -16696,17 +16696,17 @@
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5527450704225352</v>
+        <v>0.5536202764976959</v>
       </c>
       <c r="G98" s="14" t="n">
         <v>-124</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>-113</v>
+        <v>-117</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16747,31 +16747,33 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.4398</v>
+        <v>0.5213121951219513</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>127</v>
-      </c>
-      <c r="H99" s="15" t="n"/>
+        <v>-109</v>
+      </c>
+      <c r="H99" s="15" t="n">
+        <v>-105</v>
+      </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
         <v/>
@@ -16794,7 +16796,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16811,31 +16813,33 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C100" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.5602</v>
+        <v>0.4786829268292683</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>-127</v>
-      </c>
-      <c r="H100" s="15" t="n"/>
+        <v>109</v>
+      </c>
+      <c r="H100" s="15" t="n">
+        <v>105</v>
+      </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
         <v/>
@@ -16858,7 +16862,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16875,31 +16879,33 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.5869</v>
+        <v>0.4317358490566037</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>-142</v>
-      </c>
-      <c r="H101" s="15" t="n"/>
+        <v>132</v>
+      </c>
+      <c r="H101" s="15" t="n">
+        <v>165</v>
+      </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
         <v/>
@@ -16922,7 +16928,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 43.2% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -16939,31 +16945,33 @@
       </c>
       <c r="B102" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C102" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Atlanta Braves +1.5</t>
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.4131</v>
+        <v>0.5682462686567165</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>142</v>
-      </c>
-      <c r="H102" s="15" t="n"/>
+        <v>-132</v>
+      </c>
+      <c r="H102" s="15" t="n">
+        <v>168</v>
+      </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
         <v/>
@@ -16986,7 +16994,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 56.8% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17003,12 +17011,12 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
@@ -17018,16 +17026,18 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.4736</v>
+        <v>0.47385</v>
       </c>
       <c r="G103" s="14" t="n">
         <v>111</v>
       </c>
-      <c r="H103" s="15" t="n"/>
+      <c r="H103" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
         <v/>
@@ -17067,12 +17077,12 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C104" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
@@ -17082,16 +17092,18 @@
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5264</v>
+        <v>0.52615</v>
       </c>
       <c r="G104" s="14" t="n">
         <v>-111</v>
       </c>
-      <c r="H104" s="15" t="n"/>
+      <c r="H104" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
         <v/>
@@ -17131,12 +17143,12 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -17146,16 +17158,18 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4976</v>
+        <v>0.4557603686635945</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>101</v>
-      </c>
-      <c r="H105" s="15" t="n"/>
+        <v>119</v>
+      </c>
+      <c r="H105" s="15" t="n">
+        <v>117</v>
+      </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
         <v/>
@@ -17178,7 +17192,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17195,12 +17209,12 @@
       </c>
       <c r="B106" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C106" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
@@ -17210,16 +17224,18 @@
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5024</v>
+        <v>0.5442545454545454</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-101</v>
-      </c>
-      <c r="H106" s="15" t="n"/>
+        <v>-119</v>
+      </c>
+      <c r="H106" s="15" t="n">
+        <v>-120</v>
+      </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
         <v/>
@@ -17242,7 +17258,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17259,31 +17275,33 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.4289</v>
+        <v>0.5294048780487806</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>133</v>
-      </c>
-      <c r="H107" s="15" t="n"/>
+        <v>-112</v>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>-105</v>
+      </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
         <v/>
@@ -17306,7 +17324,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17323,31 +17341,33 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C108" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>-133</v>
-      </c>
-      <c r="H108" s="15" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>104</v>
+      </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
         <v/>
@@ -17370,7 +17390,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17379,9 +17399,2629 @@
         <v/>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>New York Yankees @ Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays -1.5</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="n">
+        <v>0.3689615384615385</v>
+      </c>
+      <c r="G109" s="14" t="n">
+        <v>171</v>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>160</v>
+      </c>
+      <c r="I109" s="13">
+        <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
+        <v/>
+      </c>
+      <c r="J109" s="16">
+        <f>IF($H$109="","",$F$109*IF($H$109&lt;0,-100/$H$109,$H$109/100)-(1-$F$109))</f>
+        <v/>
+      </c>
+      <c r="K109" s="17">
+        <f>IF($H$109="","",MAX(0,($F$109*IF($H$109&lt;0,-100/$H$109,$H$109/100)-(1-$F$109))/IF($H$109&lt;0,-100/$H$109,$H$109/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L109" s="18">
+        <f>IF($H$109="","",ROUND(MIN($K$109,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M109" s="12">
+        <f>IF($J$109="","",IF($J$109&lt;0,"Pass",IF($J$109&lt;'Settings'!$B$4,"Thin",IF($J$109&lt;0.06,"✅ Sharp band",IF($J$109&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N109" s="19" t="inlineStr">
+        <is>
+          <t>Model 36.9% (fair +171). Your call.</t>
+        </is>
+      </c>
+      <c r="O109" s="15" t="n"/>
+      <c r="P109" s="16">
+        <f>IF(OR($H$109="",$O$109=""),"",(1+IF($H$109&lt;0,-100/$H$109,$H$109/100))/(1+IF($O$109&lt;0,-100/$O$109,$O$109/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B110" s="20" t="inlineStr">
+        <is>
+          <t>New York Yankees @ Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="D110" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E110" s="20" t="inlineStr">
+        <is>
+          <t>New York Yankees +1.5</t>
+        </is>
+      </c>
+      <c r="F110" s="13" t="n">
+        <v>0.6310661764705883</v>
+      </c>
+      <c r="G110" s="14" t="n">
+        <v>-171</v>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>172</v>
+      </c>
+      <c r="I110" s="13">
+        <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
+        <v/>
+      </c>
+      <c r="J110" s="16">
+        <f>IF($H$110="","",$F$110*IF($H$110&lt;0,-100/$H$110,$H$110/100)-(1-$F$110))</f>
+        <v/>
+      </c>
+      <c r="K110" s="17">
+        <f>IF($H$110="","",MAX(0,($F$110*IF($H$110&lt;0,-100/$H$110,$H$110/100)-(1-$F$110))/IF($H$110&lt;0,-100/$H$110,$H$110/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L110" s="18">
+        <f>IF($H$110="","",ROUND(MIN($K$110,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M110" s="12">
+        <f>IF($J$110="","",IF($J$110&lt;0,"Pass",IF($J$110&lt;'Settings'!$B$4,"Thin",IF($J$110&lt;0.06,"✅ Sharp band",IF($J$110&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N110" s="19" t="inlineStr">
+        <is>
+          <t>Model 63.1% (fair -171). Your call.</t>
+        </is>
+      </c>
+      <c r="O110" s="15" t="n"/>
+      <c r="P110" s="16">
+        <f>IF(OR($H$110="",$O$110=""),"",(1+IF($H$110&lt;0,-100/$H$110,$H$110/100))/(1+IF($O$110&lt;0,-100/$O$110,$O$110/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>Houston Astros @ Washington Nationals</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>0.4464055299539171</v>
+      </c>
+      <c r="G111" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>117</v>
+      </c>
+      <c r="I111" s="13">
+        <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
+        <v/>
+      </c>
+      <c r="J111" s="16">
+        <f>IF($H$111="","",$F$111*IF($H$111&lt;0,-100/$H$111,$H$111/100)-(1-$F$111))</f>
+        <v/>
+      </c>
+      <c r="K111" s="17">
+        <f>IF($H$111="","",MAX(0,($F$111*IF($H$111&lt;0,-100/$H$111,$H$111/100)-(1-$F$111))/IF($H$111&lt;0,-100/$H$111,$H$111/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L111" s="18">
+        <f>IF($H$111="","",ROUND(MIN($K$111,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M111" s="12">
+        <f>IF($J$111="","",IF($J$111&lt;0,"Pass",IF($J$111&lt;'Settings'!$B$4,"Thin",IF($J$111&lt;0.06,"✅ Sharp band",IF($J$111&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N111" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.6% (fair +124). Your call.</t>
+        </is>
+      </c>
+      <c r="O111" s="15" t="n"/>
+      <c r="P111" s="16">
+        <f>IF(OR($H$111="",$O$111=""),"",(1+IF($H$111&lt;0,-100/$H$111,$H$111/100))/(1+IF($O$111&lt;0,-100/$O$111,$O$111/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B112" s="20" t="inlineStr">
+        <is>
+          <t>Houston Astros @ Washington Nationals</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E112" s="20" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="F112" s="13" t="n">
+        <v>0.5536202764976959</v>
+      </c>
+      <c r="G112" s="14" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H112" s="15" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I112" s="13">
+        <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
+        <v/>
+      </c>
+      <c r="J112" s="16">
+        <f>IF($H$112="","",$F$112*IF($H$112&lt;0,-100/$H$112,$H$112/100)-(1-$F$112))</f>
+        <v/>
+      </c>
+      <c r="K112" s="17">
+        <f>IF($H$112="","",MAX(0,($F$112*IF($H$112&lt;0,-100/$H$112,$H$112/100)-(1-$F$112))/IF($H$112&lt;0,-100/$H$112,$H$112/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L112" s="18">
+        <f>IF($H$112="","",ROUND(MIN($K$112,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M112" s="12">
+        <f>IF($J$112="","",IF($J$112&lt;0,"Pass",IF($J$112&lt;'Settings'!$B$4,"Thin",IF($J$112&lt;0.06,"✅ Sharp band",IF($J$112&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N112" s="19" t="inlineStr">
+        <is>
+          <t>Model 55.4% (fair -124). Your call.</t>
+        </is>
+      </c>
+      <c r="O112" s="15" t="n"/>
+      <c r="P112" s="16">
+        <f>IF(OR($H$112="",$O$112=""),"",(1+IF($H$112&lt;0,-100/$H$112,$H$112/100))/(1+IF($O$112&lt;0,-100/$O$112,$O$112/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Houston Astros @ Washington Nationals</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Over 9.5</t>
+        </is>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>-128</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>117</v>
+      </c>
+      <c r="I113" s="13">
+        <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
+        <v/>
+      </c>
+      <c r="J113" s="16">
+        <f>IF($H$113="","",$F$113*IF($H$113&lt;0,-100/$H$113,$H$113/100)-(1-$F$113))</f>
+        <v/>
+      </c>
+      <c r="K113" s="17">
+        <f>IF($H$113="","",MAX(0,($F$113*IF($H$113&lt;0,-100/$H$113,$H$113/100)-(1-$F$113))/IF($H$113&lt;0,-100/$H$113,$H$113/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L113" s="18">
+        <f>IF($H$113="","",ROUND(MIN($K$113,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M113" s="12">
+        <f>IF($J$113="","",IF($J$113&lt;0,"Pass",IF($J$113&lt;'Settings'!$B$4,"Thin",IF($J$113&lt;0.06,"✅ Sharp band",IF($J$113&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N113" s="19" t="inlineStr">
+        <is>
+          <t>Model 56.1% (fair -128). Your call.</t>
+        </is>
+      </c>
+      <c r="O113" s="15" t="n"/>
+      <c r="P113" s="16">
+        <f>IF(OR($H$113="",$O$113=""),"",(1+IF($H$113&lt;0,-100/$H$113,$H$113/100))/(1+IF($O$113&lt;0,-100/$O$113,$O$113/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B114" s="20" t="inlineStr">
+        <is>
+          <t>Houston Astros @ Washington Nationals</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="D114" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E114" s="20" t="inlineStr">
+        <is>
+          <t>Under 9.5</t>
+        </is>
+      </c>
+      <c r="F114" s="13" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="G114" s="14" t="n">
+        <v>128</v>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="I114" s="13">
+        <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
+        <v/>
+      </c>
+      <c r="J114" s="16">
+        <f>IF($H$114="","",$F$114*IF($H$114&lt;0,-100/$H$114,$H$114/100)-(1-$F$114))</f>
+        <v/>
+      </c>
+      <c r="K114" s="17">
+        <f>IF($H$114="","",MAX(0,($F$114*IF($H$114&lt;0,-100/$H$114,$H$114/100)-(1-$F$114))/IF($H$114&lt;0,-100/$H$114,$H$114/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L114" s="18">
+        <f>IF($H$114="","",ROUND(MIN($K$114,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M114" s="12">
+        <f>IF($J$114="","",IF($J$114&lt;0,"Pass",IF($J$114&lt;'Settings'!$B$4,"Thin",IF($J$114&lt;0.06,"✅ Sharp band",IF($J$114&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N114" s="19" t="inlineStr">
+        <is>
+          <t>Model 43.9% (fair +128). Your call.</t>
+        </is>
+      </c>
+      <c r="O114" s="15" t="n"/>
+      <c r="P114" s="16">
+        <f>IF(OR($H$114="",$O$114=""),"",(1+IF($H$114&lt;0,-100/$H$114,$H$114/100))/(1+IF($O$114&lt;0,-100/$O$114,$O$114/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>Houston Astros @ Washington Nationals</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>Washington Nationals -1.5</t>
+        </is>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>0.403968253968254</v>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>148</v>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>152</v>
+      </c>
+      <c r="I115" s="13">
+        <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
+        <v/>
+      </c>
+      <c r="J115" s="16">
+        <f>IF($H$115="","",$F$115*IF($H$115&lt;0,-100/$H$115,$H$115/100)-(1-$F$115))</f>
+        <v/>
+      </c>
+      <c r="K115" s="17">
+        <f>IF($H$115="","",MAX(0,($F$115*IF($H$115&lt;0,-100/$H$115,$H$115/100)-(1-$F$115))/IF($H$115&lt;0,-100/$H$115,$H$115/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L115" s="18">
+        <f>IF($H$115="","",ROUND(MIN($K$115,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M115" s="12">
+        <f>IF($J$115="","",IF($J$115&lt;0,"Pass",IF($J$115&lt;'Settings'!$B$4,"Thin",IF($J$115&lt;0.06,"✅ Sharp band",IF($J$115&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N115" s="19" t="inlineStr">
+        <is>
+          <t>Model 40.4% (fair +148). Your call.</t>
+        </is>
+      </c>
+      <c r="O115" s="15" t="n"/>
+      <c r="P115" s="16">
+        <f>IF(OR($H$115="",$O$115=""),"",(1+IF($H$115&lt;0,-100/$H$115,$H$115/100))/(1+IF($O$115&lt;0,-100/$O$115,$O$115/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B116" s="20" t="inlineStr">
+        <is>
+          <t>Houston Astros @ Washington Nationals</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="D116" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E116" s="20" t="inlineStr">
+        <is>
+          <t>Houston Astros +1.5</t>
+        </is>
+      </c>
+      <c r="F116" s="13" t="n">
+        <v>0.5959924528301888</v>
+      </c>
+      <c r="G116" s="14" t="n">
+        <v>-148</v>
+      </c>
+      <c r="H116" s="15" t="n">
+        <v>-165</v>
+      </c>
+      <c r="I116" s="13">
+        <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
+        <v/>
+      </c>
+      <c r="J116" s="16">
+        <f>IF($H$116="","",$F$116*IF($H$116&lt;0,-100/$H$116,$H$116/100)-(1-$F$116))</f>
+        <v/>
+      </c>
+      <c r="K116" s="17">
+        <f>IF($H$116="","",MAX(0,($F$116*IF($H$116&lt;0,-100/$H$116,$H$116/100)-(1-$F$116))/IF($H$116&lt;0,-100/$H$116,$H$116/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L116" s="18">
+        <f>IF($H$116="","",ROUND(MIN($K$116,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M116" s="12">
+        <f>IF($J$116="","",IF($J$116&lt;0,"Pass",IF($J$116&lt;'Settings'!$B$4,"Thin",IF($J$116&lt;0.06,"✅ Sharp band",IF($J$116&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N116" s="19" t="inlineStr">
+        <is>
+          <t>Model 59.6% (fair -148). Your call.</t>
+        </is>
+      </c>
+      <c r="O116" s="15" t="n"/>
+      <c r="P116" s="16">
+        <f>IF(OR($H$116="",$O$116=""),"",(1+IF($H$116&lt;0,-100/$H$116,$H$116/100))/(1+IF($O$116&lt;0,-100/$O$116,$O$116/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>Kansas City Royals @ New York Mets</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>0.430704845814978</v>
+      </c>
+      <c r="G117" s="14" t="n">
+        <v>132</v>
+      </c>
+      <c r="H117" s="15" t="n">
+        <v>127</v>
+      </c>
+      <c r="I117" s="13">
+        <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
+        <v/>
+      </c>
+      <c r="J117" s="16">
+        <f>IF($H$117="","",$F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))</f>
+        <v/>
+      </c>
+      <c r="K117" s="17">
+        <f>IF($H$117="","",MAX(0,($F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))/IF($H$117&lt;0,-100/$H$117,$H$117/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L117" s="18">
+        <f>IF($H$117="","",ROUND(MIN($K$117,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M117" s="12">
+        <f>IF($J$117="","",IF($J$117&lt;0,"Pass",IF($J$117&lt;'Settings'!$B$4,"Thin",IF($J$117&lt;0.06,"✅ Sharp band",IF($J$117&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N117" s="19" t="inlineStr">
+        <is>
+          <t>Model 43.1% (fair +132). Your call.</t>
+        </is>
+      </c>
+      <c r="O117" s="15" t="n"/>
+      <c r="P117" s="16">
+        <f>IF(OR($H$117="",$O$117=""),"",(1+IF($H$117&lt;0,-100/$H$117,$H$117/100))/(1+IF($O$117&lt;0,-100/$O$117,$O$117/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>Kansas City Royals @ New York Mets</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D118" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E118" s="20" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="F118" s="13" t="n">
+        <v>0.5692742489270386</v>
+      </c>
+      <c r="G118" s="14" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H118" s="15" t="n">
+        <v>-133</v>
+      </c>
+      <c r="I118" s="13">
+        <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
+        <v/>
+      </c>
+      <c r="J118" s="16">
+        <f>IF($H$118="","",$F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))</f>
+        <v/>
+      </c>
+      <c r="K118" s="17">
+        <f>IF($H$118="","",MAX(0,($F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))/IF($H$118&lt;0,-100/$H$118,$H$118/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L118" s="18">
+        <f>IF($H$118="","",ROUND(MIN($K$118,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M118" s="12">
+        <f>IF($J$118="","",IF($J$118&lt;0,"Pass",IF($J$118&lt;'Settings'!$B$4,"Thin",IF($J$118&lt;0.06,"✅ Sharp band",IF($J$118&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N118" s="19" t="inlineStr">
+        <is>
+          <t>Model 56.9% (fair -132). Your call.</t>
+        </is>
+      </c>
+      <c r="O118" s="15" t="n"/>
+      <c r="P118" s="16">
+        <f>IF(OR($H$118="",$O$118=""),"",(1+IF($H$118&lt;0,-100/$H$118,$H$118/100))/(1+IF($O$118&lt;0,-100/$O$118,$O$118/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>0.5134803921568628</v>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>-106</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="I119" s="13">
+        <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
+        <v/>
+      </c>
+      <c r="J119" s="16">
+        <f>IF($H$119="","",$F$119*IF($H$119&lt;0,-100/$H$119,$H$119/100)-(1-$F$119))</f>
+        <v/>
+      </c>
+      <c r="K119" s="17">
+        <f>IF($H$119="","",MAX(0,($F$119*IF($H$119&lt;0,-100/$H$119,$H$119/100)-(1-$F$119))/IF($H$119&lt;0,-100/$H$119,$H$119/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L119" s="18">
+        <f>IF($H$119="","",ROUND(MIN($K$119,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M119" s="12">
+        <f>IF($J$119="","",IF($J$119&lt;0,"Pass",IF($J$119&lt;'Settings'!$B$4,"Thin",IF($J$119&lt;0.06,"✅ Sharp band",IF($J$119&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N119" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.3% (fair -106). Your call.</t>
+        </is>
+      </c>
+      <c r="O119" s="15" t="n"/>
+      <c r="P119" s="16">
+        <f>IF(OR($H$119="",$O$119=""),"",(1+IF($H$119&lt;0,-100/$H$119,$H$119/100))/(1+IF($O$119&lt;0,-100/$O$119,$O$119/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B120" s="20" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D120" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E120" s="20" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="F120" s="13" t="n">
+        <v>0.4865058823529412</v>
+      </c>
+      <c r="G120" s="14" t="n">
+        <v>106</v>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I120" s="13">
+        <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
+        <v/>
+      </c>
+      <c r="J120" s="16">
+        <f>IF($H$120="","",$F$120*IF($H$120&lt;0,-100/$H$120,$H$120/100)-(1-$F$120))</f>
+        <v/>
+      </c>
+      <c r="K120" s="17">
+        <f>IF($H$120="","",MAX(0,($F$120*IF($H$120&lt;0,-100/$H$120,$H$120/100)-(1-$F$120))/IF($H$120&lt;0,-100/$H$120,$H$120/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L120" s="18">
+        <f>IF($H$120="","",ROUND(MIN($K$120,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M120" s="12">
+        <f>IF($J$120="","",IF($J$120&lt;0,"Pass",IF($J$120&lt;'Settings'!$B$4,"Thin",IF($J$120&lt;0.06,"✅ Sharp band",IF($J$120&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N120" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.7% (fair +106). Your call.</t>
+        </is>
+      </c>
+      <c r="O120" s="15" t="n"/>
+      <c r="P120" s="16">
+        <f>IF(OR($H$120="",$O$120=""),"",(1+IF($H$120&lt;0,-100/$H$120,$H$120/100))/(1+IF($O$120&lt;0,-100/$O$120,$O$120/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>0.4292093023255814</v>
+      </c>
+      <c r="G121" s="14" t="n">
+        <v>133</v>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>115</v>
+      </c>
+      <c r="I121" s="13">
+        <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
+        <v/>
+      </c>
+      <c r="J121" s="16">
+        <f>IF($H$121="","",$F$121*IF($H$121&lt;0,-100/$H$121,$H$121/100)-(1-$F$121))</f>
+        <v/>
+      </c>
+      <c r="K121" s="17">
+        <f>IF($H$121="","",MAX(0,($F$121*IF($H$121&lt;0,-100/$H$121,$H$121/100)-(1-$F$121))/IF($H$121&lt;0,-100/$H$121,$H$121/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L121" s="18">
+        <f>IF($H$121="","",ROUND(MIN($K$121,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M121" s="12">
+        <f>IF($J$121="","",IF($J$121&lt;0,"Pass",IF($J$121&lt;'Settings'!$B$4,"Thin",IF($J$121&lt;0.06,"✅ Sharp band",IF($J$121&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N121" s="19" t="inlineStr">
+        <is>
+          <t>Model 42.9% (fair +133). Your call.</t>
+        </is>
+      </c>
+      <c r="O121" s="15" t="n"/>
+      <c r="P121" s="16">
+        <f>IF(OR($H$121="",$O$121=""),"",(1+IF($H$121&lt;0,-100/$H$121,$H$121/100))/(1+IF($O$121&lt;0,-100/$O$121,$O$121/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B122" s="20" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D122" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E122" s="20" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="F122" s="13" t="n">
+        <v>0.5707826291079813</v>
+      </c>
+      <c r="G122" s="14" t="n">
+        <v>-133</v>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>-113</v>
+      </c>
+      <c r="I122" s="13">
+        <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
+        <v/>
+      </c>
+      <c r="J122" s="16">
+        <f>IF($H$122="","",$F$122*IF($H$122&lt;0,-100/$H$122,$H$122/100)-(1-$F$122))</f>
+        <v/>
+      </c>
+      <c r="K122" s="17">
+        <f>IF($H$122="","",MAX(0,($F$122*IF($H$122&lt;0,-100/$H$122,$H$122/100)-(1-$F$122))/IF($H$122&lt;0,-100/$H$122,$H$122/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L122" s="18">
+        <f>IF($H$122="","",ROUND(MIN($K$122,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M122" s="12">
+        <f>IF($J$122="","",IF($J$122&lt;0,"Pass",IF($J$122&lt;'Settings'!$B$4,"Thin",IF($J$122&lt;0.06,"✅ Sharp band",IF($J$122&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N122" s="19" t="inlineStr">
+        <is>
+          <t>Model 57.1% (fair -133). Your call.</t>
+        </is>
+      </c>
+      <c r="O122" s="15" t="n"/>
+      <c r="P122" s="16">
+        <f>IF(OR($H$122="",$O$122=""),"",(1+IF($H$122&lt;0,-100/$H$122,$H$122/100))/(1+IF($O$122&lt;0,-100/$O$122,$O$122/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>Over 8.5</t>
+        </is>
+      </c>
+      <c r="F123" s="13" t="n">
+        <v>0.510709756097561</v>
+      </c>
+      <c r="G123" s="14" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I123" s="13">
+        <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
+        <v/>
+      </c>
+      <c r="J123" s="16">
+        <f>IF($H$123="","",$F$123*IF($H$123&lt;0,-100/$H$123,$H$123/100)-(1-$F$123))</f>
+        <v/>
+      </c>
+      <c r="K123" s="17">
+        <f>IF($H$123="","",MAX(0,($F$123*IF($H$123&lt;0,-100/$H$123,$H$123/100)-(1-$F$123))/IF($H$123&lt;0,-100/$H$123,$H$123/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L123" s="18">
+        <f>IF($H$123="","",ROUND(MIN($K$123,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M123" s="12">
+        <f>IF($J$123="","",IF($J$123&lt;0,"Pass",IF($J$123&lt;'Settings'!$B$4,"Thin",IF($J$123&lt;0.06,"✅ Sharp band",IF($J$123&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N123" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.1% (fair -104). Your call.</t>
+        </is>
+      </c>
+      <c r="O123" s="15" t="n"/>
+      <c r="P123" s="16">
+        <f>IF(OR($H$123="",$O$123=""),"",(1+IF($H$123&lt;0,-100/$H$123,$H$123/100))/(1+IF($O$123&lt;0,-100/$O$123,$O$123/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B124" s="20" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D124" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E124" s="20" t="inlineStr">
+        <is>
+          <t>Under 8.5</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="n">
+        <v>0.4892411214953271</v>
+      </c>
+      <c r="G124" s="14" t="n">
+        <v>104</v>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>-114</v>
+      </c>
+      <c r="I124" s="13">
+        <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
+        <v/>
+      </c>
+      <c r="J124" s="16">
+        <f>IF($H$124="","",$F$124*IF($H$124&lt;0,-100/$H$124,$H$124/100)-(1-$F$124))</f>
+        <v/>
+      </c>
+      <c r="K124" s="17">
+        <f>IF($H$124="","",MAX(0,($F$124*IF($H$124&lt;0,-100/$H$124,$H$124/100)-(1-$F$124))/IF($H$124&lt;0,-100/$H$124,$H$124/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L124" s="18">
+        <f>IF($H$124="","",ROUND(MIN($K$124,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M124" s="12">
+        <f>IF($J$124="","",IF($J$124&lt;0,"Pass",IF($J$124&lt;'Settings'!$B$4,"Thin",IF($J$124&lt;0.06,"✅ Sharp band",IF($J$124&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N124" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.9% (fair +104). Your call.</t>
+        </is>
+      </c>
+      <c r="O124" s="15" t="n"/>
+      <c r="P124" s="16">
+        <f>IF(OR($H$124="",$O$124=""),"",(1+IF($H$124&lt;0,-100/$H$124,$H$124/100))/(1+IF($O$124&lt;0,-100/$O$124,$O$124/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>Minnesota Twins -1.5</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="n">
+        <v>0.3965530303030304</v>
+      </c>
+      <c r="G125" s="14" t="n">
+        <v>152</v>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>164</v>
+      </c>
+      <c r="I125" s="13">
+        <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
+        <v/>
+      </c>
+      <c r="J125" s="16">
+        <f>IF($H$125="","",$F$125*IF($H$125&lt;0,-100/$H$125,$H$125/100)-(1-$F$125))</f>
+        <v/>
+      </c>
+      <c r="K125" s="17">
+        <f>IF($H$125="","",MAX(0,($F$125*IF($H$125&lt;0,-100/$H$125,$H$125/100)-(1-$F$125))/IF($H$125&lt;0,-100/$H$125,$H$125/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L125" s="18">
+        <f>IF($H$125="","",ROUND(MIN($K$125,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M125" s="12">
+        <f>IF($J$125="","",IF($J$125&lt;0,"Pass",IF($J$125&lt;'Settings'!$B$4,"Thin",IF($J$125&lt;0.06,"✅ Sharp band",IF($J$125&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N125" s="19" t="inlineStr">
+        <is>
+          <t>Model 39.7% (fair +152). Your call.</t>
+        </is>
+      </c>
+      <c r="O125" s="15" t="n"/>
+      <c r="P125" s="16">
+        <f>IF(OR($H$125="",$O$125=""),"",(1+IF($H$125&lt;0,-100/$H$125,$H$125/100))/(1+IF($O$125&lt;0,-100/$O$125,$O$125/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B126" s="20" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D126" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E126" s="20" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians +1.5</t>
+        </is>
+      </c>
+      <c r="F126" s="13" t="n">
+        <v>0.6034245614035088</v>
+      </c>
+      <c r="G126" s="14" t="n">
+        <v>-152</v>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>-185</v>
+      </c>
+      <c r="I126" s="13">
+        <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
+        <v/>
+      </c>
+      <c r="J126" s="16">
+        <f>IF($H$126="","",$F$126*IF($H$126&lt;0,-100/$H$126,$H$126/100)-(1-$F$126))</f>
+        <v/>
+      </c>
+      <c r="K126" s="17">
+        <f>IF($H$126="","",MAX(0,($F$126*IF($H$126&lt;0,-100/$H$126,$H$126/100)-(1-$F$126))/IF($H$126&lt;0,-100/$H$126,$H$126/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L126" s="18">
+        <f>IF($H$126="","",ROUND(MIN($K$126,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M126" s="12">
+        <f>IF($J$126="","",IF($J$126&lt;0,"Pass",IF($J$126&lt;'Settings'!$B$4,"Thin",IF($J$126&lt;0.06,"✅ Sharp band",IF($J$126&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N126" s="19" t="inlineStr">
+        <is>
+          <t>Model 60.3% (fair -152). Your call.</t>
+        </is>
+      </c>
+      <c r="O126" s="15" t="n"/>
+      <c r="P126" s="16">
+        <f>IF(OR($H$126="",$O$126=""),"",(1+IF($H$126&lt;0,-100/$H$126,$H$126/100))/(1+IF($O$126&lt;0,-100/$O$126,$O$126/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="F127" s="13" t="n">
+        <v>0.4398</v>
+      </c>
+      <c r="G127" s="14" t="n">
+        <v>127</v>
+      </c>
+      <c r="H127" s="15" t="n"/>
+      <c r="I127" s="13">
+        <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
+        <v/>
+      </c>
+      <c r="J127" s="16">
+        <f>IF($H$127="","",$F$127*IF($H$127&lt;0,-100/$H$127,$H$127/100)-(1-$F$127))</f>
+        <v/>
+      </c>
+      <c r="K127" s="17">
+        <f>IF($H$127="","",MAX(0,($F$127*IF($H$127&lt;0,-100/$H$127,$H$127/100)-(1-$F$127))/IF($H$127&lt;0,-100/$H$127,$H$127/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L127" s="18">
+        <f>IF($H$127="","",ROUND(MIN($K$127,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M127" s="12">
+        <f>IF($J$127="","",IF($J$127&lt;0,"Pass",IF($J$127&lt;'Settings'!$B$4,"Thin",IF($J$127&lt;0.06,"✅ Sharp band",IF($J$127&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N127" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.0% (fair +127). Your call.</t>
+        </is>
+      </c>
+      <c r="O127" s="15" t="n"/>
+      <c r="P127" s="16">
+        <f>IF(OR($H$127="",$O$127=""),"",(1+IF($H$127&lt;0,-100/$H$127,$H$127/100))/(1+IF($O$127&lt;0,-100/$O$127,$O$127/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B128" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C128" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D128" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E128" s="20" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="F128" s="13" t="n">
+        <v>0.5602</v>
+      </c>
+      <c r="G128" s="14" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H128" s="15" t="n"/>
+      <c r="I128" s="13">
+        <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
+        <v/>
+      </c>
+      <c r="J128" s="16">
+        <f>IF($H$128="","",$F$128*IF($H$128&lt;0,-100/$H$128,$H$128/100)-(1-$F$128))</f>
+        <v/>
+      </c>
+      <c r="K128" s="17">
+        <f>IF($H$128="","",MAX(0,($F$128*IF($H$128&lt;0,-100/$H$128,$H$128/100)-(1-$F$128))/IF($H$128&lt;0,-100/$H$128,$H$128/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L128" s="18">
+        <f>IF($H$128="","",ROUND(MIN($K$128,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M128" s="12">
+        <f>IF($J$128="","",IF($J$128&lt;0,"Pass",IF($J$128&lt;'Settings'!$B$4,"Thin",IF($J$128&lt;0.06,"✅ Sharp band",IF($J$128&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N128" s="19" t="inlineStr">
+        <is>
+          <t>Model 56.0% (fair -127). Your call.</t>
+        </is>
+      </c>
+      <c r="O128" s="15" t="n"/>
+      <c r="P128" s="16">
+        <f>IF(OR($H$128="",$O$128=""),"",(1+IF($H$128&lt;0,-100/$H$128,$H$128/100))/(1+IF($O$128&lt;0,-100/$O$128,$O$128/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>Over 8.5</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="n">
+        <v>0.4969</v>
+      </c>
+      <c r="G129" s="14" t="n">
+        <v>101</v>
+      </c>
+      <c r="H129" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I129" s="13">
+        <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
+        <v/>
+      </c>
+      <c r="J129" s="16">
+        <f>IF($H$129="","",$F$129*IF($H$129&lt;0,-100/$H$129,$H$129/100)-(1-$F$129))</f>
+        <v/>
+      </c>
+      <c r="K129" s="17">
+        <f>IF($H$129="","",MAX(0,($F$129*IF($H$129&lt;0,-100/$H$129,$H$129/100)-(1-$F$129))/IF($H$129&lt;0,-100/$H$129,$H$129/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L129" s="18">
+        <f>IF($H$129="","",ROUND(MIN($K$129,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M129" s="12">
+        <f>IF($J$129="","",IF($J$129&lt;0,"Pass",IF($J$129&lt;'Settings'!$B$4,"Thin",IF($J$129&lt;0.06,"✅ Sharp band",IF($J$129&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N129" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.7% (fair +101). Your call.</t>
+        </is>
+      </c>
+      <c r="O129" s="15" t="n"/>
+      <c r="P129" s="16">
+        <f>IF(OR($H$129="",$O$129=""),"",(1+IF($H$129&lt;0,-100/$H$129,$H$129/100))/(1+IF($O$129&lt;0,-100/$O$129,$O$129/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B130" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C130" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D130" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E130" s="20" t="inlineStr">
+        <is>
+          <t>Under 8.5</t>
+        </is>
+      </c>
+      <c r="F130" s="13" t="n">
+        <v>0.5031219512195123</v>
+      </c>
+      <c r="G130" s="14" t="n">
+        <v>-101</v>
+      </c>
+      <c r="H130" s="15" t="n">
+        <v>105</v>
+      </c>
+      <c r="I130" s="13">
+        <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
+        <v/>
+      </c>
+      <c r="J130" s="16">
+        <f>IF($H$130="","",$F$130*IF($H$130&lt;0,-100/$H$130,$H$130/100)-(1-$F$130))</f>
+        <v/>
+      </c>
+      <c r="K130" s="17">
+        <f>IF($H$130="","",MAX(0,($F$130*IF($H$130&lt;0,-100/$H$130,$H$130/100)-(1-$F$130))/IF($H$130&lt;0,-100/$H$130,$H$130/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L130" s="18">
+        <f>IF($H$130="","",ROUND(MIN($K$130,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M130" s="12">
+        <f>IF($J$130="","",IF($J$130&lt;0,"Pass",IF($J$130&lt;'Settings'!$B$4,"Thin",IF($J$130&lt;0.06,"✅ Sharp band",IF($J$130&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N130" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.3% (fair -101). Your call.</t>
+        </is>
+      </c>
+      <c r="O130" s="15" t="n"/>
+      <c r="P130" s="16">
+        <f>IF(OR($H$130="",$O$130=""),"",(1+IF($H$130&lt;0,-100/$H$130,$H$130/100))/(1+IF($O$130&lt;0,-100/$O$130,$O$130/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Chicago White Sox -1.5</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="n">
+        <v>0.4123880597014926</v>
+      </c>
+      <c r="G131" s="14" t="n">
+        <v>142</v>
+      </c>
+      <c r="H131" s="15" t="n">
+        <v>168</v>
+      </c>
+      <c r="I131" s="13">
+        <f>IF($H$131="","",IF($H$131&lt;0,-$H$131/(-$H$131+100),100/($H$131+100)))</f>
+        <v/>
+      </c>
+      <c r="J131" s="16">
+        <f>IF($H$131="","",$F$131*IF($H$131&lt;0,-100/$H$131,$H$131/100)-(1-$F$131))</f>
+        <v/>
+      </c>
+      <c r="K131" s="17">
+        <f>IF($H$131="","",MAX(0,($F$131*IF($H$131&lt;0,-100/$H$131,$H$131/100)-(1-$F$131))/IF($H$131&lt;0,-100/$H$131,$H$131/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L131" s="18">
+        <f>IF($H$131="","",ROUND(MIN($K$131,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M131" s="12">
+        <f>IF($J$131="","",IF($J$131&lt;0,"Pass",IF($J$131&lt;'Settings'!$B$4,"Thin",IF($J$131&lt;0.06,"✅ Sharp band",IF($J$131&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N131" s="19" t="inlineStr">
+        <is>
+          <t>Model 41.2% (fair +142). Your call.</t>
+        </is>
+      </c>
+      <c r="O131" s="15" t="n"/>
+      <c r="P131" s="16">
+        <f>IF(OR($H$131="",$O$131=""),"",(1+IF($H$131&lt;0,-100/$H$131,$H$131/100))/(1+IF($O$131&lt;0,-100/$O$131,$O$131/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C132" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D132" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox +1.5</t>
+        </is>
+      </c>
+      <c r="F132" s="13" t="n">
+        <v>0.5876119402985075</v>
+      </c>
+      <c r="G132" s="14" t="n">
+        <v>-142</v>
+      </c>
+      <c r="H132" s="15" t="n">
+        <v>168</v>
+      </c>
+      <c r="I132" s="13">
+        <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
+        <v/>
+      </c>
+      <c r="J132" s="16">
+        <f>IF($H$132="","",$F$132*IF($H$132&lt;0,-100/$H$132,$H$132/100)-(1-$F$132))</f>
+        <v/>
+      </c>
+      <c r="K132" s="17">
+        <f>IF($H$132="","",MAX(0,($F$132*IF($H$132&lt;0,-100/$H$132,$H$132/100)-(1-$F$132))/IF($H$132&lt;0,-100/$H$132,$H$132/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L132" s="18">
+        <f>IF($H$132="","",ROUND(MIN($K$132,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M132" s="12">
+        <f>IF($J$132="","",IF($J$132&lt;0,"Pass",IF($J$132&lt;'Settings'!$B$4,"Thin",IF($J$132&lt;0.06,"✅ Sharp band",IF($J$132&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N132" s="19" t="inlineStr">
+        <is>
+          <t>Model 58.8% (fair -142). Your call.</t>
+        </is>
+      </c>
+      <c r="O132" s="15" t="n"/>
+      <c r="P132" s="16">
+        <f>IF(OR($H$132="",$O$132=""),"",(1+IF($H$132&lt;0,-100/$H$132,$H$132/100))/(1+IF($O$132&lt;0,-100/$O$132,$O$132/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="n">
+        <v>0.5924</v>
+      </c>
+      <c r="G133" s="14" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H133" s="15" t="n"/>
+      <c r="I133" s="13">
+        <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
+        <v/>
+      </c>
+      <c r="J133" s="16">
+        <f>IF($H$133="","",$F$133*IF($H$133&lt;0,-100/$H$133,$H$133/100)-(1-$F$133))</f>
+        <v/>
+      </c>
+      <c r="K133" s="17">
+        <f>IF($H$133="","",MAX(0,($F$133*IF($H$133&lt;0,-100/$H$133,$H$133/100)-(1-$F$133))/IF($H$133&lt;0,-100/$H$133,$H$133/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L133" s="18">
+        <f>IF($H$133="","",ROUND(MIN($K$133,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M133" s="12">
+        <f>IF($J$133="","",IF($J$133&lt;0,"Pass",IF($J$133&lt;'Settings'!$B$4,"Thin",IF($J$133&lt;0.06,"✅ Sharp band",IF($J$133&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N133" s="19" t="inlineStr">
+        <is>
+          <t>Model 59.2% (fair -145). Your call.</t>
+        </is>
+      </c>
+      <c r="O133" s="15" t="n"/>
+      <c r="P133" s="16">
+        <f>IF(OR($H$133="",$O$133=""),"",(1+IF($H$133&lt;0,-100/$H$133,$H$133/100))/(1+IF($O$133&lt;0,-100/$O$133,$O$133/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B134" s="20" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C134" s="20" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="D134" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E134" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="F134" s="13" t="n">
+        <v>0.4076</v>
+      </c>
+      <c r="G134" s="14" t="n">
+        <v>145</v>
+      </c>
+      <c r="H134" s="15" t="n"/>
+      <c r="I134" s="13">
+        <f>IF($H$134="","",IF($H$134&lt;0,-$H$134/(-$H$134+100),100/($H$134+100)))</f>
+        <v/>
+      </c>
+      <c r="J134" s="16">
+        <f>IF($H$134="","",$F$134*IF($H$134&lt;0,-100/$H$134,$H$134/100)-(1-$F$134))</f>
+        <v/>
+      </c>
+      <c r="K134" s="17">
+        <f>IF($H$134="","",MAX(0,($F$134*IF($H$134&lt;0,-100/$H$134,$H$134/100)-(1-$F$134))/IF($H$134&lt;0,-100/$H$134,$H$134/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L134" s="18">
+        <f>IF($H$134="","",ROUND(MIN($K$134,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M134" s="12">
+        <f>IF($J$134="","",IF($J$134&lt;0,"Pass",IF($J$134&lt;'Settings'!$B$4,"Thin",IF($J$134&lt;0.06,"✅ Sharp band",IF($J$134&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N134" s="19" t="inlineStr">
+        <is>
+          <t>Model 40.8% (fair +145). Your call.</t>
+        </is>
+      </c>
+      <c r="O134" s="15" t="n"/>
+      <c r="P134" s="16">
+        <f>IF(OR($H$134="",$O$134=""),"",(1+IF($H$134&lt;0,-100/$H$134,$H$134/100))/(1+IF($O$134&lt;0,-100/$O$134,$O$134/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>Over 8.5</t>
+        </is>
+      </c>
+      <c r="F135" s="13" t="n">
+        <v>0.50425</v>
+      </c>
+      <c r="G135" s="14" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H135" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I135" s="13">
+        <f>IF($H$135="","",IF($H$135&lt;0,-$H$135/(-$H$135+100),100/($H$135+100)))</f>
+        <v/>
+      </c>
+      <c r="J135" s="16">
+        <f>IF($H$135="","",$F$135*IF($H$135&lt;0,-100/$H$135,$H$135/100)-(1-$F$135))</f>
+        <v/>
+      </c>
+      <c r="K135" s="17">
+        <f>IF($H$135="","",MAX(0,($F$135*IF($H$135&lt;0,-100/$H$135,$H$135/100)-(1-$F$135))/IF($H$135&lt;0,-100/$H$135,$H$135/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L135" s="18">
+        <f>IF($H$135="","",ROUND(MIN($K$135,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M135" s="12">
+        <f>IF($J$135="","",IF($J$135&lt;0,"Pass",IF($J$135&lt;'Settings'!$B$4,"Thin",IF($J$135&lt;0.06,"✅ Sharp band",IF($J$135&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N135" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.4% (fair -102). Your call.</t>
+        </is>
+      </c>
+      <c r="O135" s="15" t="n"/>
+      <c r="P135" s="16">
+        <f>IF(OR($H$135="",$O$135=""),"",(1+IF($H$135&lt;0,-100/$H$135,$H$135/100))/(1+IF($O$135&lt;0,-100/$O$135,$O$135/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B136" s="20" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C136" s="20" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="D136" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E136" s="20" t="inlineStr">
+        <is>
+          <t>Under 8.5</t>
+        </is>
+      </c>
+      <c r="F136" s="13" t="n">
+        <v>0.4957333333333333</v>
+      </c>
+      <c r="G136" s="14" t="n">
+        <v>102</v>
+      </c>
+      <c r="H136" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I136" s="13">
+        <f>IF($H$136="","",IF($H$136&lt;0,-$H$136/(-$H$136+100),100/($H$136+100)))</f>
+        <v/>
+      </c>
+      <c r="J136" s="16">
+        <f>IF($H$136="","",$F$136*IF($H$136&lt;0,-100/$H$136,$H$136/100)-(1-$F$136))</f>
+        <v/>
+      </c>
+      <c r="K136" s="17">
+        <f>IF($H$136="","",MAX(0,($F$136*IF($H$136&lt;0,-100/$H$136,$H$136/100)-(1-$F$136))/IF($H$136&lt;0,-100/$H$136,$H$136/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L136" s="18">
+        <f>IF($H$136="","",ROUND(MIN($K$136,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M136" s="12">
+        <f>IF($J$136="","",IF($J$136&lt;0,"Pass",IF($J$136&lt;'Settings'!$B$4,"Thin",IF($J$136&lt;0.06,"✅ Sharp band",IF($J$136&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N136" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.6% (fair +102). Your call.</t>
+        </is>
+      </c>
+      <c r="O136" s="15" t="n"/>
+      <c r="P136" s="16">
+        <f>IF(OR($H$136="",$O$136=""),"",(1+IF($H$136&lt;0,-100/$H$136,$H$136/100))/(1+IF($O$136&lt;0,-100/$O$136,$O$136/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals +1.5</t>
+        </is>
+      </c>
+      <c r="F137" s="13" t="n">
+        <v>0.5539333333333333</v>
+      </c>
+      <c r="G137" s="14" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H137" s="15" t="n">
+        <v>-140</v>
+      </c>
+      <c r="I137" s="13">
+        <f>IF($H$137="","",IF($H$137&lt;0,-$H$137/(-$H$137+100),100/($H$137+100)))</f>
+        <v/>
+      </c>
+      <c r="J137" s="16">
+        <f>IF($H$137="","",$F$137*IF($H$137&lt;0,-100/$H$137,$H$137/100)-(1-$F$137))</f>
+        <v/>
+      </c>
+      <c r="K137" s="17">
+        <f>IF($H$137="","",MAX(0,($F$137*IF($H$137&lt;0,-100/$H$137,$H$137/100)-(1-$F$137))/IF($H$137&lt;0,-100/$H$137,$H$137/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L137" s="18">
+        <f>IF($H$137="","",ROUND(MIN($K$137,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M137" s="12">
+        <f>IF($J$137="","",IF($J$137&lt;0,"Pass",IF($J$137&lt;'Settings'!$B$4,"Thin",IF($J$137&lt;0.06,"✅ Sharp band",IF($J$137&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N137" s="19" t="inlineStr">
+        <is>
+          <t>Model 55.4% (fair -124). Your call.</t>
+        </is>
+      </c>
+      <c r="O137" s="15" t="n"/>
+      <c r="P137" s="16">
+        <f>IF(OR($H$137="",$O$137=""),"",(1+IF($H$137&lt;0,-100/$H$137,$H$137/100))/(1+IF($O$137&lt;0,-100/$O$137,$O$137/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B138" s="20" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C138" s="20" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="D138" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E138" s="20" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers -1.5</t>
+        </is>
+      </c>
+      <c r="F138" s="13" t="n">
+        <v>0.4461009174311927</v>
+      </c>
+      <c r="G138" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="H138" s="15" t="n">
+        <v>118</v>
+      </c>
+      <c r="I138" s="13">
+        <f>IF($H$138="","",IF($H$138&lt;0,-$H$138/(-$H$138+100),100/($H$138+100)))</f>
+        <v/>
+      </c>
+      <c r="J138" s="16">
+        <f>IF($H$138="","",$F$138*IF($H$138&lt;0,-100/$H$138,$H$138/100)-(1-$F$138))</f>
+        <v/>
+      </c>
+      <c r="K138" s="17">
+        <f>IF($H$138="","",MAX(0,($F$138*IF($H$138&lt;0,-100/$H$138,$H$138/100)-(1-$F$138))/IF($H$138&lt;0,-100/$H$138,$H$138/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L138" s="18">
+        <f>IF($H$138="","",ROUND(MIN($K$138,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M138" s="12">
+        <f>IF($J$138="","",IF($J$138&lt;0,"Pass",IF($J$138&lt;'Settings'!$B$4,"Thin",IF($J$138&lt;0.06,"✅ Sharp band",IF($J$138&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N138" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.6% (fair +124). Your call.</t>
+        </is>
+      </c>
+      <c r="O138" s="15" t="n"/>
+      <c r="P138" s="16">
+        <f>IF(OR($H$138="",$O$138=""),"",(1+IF($H$138&lt;0,-100/$H$138,$H$138/100))/(1+IF($O$138&lt;0,-100/$O$138,$O$138/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="F139" s="13" t="n">
+        <v>0.4669</v>
+      </c>
+      <c r="G139" s="14" t="n">
+        <v>114</v>
+      </c>
+      <c r="H139" s="15" t="n"/>
+      <c r="I139" s="13">
+        <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
+        <v/>
+      </c>
+      <c r="J139" s="16">
+        <f>IF($H$139="","",$F$139*IF($H$139&lt;0,-100/$H$139,$H$139/100)-(1-$F$139))</f>
+        <v/>
+      </c>
+      <c r="K139" s="17">
+        <f>IF($H$139="","",MAX(0,($F$139*IF($H$139&lt;0,-100/$H$139,$H$139/100)-(1-$F$139))/IF($H$139&lt;0,-100/$H$139,$H$139/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L139" s="18">
+        <f>IF($H$139="","",ROUND(MIN($K$139,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M139" s="12">
+        <f>IF($J$139="","",IF($J$139&lt;0,"Pass",IF($J$139&lt;'Settings'!$B$4,"Thin",IF($J$139&lt;0.06,"✅ Sharp band",IF($J$139&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N139" s="19" t="inlineStr">
+        <is>
+          <t>Model 46.7% (fair +114). Your call.</t>
+        </is>
+      </c>
+      <c r="O139" s="15" t="n"/>
+      <c r="P139" s="16">
+        <f>IF(OR($H$139="",$O$139=""),"",(1+IF($H$139&lt;0,-100/$H$139,$H$139/100))/(1+IF($O$139&lt;0,-100/$O$139,$O$139/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B140" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C140" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D140" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E140" s="20" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="F140" s="13" t="n">
+        <v>0.5331</v>
+      </c>
+      <c r="G140" s="14" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H140" s="15" t="n"/>
+      <c r="I140" s="13">
+        <f>IF($H$140="","",IF($H$140&lt;0,-$H$140/(-$H$140+100),100/($H$140+100)))</f>
+        <v/>
+      </c>
+      <c r="J140" s="16">
+        <f>IF($H$140="","",$F$140*IF($H$140&lt;0,-100/$H$140,$H$140/100)-(1-$F$140))</f>
+        <v/>
+      </c>
+      <c r="K140" s="17">
+        <f>IF($H$140="","",MAX(0,($F$140*IF($H$140&lt;0,-100/$H$140,$H$140/100)-(1-$F$140))/IF($H$140&lt;0,-100/$H$140,$H$140/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L140" s="18">
+        <f>IF($H$140="","",ROUND(MIN($K$140,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M140" s="12">
+        <f>IF($J$140="","",IF($J$140&lt;0,"Pass",IF($J$140&lt;'Settings'!$B$4,"Thin",IF($J$140&lt;0.06,"✅ Sharp band",IF($J$140&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N140" s="19" t="inlineStr">
+        <is>
+          <t>Model 53.3% (fair -114). Your call.</t>
+        </is>
+      </c>
+      <c r="O140" s="15" t="n"/>
+      <c r="P140" s="16">
+        <f>IF(OR($H$140="",$O$140=""),"",(1+IF($H$140&lt;0,-100/$H$140,$H$140/100))/(1+IF($O$140&lt;0,-100/$O$140,$O$140/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>Over 8</t>
+        </is>
+      </c>
+      <c r="F141" s="13" t="n">
+        <v>0.5116000000000001</v>
+      </c>
+      <c r="G141" s="14" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H141" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I141" s="13">
+        <f>IF($H$141="","",IF($H$141&lt;0,-$H$141/(-$H$141+100),100/($H$141+100)))</f>
+        <v/>
+      </c>
+      <c r="J141" s="16">
+        <f>IF($H$141="","",$F$141*IF($H$141&lt;0,-100/$H$141,$H$141/100)-(1-$F$141))</f>
+        <v/>
+      </c>
+      <c r="K141" s="17">
+        <f>IF($H$141="","",MAX(0,($F$141*IF($H$141&lt;0,-100/$H$141,$H$141/100)-(1-$F$141))/IF($H$141&lt;0,-100/$H$141,$H$141/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L141" s="18">
+        <f>IF($H$141="","",ROUND(MIN($K$141,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M141" s="12">
+        <f>IF($J$141="","",IF($J$141&lt;0,"Pass",IF($J$141&lt;'Settings'!$B$4,"Thin",IF($J$141&lt;0.06,"✅ Sharp band",IF($J$141&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N141" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.2% (fair -105). Your call.</t>
+        </is>
+      </c>
+      <c r="O141" s="15" t="n"/>
+      <c r="P141" s="16">
+        <f>IF(OR($H$141="",$O$141=""),"",(1+IF($H$141&lt;0,-100/$H$141,$H$141/100))/(1+IF($O$141&lt;0,-100/$O$141,$O$141/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B142" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C142" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D142" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E142" s="20" t="inlineStr">
+        <is>
+          <t>Under 8</t>
+        </is>
+      </c>
+      <c r="F142" s="13" t="n">
+        <v>0.4883780487804879</v>
+      </c>
+      <c r="G142" s="14" t="n">
+        <v>105</v>
+      </c>
+      <c r="H142" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I142" s="13">
+        <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
+        <v/>
+      </c>
+      <c r="J142" s="16">
+        <f>IF($H$142="","",$F$142*IF($H$142&lt;0,-100/$H$142,$H$142/100)-(1-$F$142))</f>
+        <v/>
+      </c>
+      <c r="K142" s="17">
+        <f>IF($H$142="","",MAX(0,($F$142*IF($H$142&lt;0,-100/$H$142,$H$142/100)-(1-$F$142))/IF($H$142&lt;0,-100/$H$142,$H$142/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L142" s="18">
+        <f>IF($H$142="","",ROUND(MIN($K$142,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M142" s="12">
+        <f>IF($J$142="","",IF($J$142&lt;0,"Pass",IF($J$142&lt;'Settings'!$B$4,"Thin",IF($J$142&lt;0.06,"✅ Sharp band",IF($J$142&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N142" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.8% (fair +105). Your call.</t>
+        </is>
+      </c>
+      <c r="O142" s="15" t="n"/>
+      <c r="P142" s="16">
+        <f>IF(OR($H$142="",$O$142=""),"",(1+IF($H$142&lt;0,-100/$H$142,$H$142/100))/(1+IF($O$142&lt;0,-100/$O$142,$O$142/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>Texas Rangers -1.5</t>
+        </is>
+      </c>
+      <c r="F143" s="13" t="n">
+        <v>0.3926984126984127</v>
+      </c>
+      <c r="G143" s="14" t="n">
+        <v>155</v>
+      </c>
+      <c r="H143" s="15" t="n">
+        <v>152</v>
+      </c>
+      <c r="I143" s="13">
+        <f>IF($H$143="","",IF($H$143&lt;0,-$H$143/(-$H$143+100),100/($H$143+100)))</f>
+        <v/>
+      </c>
+      <c r="J143" s="16">
+        <f>IF($H$143="","",$F$143*IF($H$143&lt;0,-100/$H$143,$H$143/100)-(1-$F$143))</f>
+        <v/>
+      </c>
+      <c r="K143" s="17">
+        <f>IF($H$143="","",MAX(0,($F$143*IF($H$143&lt;0,-100/$H$143,$H$143/100)-(1-$F$143))/IF($H$143&lt;0,-100/$H$143,$H$143/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L143" s="18">
+        <f>IF($H$143="","",ROUND(MIN($K$143,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M143" s="12">
+        <f>IF($J$143="","",IF($J$143&lt;0,"Pass",IF($J$143&lt;'Settings'!$B$4,"Thin",IF($J$143&lt;0.06,"✅ Sharp band",IF($J$143&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N143" s="19" t="inlineStr">
+        <is>
+          <t>Model 39.3% (fair +155). Your call.</t>
+        </is>
+      </c>
+      <c r="O143" s="15" t="n"/>
+      <c r="P143" s="16">
+        <f>IF(OR($H$143="",$O$143=""),"",(1+IF($H$143&lt;0,-100/$H$143,$H$143/100))/(1+IF($O$143&lt;0,-100/$O$143,$O$143/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B144" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C144" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D144" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E144" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels +1.5</t>
+        </is>
+      </c>
+      <c r="F144" s="13" t="n">
+        <v>0.6072622641509434</v>
+      </c>
+      <c r="G144" s="14" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H144" s="15" t="n">
+        <v>-165</v>
+      </c>
+      <c r="I144" s="13">
+        <f>IF($H$144="","",IF($H$144&lt;0,-$H$144/(-$H$144+100),100/($H$144+100)))</f>
+        <v/>
+      </c>
+      <c r="J144" s="16">
+        <f>IF($H$144="","",$F$144*IF($H$144&lt;0,-100/$H$144,$H$144/100)-(1-$F$144))</f>
+        <v/>
+      </c>
+      <c r="K144" s="17">
+        <f>IF($H$144="","",MAX(0,($F$144*IF($H$144&lt;0,-100/$H$144,$H$144/100)-(1-$F$144))/IF($H$144&lt;0,-100/$H$144,$H$144/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L144" s="18">
+        <f>IF($H$144="","",ROUND(MIN($K$144,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M144" s="12">
+        <f>IF($J$144="","",IF($J$144&lt;0,"Pass",IF($J$144&lt;'Settings'!$B$4,"Thin",IF($J$144&lt;0.06,"✅ Sharp band",IF($J$144&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N144" s="19" t="inlineStr">
+        <is>
+          <t>Model 60.7% (fair -155). Your call.</t>
+        </is>
+      </c>
+      <c r="O144" s="15" t="n"/>
+      <c r="P144" s="16">
+        <f>IF(OR($H$144="",$O$144=""),"",(1+IF($H$144&lt;0,-100/$H$144,$H$144/100))/(1+IF($O$144&lt;0,-100/$O$144,$O$144/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="F145" s="13" t="n">
+        <v>0.4976</v>
+      </c>
+      <c r="G145" s="14" t="n">
+        <v>101</v>
+      </c>
+      <c r="H145" s="15" t="n"/>
+      <c r="I145" s="13">
+        <f>IF($H$145="","",IF($H$145&lt;0,-$H$145/(-$H$145+100),100/($H$145+100)))</f>
+        <v/>
+      </c>
+      <c r="J145" s="16">
+        <f>IF($H$145="","",$F$145*IF($H$145&lt;0,-100/$H$145,$H$145/100)-(1-$F$145))</f>
+        <v/>
+      </c>
+      <c r="K145" s="17">
+        <f>IF($H$145="","",MAX(0,($F$145*IF($H$145&lt;0,-100/$H$145,$H$145/100)-(1-$F$145))/IF($H$145&lt;0,-100/$H$145,$H$145/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L145" s="18">
+        <f>IF($H$145="","",ROUND(MIN($K$145,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M145" s="12">
+        <f>IF($J$145="","",IF($J$145&lt;0,"Pass",IF($J$145&lt;'Settings'!$B$4,"Thin",IF($J$145&lt;0.06,"✅ Sharp band",IF($J$145&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N145" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.8% (fair +101). Your call.</t>
+        </is>
+      </c>
+      <c r="O145" s="15" t="n"/>
+      <c r="P145" s="16">
+        <f>IF(OR($H$145="",$O$145=""),"",(1+IF($H$145&lt;0,-100/$H$145,$H$145/100))/(1+IF($O$145&lt;0,-100/$O$145,$O$145/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B146" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C146" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D146" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E146" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="F146" s="13" t="n">
+        <v>0.5024</v>
+      </c>
+      <c r="G146" s="14" t="n">
+        <v>-101</v>
+      </c>
+      <c r="H146" s="15" t="n"/>
+      <c r="I146" s="13">
+        <f>IF($H$146="","",IF($H$146&lt;0,-$H$146/(-$H$146+100),100/($H$146+100)))</f>
+        <v/>
+      </c>
+      <c r="J146" s="16">
+        <f>IF($H$146="","",$F$146*IF($H$146&lt;0,-100/$H$146,$H$146/100)-(1-$F$146))</f>
+        <v/>
+      </c>
+      <c r="K146" s="17">
+        <f>IF($H$146="","",MAX(0,($F$146*IF($H$146&lt;0,-100/$H$146,$H$146/100)-(1-$F$146))/IF($H$146&lt;0,-100/$H$146,$H$146/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L146" s="18">
+        <f>IF($H$146="","",ROUND(MIN($K$146,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M146" s="12">
+        <f>IF($J$146="","",IF($J$146&lt;0,"Pass",IF($J$146&lt;'Settings'!$B$4,"Thin",IF($J$146&lt;0.06,"✅ Sharp band",IF($J$146&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N146" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.2% (fair -101). Your call.</t>
+        </is>
+      </c>
+      <c r="O146" s="15" t="n"/>
+      <c r="P146" s="16">
+        <f>IF(OR($H$146="",$O$146=""),"",(1+IF($H$146&lt;0,-100/$H$146,$H$146/100))/(1+IF($O$146&lt;0,-100/$O$146,$O$146/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="F147" s="13" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="G147" s="14" t="n">
+        <v>133</v>
+      </c>
+      <c r="H147" s="15" t="n"/>
+      <c r="I147" s="13">
+        <f>IF($H$147="","",IF($H$147&lt;0,-$H$147/(-$H$147+100),100/($H$147+100)))</f>
+        <v/>
+      </c>
+      <c r="J147" s="16">
+        <f>IF($H$147="","",$F$147*IF($H$147&lt;0,-100/$H$147,$H$147/100)-(1-$F$147))</f>
+        <v/>
+      </c>
+      <c r="K147" s="17">
+        <f>IF($H$147="","",MAX(0,($F$147*IF($H$147&lt;0,-100/$H$147,$H$147/100)-(1-$F$147))/IF($H$147&lt;0,-100/$H$147,$H$147/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L147" s="18">
+        <f>IF($H$147="","",ROUND(MIN($K$147,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M147" s="12">
+        <f>IF($J$147="","",IF($J$147&lt;0,"Pass",IF($J$147&lt;'Settings'!$B$4,"Thin",IF($J$147&lt;0.06,"✅ Sharp band",IF($J$147&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N147" s="19" t="inlineStr">
+        <is>
+          <t>Model 42.9% (fair +133). Your call.</t>
+        </is>
+      </c>
+      <c r="O147" s="15" t="n"/>
+      <c r="P147" s="16">
+        <f>IF(OR($H$147="",$O$147=""),"",(1+IF($H$147&lt;0,-100/$H$147,$H$147/100))/(1+IF($O$147&lt;0,-100/$O$147,$O$147/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B148" s="20" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C148" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D148" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E148" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="F148" s="13" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="G148" s="14" t="n">
+        <v>-133</v>
+      </c>
+      <c r="H148" s="15" t="n"/>
+      <c r="I148" s="13">
+        <f>IF($H$148="","",IF($H$148&lt;0,-$H$148/(-$H$148+100),100/($H$148+100)))</f>
+        <v/>
+      </c>
+      <c r="J148" s="16">
+        <f>IF($H$148="","",$F$148*IF($H$148&lt;0,-100/$H$148,$H$148/100)-(1-$F$148))</f>
+        <v/>
+      </c>
+      <c r="K148" s="17">
+        <f>IF($H$148="","",MAX(0,($F$148*IF($H$148&lt;0,-100/$H$148,$H$148/100)-(1-$F$148))/IF($H$148&lt;0,-100/$H$148,$H$148/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L148" s="18">
+        <f>IF($H$148="","",ROUND(MIN($K$148,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M148" s="12">
+        <f>IF($J$148="","",IF($J$148&lt;0,"Pass",IF($J$148&lt;'Settings'!$B$4,"Thin",IF($J$148&lt;0.06,"✅ Sharp band",IF($J$148&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N148" s="19" t="inlineStr">
+        <is>
+          <t>Model 57.1% (fair -133). Your call.</t>
+        </is>
+      </c>
+      <c r="O148" s="15" t="n"/>
+      <c r="P148" s="16">
+        <f>IF(OR($H$148="",$O$148=""),"",(1+IF($H$148&lt;0,-100/$H$148,$H$148/100))/(1+IF($O$148&lt;0,-100/$O$148,$O$148/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J108">
+  <conditionalFormatting sqref="J5:J148">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -19644,7 +22284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19661,321 +22301,167 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="28" t="inlineStr">
         <is>
           <t>Milwaukee Brewers offense vs St. Louis Cardinals defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B71" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C71" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D71" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E71" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F71" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G71" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H71" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I71" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="29" t="inlineStr">
+      <c r="J71" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K71" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L71" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr">
+      <c r="M71" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="29" t="inlineStr">
+      <c r="N71" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O71" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="29" t="inlineStr">
+      <c r="P71" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="29" t="inlineStr">
+      <c r="Q71" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>5.367</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H70" s="32" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>4.474</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B71" s="31" t="n">
-        <v>7.935</v>
-      </c>
-      <c r="C71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="P71" s="31" t="n">
-        <v>8.651999999999999</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="C72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5</v>
+      </c>
+      <c r="C72" s="31" t="n">
+        <v>5.367</v>
+      </c>
+      <c r="D72" s="31" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E72" s="31" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F72" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G72" s="31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H72" s="32" t="inlineStr">
+        <is>
+          <t>24th</t>
         </is>
       </c>
       <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J72" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L72" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M72" s="31" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="N72" s="31" t="n">
+        <v>4.6</v>
       </c>
       <c r="O72" s="31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>1.043</v>
+        <v>4.474</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.151999999999999</v>
+        <v>7.935</v>
       </c>
       <c r="C73" s="31" t="inlineStr">
         <is>
@@ -20034,398 +22520,398 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>7.739</v>
+        <v>8.651999999999999</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="C74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="n">
+        <v>8.151999999999999</v>
+      </c>
+      <c r="C75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="P75" s="31" t="n">
+        <v>7.739</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B76" s="31" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C76" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D76" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E76" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F76" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G76" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="32" t="inlineStr">
+      <c r="H76" s="32" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="32" t="inlineStr">
+      <c r="I76" s="31" t="inlineStr"/>
+      <c r="J76" s="32" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K76" s="31" t="n">
         <v>1.4</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L76" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M76" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N76" s="31" t="n">
         <v>0.65</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O76" s="31" t="n">
         <v>0.667</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P76" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q76" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr">
         <is>
           <t>St. Louis Cardinals offense vs Milwaukee Brewers defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B79" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C79" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D79" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E79" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="29" t="inlineStr">
+      <c r="F79" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="29" t="inlineStr">
+      <c r="G79" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H79" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="29" t="inlineStr">
+      <c r="I79" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="29" t="inlineStr">
+      <c r="J79" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="29" t="inlineStr">
+      <c r="K79" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="29" t="inlineStr">
+      <c r="L79" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="29" t="inlineStr">
+      <c r="M79" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="29" t="inlineStr">
+      <c r="N79" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="29" t="inlineStr">
+      <c r="O79" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="29" t="inlineStr">
+      <c r="P79" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="29" t="inlineStr">
+      <c r="Q79" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>5.267</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>3.785</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B79" s="31" t="n">
-        <v>7.826</v>
-      </c>
-      <c r="C79" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P79" s="31" t="n">
-        <v>7.174</v>
-      </c>
-      <c r="Q79" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>1.109</v>
+        <v>4.59</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="31" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.267</v>
+      </c>
+      <c r="D80" s="31" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="E80" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F80" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G80" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H80" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I80" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J80" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K80" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L80" s="31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M80" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N80" s="31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O80" s="31" t="n">
+        <v>4.167</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>0.761</v>
+        <v>3.785</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>8.196</v>
+        <v>7.826</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -20484,72 +22970,226 @@
         </is>
       </c>
       <c r="P81" s="31" t="n">
-        <v>9.630000000000001</v>
+        <v>7.174</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B83" s="31" t="n">
+        <v>8.196</v>
+      </c>
+      <c r="C83" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P83" s="31" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="Q83" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="31" t="n">
+      <c r="B84" s="31" t="n">
         <v>0.547</v>
       </c>
-      <c r="C82" s="31" t="n">
+      <c r="C84" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="D82" s="31" t="n">
+      <c r="D84" s="31" t="n">
         <v>0.65</v>
       </c>
-      <c r="E82" s="31" t="n">
+      <c r="E84" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="F82" s="31" t="n">
+      <c r="F84" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G82" s="31" t="n">
+      <c r="G84" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="H82" s="35" t="inlineStr">
+      <c r="H84" s="35" t="inlineStr">
         <is>
           <t>15th</t>
         </is>
       </c>
-      <c r="I82" s="31" t="inlineStr">
+      <c r="I84" s="31" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="J82" s="32" t="inlineStr">
+      <c r="J84" s="32" t="inlineStr">
         <is>
           <t>24th</t>
         </is>
       </c>
-      <c r="K82" s="31" t="n">
+      <c r="K84" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="L82" s="31" t="n">
+      <c r="L84" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="M82" s="31" t="n">
+      <c r="M84" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="N82" s="31" t="n">
+      <c r="N84" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="O82" s="31" t="n">
+      <c r="O84" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="P82" s="31" t="n">
+      <c r="P84" s="31" t="n">
         <v>0.442</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q84" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-07.xlsx
+++ b/data/output/workbook/2026-07-07.xlsx
@@ -490,7 +490,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10887075"/>
+    <ext cx="10125075" cy="10715625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -580,7 +580,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="11144250"/>
+    <ext cx="10125075" cy="10715625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07 15:09</t>
+          <t>2026-07-07 16:07</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3022,174 +3022,251 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>Atlanta Braves offense vs Pittsburgh Pirates defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>Atlanta Braves offense vs Pittsburgh Pirates defense</t>
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>4.987</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>4.771</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4.987</v>
+        <v>8.958</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="O71" s="31" t="n">
-        <v>5.533</v>
+        <v>6.5</v>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="31" t="n">
-        <v>4.771</v>
+        <v>7.792</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>8.958</v>
+        <v>1.333</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -3248,25 +3325,25 @@
         </is>
       </c>
       <c r="P72" s="31" t="n">
-        <v>7.792</v>
+        <v>0.896</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>1.333</v>
+        <v>7.688</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -3325,319 +3402,319 @@
         </is>
       </c>
       <c r="P73" s="31" t="n">
-        <v>0.896</v>
+        <v>9.292</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>7.688</v>
+        <v>0.605</v>
       </c>
       <c r="C74" s="31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F74" s="31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L74" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M74" s="31" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates offense vs Atlanta Braves defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>5.157</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="D78" s="31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E78" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F78" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G78" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>9.292</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates offense vs Atlanta Braves defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I78" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J78" s="32" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L78" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M78" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="N78" s="31" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="O78" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P78" s="31" t="n">
+        <v>3.923</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>5.157</v>
-      </c>
-      <c r="C79" s="31" t="n">
-        <v>5.467</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J79" s="32" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>4.95</v>
+        <v>8.811999999999999</v>
+      </c>
+      <c r="C79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>4.7</v>
+        <v>9.5</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>3.923</v>
+        <v>7.312</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.811999999999999</v>
+        <v>1.188</v>
       </c>
       <c r="C80" s="31" t="inlineStr">
         <is>
@@ -3696,25 +3773,25 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>9.5</v>
+        <v>1</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>7.312</v>
+        <v>1.062</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>1.188</v>
+        <v>9.708</v>
       </c>
       <c r="C81" s="31" t="inlineStr">
         <is>
@@ -3773,148 +3850,71 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>1.062</v>
+        <v>8.561999999999999</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>9.708</v>
-      </c>
-      <c r="C82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.538</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D82" s="31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E82" s="31" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F82" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G82" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H82" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L82" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M82" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N82" s="31" t="n">
+        <v>0.6</v>
       </c>
       <c r="O82" s="31" t="n">
-        <v>11</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>8.561999999999999</v>
+        <v>0.553</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F83" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G83" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H83" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5769,7 +5769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5786,911 +5786,911 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>Houston Astros offense vs Washington Nationals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>4.914</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="32" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>5.268</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
     <row r="71">
-      <c r="A71" s="28" t="inlineStr">
-        <is>
-          <t>Houston Astros offense vs Washington Nationals defense</t>
+      <c r="A71" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B71" s="31" t="n">
+        <v>8.083</v>
+      </c>
+      <c r="C71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="31" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B72" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C72" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D72" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E72" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F72" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G72" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H72" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I72" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J72" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K72" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L72" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M72" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N72" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O72" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P72" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q72" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A72" s="30" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B72" s="31" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="C72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr"/>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q72" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>4.914</v>
-      </c>
-      <c r="C73" s="31" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="D73" s="31" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="E73" s="31" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="F73" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G73" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J73" s="32" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L73" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M73" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N73" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O73" s="31" t="n">
-        <v>5</v>
+        <v>7.729</v>
+      </c>
+      <c r="C73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P73" s="31" t="n">
-        <v>5.268</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F74" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L74" s="31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M74" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>Washington Nationals offense vs Houston Astros defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>5.354</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>5.567</v>
+      </c>
+      <c r="D78" s="31" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E78" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F78" s="31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G78" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I78" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J78" s="32" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L78" s="31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M78" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N78" s="31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O78" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="P78" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="30" t="inlineStr">
+        <is>
           <t>Hits/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
-        <v>8.083</v>
-      </c>
-      <c r="C74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="B79" s="31" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="C79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P79" s="31" t="n">
+        <v>7.625</v>
+      </c>
+      <c r="Q79" s="34" t="inlineStr">
         <is>
           <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="30" t="inlineStr">
         <is>
           <t>HR/G</t>
         </is>
       </c>
-      <c r="B75" s="31" t="n">
-        <v>1.417</v>
-      </c>
-      <c r="C75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
+      <c r="B80" s="31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="31" t="inlineStr"/>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="31" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="Q80" s="34" t="inlineStr">
         <is>
           <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B76" s="31" t="n">
-        <v>7.729</v>
-      </c>
-      <c r="C76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="31" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P76" s="31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q76" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O77" s="31" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P77" s="31" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="28" t="inlineStr">
-        <is>
-          <t>Washington Nationals offense vs Houston Astros defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B80" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C80" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D80" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E80" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F80" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G80" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H80" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I80" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J80" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K80" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L80" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M80" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N80" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O80" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P80" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q80" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>5.354</v>
-      </c>
-      <c r="C81" s="31" t="n">
-        <v>5.567</v>
-      </c>
-      <c r="D81" s="31" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E81" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F81" s="31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="G81" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H81" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J81" s="32" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L81" s="31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M81" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N81" s="31" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="O81" s="31" t="n">
-        <v>4.867</v>
+        <v>7.98</v>
+      </c>
+      <c r="C81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P81" s="31" t="n">
-        <v>5</v>
+        <v>8.417</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="C82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.825</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="D82" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E82" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F82" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G82" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L82" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M82" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N82" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>0.667</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>7.625</v>
+        <v>0.646</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="C83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>1.292</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B84" s="31" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="C84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H84" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I84" s="31" t="inlineStr"/>
-      <c r="J84" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P84" s="31" t="n">
-        <v>8.417</v>
-      </c>
-      <c r="Q84" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B85" s="31" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="C85" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="D85" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E85" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F85" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G85" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I85" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J85" s="35" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="K85" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L85" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M85" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N85" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O85" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P85" s="31" t="n">
-        <v>0.646</v>
-      </c>
-      <c r="Q85" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6628671328671327</v>
+        <v>0.6862937062937062</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-197</v>
+        <v>-219</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>186</v>
@@ -8821,7 +8821,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 66.3% (fair -197). Your call.</t>
+          <t>Model 68.6% (fair -219). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8923,13 +8923,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6310661764705883</v>
+        <v>0.6328623188405799</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 63.3% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9055,10 +9055,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5682462686567165</v>
+        <v>0.5720149253731344</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-132</v>
+        <v>-134</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>168</v>
@@ -9085,7 +9085,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -132). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5571111111111111</v>
+        <v>0.5546666666666666</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-126</v>
+        <v>-125</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>170</v>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9187,10 +9187,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5212592592592592</v>
+        <v>0.5148888888888888</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-109</v>
+        <v>-106</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>170</v>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9319,10 +9319,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4787407407407407</v>
+        <v>0.4851111111111111</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>170</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9381,17 +9381,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies -1.5</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5541921397379912</v>
+        <v>0.4453454545454545</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-124</v>
+        <v>125</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9513,17 +9513,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4429090909090909</v>
+        <v>0.6135291866028708</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>126</v>
+        <v>-159</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>175</v>
+        <v>-109</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 61.4% (fair -159). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9564,32 +9564,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.6147808612440192</v>
+        <v>0.5983096153846152</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-160</v>
+        <v>-149</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -160). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4317358490566037</v>
+        <v>0.428</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>165</v>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +132). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9691,37 +9691,37 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5865639810426539</v>
+        <v>0.4123880597014926</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-142</v>
+        <v>142</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-111</v>
+        <v>168</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9745,7 +9745,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 41.2% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9762,32 +9762,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Atlanta Braves +1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.6745078740157481</v>
+        <v>0.5678753623188406</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-207</v>
+        <v>-131</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-154</v>
+        <v>-107</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 67.5% (fair -207). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9823,37 +9823,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4123880597014926</v>
+        <v>0.3684121621621622</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +142). Your call.</t>
+          <t>Model 36.8% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9955,17 +9955,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.3687074829931973</v>
+        <v>0.5707826291079813</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>171</v>
+        <v>-133</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>194</v>
+        <v>-113</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10041,17 +10041,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves +1.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.560328502415459</v>
+        <v>0.4321544715447154</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-127</v>
+        <v>131</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-107</v>
+        <v>146</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10087,12 +10087,12 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -10102,22 +10102,22 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4396341463414634</v>
+        <v>0.5433365853658536</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>127</v>
+        <v>-119</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>146</v>
+        <v>-105</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10153,17 +10153,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -10173,17 +10173,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5707826291079813</v>
+        <v>0.4793212669683258</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-133</v>
+        <v>109</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-113</v>
+        <v>121</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10224,32 +10224,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5433365853658536</v>
+        <v>0.5134803921568628</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-119</v>
+        <v>-106</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-105</v>
+        <v>104</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 51.3% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10290,32 +10290,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.52615</v>
+        <v>0.3965530303030304</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-111</v>
+        <v>152</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 39.7% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10351,37 +10351,37 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5134803921568628</v>
+        <v>0.5535408450704226</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-106</v>
+        <v>-124</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>104</v>
+        <v>-113</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -106). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11374,13 +11374,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4932862745098039</v>
+        <v>0.4898334975369458</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5067156862745098</v>
+        <v>0.5101470588235294</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>104</v>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11506,10 +11506,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4732</v>
+        <v>0.4728</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>113</v>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11572,13 +11572,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5267999999999999</v>
+        <v>0.5272</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11638,13 +11638,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.3687074829931973</v>
+        <v>0.3684121621621622</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>171</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 36.8% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11704,13 +11704,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6312918367346939</v>
+        <v>0.6315421404682274</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>-171</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-194</v>
+        <v>-199</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 63.2% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11770,13 +11770,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6122</v>
+        <v>0.617</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-158</v>
+        <v>-161</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11800,7 +11800,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11836,10 +11836,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.3878</v>
+        <v>0.383</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>105</v>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11902,13 +11902,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4509047619047619</v>
+        <v>0.4464150943396226</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11968,10 +11968,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5490845070422534</v>
+        <v>0.5535408450704226</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-122</v>
+        <v>-124</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>-113</v>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12034,13 +12034,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4057872340425532</v>
+        <v>0.4241452991452992</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12100,13 +12100,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5942117647058823</v>
+        <v>0.5758468085106383</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-146</v>
+        <v>-136</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-138</v>
+        <v>-135</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12166,13 +12166,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5373</v>
+        <v>0.5583</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-116</v>
+        <v>-126</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12232,13 +12232,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4627</v>
+        <v>0.4417</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4396341463414634</v>
+        <v>0.4321544715447154</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>146</v>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12364,10 +12364,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.560328502415459</v>
+        <v>0.5678753623188406</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-127</v>
+        <v>-131</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>-107</v>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12430,13 +12430,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4583870967741936</v>
+        <v>0.4606542056074767</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12496,10 +12496,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5415967741935483</v>
+        <v>0.5393322580645161</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-118</v>
+        <v>-117</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>-117</v>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12558,17 +12558,17 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.5051780487804878</v>
+        <v>0.4787</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-102</v>
+        <v>109</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-105</v>
+        <v>122</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12592,7 +12592,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12624,14 +12624,14 @@
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.4948341232227488</v>
+        <v>0.5213</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>102</v>
+        <v>-109</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>111</v>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12826,13 +12826,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4723943661971831</v>
+        <v>0.4793212669683258</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12892,13 +12892,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5275985915492958</v>
+        <v>0.5206769585253456</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-112</v>
+        <v>-109</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-113</v>
+        <v>-117</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12958,10 +12958,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5077</v>
+        <v>0.5322</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-103</v>
+        <v>-114</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>127</v>
@@ -12988,7 +12988,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13024,13 +13024,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4923</v>
+        <v>0.4678</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13090,13 +13090,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.3371328671328671</v>
+        <v>0.313705035971223</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 33.7% (fair +197). Your call.</t>
+          <t>Model 31.4% (fair +219). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13156,10 +13156,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.6628671328671327</v>
+        <v>0.6862937062937062</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-197</v>
+        <v>-219</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>186</v>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 66.3% (fair -197). Your call.</t>
+          <t>Model 68.6% (fair -219). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13222,13 +13222,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4134123222748814</v>
+        <v>0.4016666666666667</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13288,13 +13288,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5865639810426539</v>
+        <v>0.5983096153846152</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-142</v>
+        <v>-149</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13350,17 +13350,17 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4703</v>
+        <v>0.5100980392156863</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>113</v>
+        <v>-104</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13384,7 +13384,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13416,14 +13416,14 @@
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5297000000000001</v>
+        <v>0.4899</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-113</v>
+        <v>104</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>100</v>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13486,10 +13486,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4787407407407407</v>
+        <v>0.4851111111111111</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>170</v>
@@ -13516,7 +13516,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13552,10 +13552,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5212592592592592</v>
+        <v>0.5148888888888888</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-109</v>
+        <v>-106</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>170</v>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.426</v>
+        <v>0.4267659574468085</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>135</v>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 42.7% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13684,10 +13684,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5739756302521009</v>
+        <v>0.5732218487394958</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-135</v>
+        <v>-134</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>-138</v>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13746,17 +13746,17 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.5037</v>
+        <v>0.3904</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>-101</v>
+        <v>156</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -101). Your call.</t>
+          <t>Model 39.0% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13812,17 +13812,17 @@
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.4963</v>
+        <v>0.6095999999999999</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>101</v>
+        <v>-156</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>113</v>
+        <v>-104</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +101). Your call.</t>
+          <t>Model 61.0% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13882,10 +13882,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.3852</v>
+        <v>0.38644</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>150</v>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 38.5% (fair +160). Your call.</t>
+          <t>Model 38.6% (fair +159). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13948,10 +13948,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.6147808612440192</v>
+        <v>0.6135291866028708</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-160</v>
+        <v>-159</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>-109</v>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -160). Your call.</t>
+          <t>Model 61.4% (fair -159). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14014,10 +14014,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.6745078740157481</v>
+        <v>0.628671653543307</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>-207</v>
+        <v>-169</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>-154</v>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 67.5% (fair -207). Your call.</t>
+          <t>Model 62.9% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14080,10 +14080,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.32546875</v>
+        <v>0.3713671875</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>156</v>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 32.5% (fair +207). Your call.</t>
+          <t>Model 37.1% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14146,10 +14146,10 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5393</v>
+        <v>0.5079</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-117</v>
+        <v>-103</v>
       </c>
       <c r="H59" s="15" t="n">
         <v>127</v>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14212,10 +14212,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4607</v>
+        <v>0.4921</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="H60" s="15" t="n">
         <v>120</v>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14278,10 +14278,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4458235294117647</v>
+        <v>0.4941529411764706</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>-104</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5541921397379912</v>
+        <v>0.5058415841584158</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-124</v>
+        <v>-102</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14542,10 +14542,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4031</v>
+        <v>0.4342</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="H65" s="15" t="n">
         <v>117</v>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 40.3% (fair +148). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14608,10 +14608,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5969</v>
+        <v>0.5658000000000001</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-148</v>
+        <v>-130</v>
       </c>
       <c r="H66" s="15" t="n">
         <v>104</v>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14674,10 +14674,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.4429090909090909</v>
+        <v>0.4453454545454545</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H67" s="15" t="n">
         <v>175</v>
@@ -14704,7 +14704,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14740,10 +14740,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5571111111111111</v>
+        <v>0.5546666666666666</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-126</v>
+        <v>-125</v>
       </c>
       <c r="H68" s="15" t="n">
         <v>170</v>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14806,10 +14806,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4942</v>
+        <v>0.5085</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>102</v>
+        <v>-103</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5058</v>
+        <v>0.4915</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-102</v>
+        <v>103</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 49.1% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14934,10 +14934,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4778</v>
+        <v>0.4713</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14998,10 +14998,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5222</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-109</v>
+        <v>-112</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15318,10 +15318,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.381</v>
+        <v>0.3789</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H77" s="15" t="n"/>
       <c r="I77" s="13">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15382,10 +15382,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.619</v>
+        <v>0.6211</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-162</v>
+        <v>-164</v>
       </c>
       <c r="H78" s="15" t="n"/>
       <c r="I78" s="13">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Over 7</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
@@ -15584,7 +15584,7 @@
         <v>116</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15640,7 +15640,7 @@
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Under 7</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
@@ -15650,7 +15650,7 @@
         <v>-116</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15710,7 +15710,7 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.6359456140350878</v>
+        <v>0.6365298245614035</v>
       </c>
       <c r="G83" s="14" t="n">
         <v>-175</v>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 63.6% (fair -175). Your call.</t>
+          <t>Model 63.7% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.3640530303030303</v>
+        <v>0.3634716981132076</v>
       </c>
       <c r="G84" s="14" t="n">
         <v>175</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 36.4% (fair +175). Your call.</t>
+          <t>Model 36.3% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -16106,13 +16106,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.6188087719298245</v>
+        <v>0.6155357142857143</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-162</v>
+        <v>-160</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-185</v>
+        <v>-180</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 61.6% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16172,13 +16172,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.3811627906976744</v>
+        <v>0.3844313725490196</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 38.4% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16502,13 +16502,13 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4314583333333334</v>
+        <v>0.4328151260504202</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16568,10 +16568,10 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5685183673469387</v>
+        <v>0.5672163265306123</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-132</v>
+        <v>-131</v>
       </c>
       <c r="H96" s="15" t="n">
         <v>-145</v>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16766,10 +16766,10 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.5213121951219513</v>
+        <v>0.5068170731707318</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-109</v>
+        <v>-103</v>
       </c>
       <c r="H99" s="15" t="n">
         <v>-105</v>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16832,10 +16832,10 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.4786829268292683</v>
+        <v>0.4931707317073171</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H100" s="15" t="n">
         <v>105</v>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16898,10 +16898,10 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4317358490566037</v>
+        <v>0.428</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H101" s="15" t="n">
         <v>165</v>
@@ -16928,7 +16928,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +132). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -16964,10 +16964,10 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5682462686567165</v>
+        <v>0.5720149253731344</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-132</v>
+        <v>-134</v>
       </c>
       <c r="H102" s="15" t="n">
         <v>168</v>
@@ -16994,7 +16994,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -132). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17030,10 +17030,10 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.47385</v>
+        <v>0.4897</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H103" s="15" t="n">
         <v>100</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17096,10 +17096,10 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.52615</v>
+        <v>0.5103</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-111</v>
+        <v>-104</v>
       </c>
       <c r="H104" s="15" t="n">
         <v>100</v>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17162,10 +17162,10 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4557603686635945</v>
+        <v>0.4554377880184332</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H105" s="15" t="n">
         <v>117</v>
@@ -17192,7 +17192,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17228,10 +17228,10 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5442545454545454</v>
+        <v>0.5445818181818182</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-119</v>
+        <v>-120</v>
       </c>
       <c r="H106" s="15" t="n">
         <v>-120</v>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17294,10 +17294,10 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.5294048780487806</v>
+        <v>0.5092243902439024</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-112</v>
+        <v>-104</v>
       </c>
       <c r="H107" s="15" t="n">
         <v>-105</v>
@@ -17324,7 +17324,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17360,13 +17360,13 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4907882352941176</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -17390,7 +17390,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17426,10 +17426,10 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.3689615384615385</v>
+        <v>0.3671538461538462</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H109" s="15" t="n">
         <v>160</v>
@@ -17456,7 +17456,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 36.7% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17492,13 +17492,13 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.6310661764705883</v>
+        <v>0.6328623188405799</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -17522,7 +17522,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 63.3% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17690,10 +17690,10 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.5615</v>
+        <v>0.5317</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>-128</v>
+        <v>-114</v>
       </c>
       <c r="H113" s="15" t="n">
         <v>117</v>
@@ -17720,7 +17720,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17756,10 +17756,10 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.4385</v>
+        <v>0.4683</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H114" s="15" t="n">
         <v>110</v>
@@ -17786,7 +17786,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17822,13 +17822,13 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.403968253968254</v>
+        <v>0.4063008130081301</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +148). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17888,10 +17888,10 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5959924528301888</v>
+        <v>0.593688679245283</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-148</v>
+        <v>-146</v>
       </c>
       <c r="H116" s="15" t="n">
         <v>-165</v>
@@ -17918,7 +17918,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -148). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -17954,13 +17954,13 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.430704845814978</v>
+        <v>0.4265665236051502</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 42.7% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18020,10 +18020,10 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.5692742489270386</v>
+        <v>0.5734412017167382</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>-132</v>
+        <v>-134</v>
       </c>
       <c r="H118" s="15" t="n">
         <v>-133</v>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18742,10 +18742,10 @@
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.4969</v>
+        <v>0.48895</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H129" s="15" t="n">
         <v>100</v>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18808,13 +18808,13 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.5031219512195123</v>
+        <v>0.5110170731707318</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>-101</v>
+        <v>-105</v>
       </c>
       <c r="H130" s="15" t="n">
-        <v>105</v>
+        <v>-105</v>
       </c>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
@@ -18838,7 +18838,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -19266,10 +19266,10 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.5539333333333333</v>
+        <v>0.5553916666666666</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-124</v>
+        <v>-125</v>
       </c>
       <c r="H137" s="15" t="n">
         <v>-140</v>
@@ -19296,7 +19296,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -19332,13 +19332,13 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4461009174311927</v>
+        <v>0.4446363636363636</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H138" s="15" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I138" s="13">
         <f>IF($H$138="","",IF($H$138&lt;0,-$H$138/(-$H$138+100),100/($H$138+100)))</f>
@@ -19362,7 +19362,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -19522,17 +19522,17 @@
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.5444</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>-105</v>
+        <v>-119</v>
       </c>
       <c r="H141" s="15" t="n">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I141" s="13">
         <f>IF($H$141="","",IF($H$141&lt;0,-$H$141/(-$H$141+100),100/($H$141+100)))</f>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="N141" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O141" s="15" t="n"/>
@@ -19588,14 +19588,14 @@
       </c>
       <c r="E142" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.4883780487804879</v>
+        <v>0.4556</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="H142" s="15" t="n">
         <v>-105</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="N142" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O142" s="15" t="n"/>
@@ -19658,13 +19658,13 @@
         </is>
       </c>
       <c r="F143" s="13" t="n">
-        <v>0.3926984126984127</v>
+        <v>0.3909019607843138</v>
       </c>
       <c r="G143" s="14" t="n">
+        <v>156</v>
+      </c>
+      <c r="H143" s="15" t="n">
         <v>155</v>
-      </c>
-      <c r="H143" s="15" t="n">
-        <v>152</v>
       </c>
       <c r="I143" s="13">
         <f>IF($H$143="","",IF($H$143&lt;0,-$H$143/(-$H$143+100),100/($H$143+100)))</f>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="N143" s="19" t="inlineStr">
         <is>
-          <t>Model 39.3% (fair +155). Your call.</t>
+          <t>Model 39.1% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O143" s="15" t="n"/>
@@ -19724,10 +19724,10 @@
         </is>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.6072622641509434</v>
+        <v>0.6091301886792453</v>
       </c>
       <c r="G144" s="14" t="n">
-        <v>-155</v>
+        <v>-156</v>
       </c>
       <c r="H144" s="15" t="n">
         <v>-165</v>
@@ -19754,7 +19754,7 @@
       </c>
       <c r="N144" s="19" t="inlineStr">
         <is>
-          <t>Model 60.7% (fair -155). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O144" s="15" t="n"/>
@@ -19790,7 +19790,7 @@
         </is>
       </c>
       <c r="F145" s="13" t="n">
-        <v>0.4976</v>
+        <v>0.4973</v>
       </c>
       <c r="G145" s="14" t="n">
         <v>101</v>
@@ -19818,7 +19818,7 @@
       </c>
       <c r="N145" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O145" s="15" t="n"/>
@@ -19854,7 +19854,7 @@
         </is>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.5024</v>
+        <v>0.5027</v>
       </c>
       <c r="G146" s="14" t="n">
         <v>-101</v>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="N146" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O146" s="15" t="n"/>
@@ -19918,7 +19918,7 @@
         </is>
       </c>
       <c r="F147" s="13" t="n">
-        <v>0.4289</v>
+        <v>0.4293</v>
       </c>
       <c r="G147" s="14" t="n">
         <v>133</v>
@@ -19982,7 +19982,7 @@
         </is>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5707</v>
       </c>
       <c r="G148" s="14" t="n">
         <v>-133</v>

--- a/data/output/workbook/2026-07-07.xlsx
+++ b/data/output/workbook/2026-07-07.xlsx
@@ -490,7 +490,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10715625"/>
+    <ext cx="10125075" cy="11144250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -580,7 +580,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10715625"/>
+    <ext cx="10125075" cy="11144250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07 16:07</t>
+          <t>2026-07-07 18:20</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3022,899 +3022,899 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="28" t="inlineStr">
         <is>
           <t>Atlanta Braves offense vs Pittsburgh Pirates defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B72" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C72" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D72" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E72" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F72" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G72" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H72" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I72" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="29" t="inlineStr">
+      <c r="J72" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K72" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L72" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr">
+      <c r="M72" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="29" t="inlineStr">
+      <c r="N72" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O72" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="29" t="inlineStr">
+      <c r="P72" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="29" t="inlineStr">
+      <c r="Q72" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>4.987</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>4.771</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B71" s="31" t="n">
-        <v>8.958</v>
-      </c>
-      <c r="C71" s="31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="31" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B72" s="31" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="C72" s="31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="31" t="n">
-        <v>0.896</v>
-      </c>
-      <c r="Q72" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>7.688</v>
+        <v>4.987</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.167</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="O73" s="31" t="n">
+        <v>5.533</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>9.292</v>
+        <v>4.771</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>8.958</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="C75" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="31" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B76" s="31" t="n">
+        <v>7.688</v>
+      </c>
+      <c r="C76" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="31" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P76" s="31" t="n">
+        <v>9.292</v>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B77" s="31" t="n">
         <v>0.605</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C77" s="31" t="n">
         <v>0.667</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D77" s="31" t="n">
         <v>0.65</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E77" s="31" t="n">
         <v>0.667</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F77" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G77" s="31" t="n">
         <v>1.6</v>
       </c>
-      <c r="H74" s="33" t="inlineStr">
+      <c r="H77" s="33" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr">
+      <c r="I77" s="31" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J74" s="33" t="inlineStr">
+      <c r="J77" s="33" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K77" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L77" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M77" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N77" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O77" s="31" t="n">
         <v>0.433</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P77" s="31" t="n">
         <v>0.41</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q77" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="28" t="inlineStr">
         <is>
           <t>Pittsburgh Pirates offense vs Atlanta Braves defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B80" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C80" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D80" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E80" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="29" t="inlineStr">
+      <c r="F80" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="29" t="inlineStr">
+      <c r="G80" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H80" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="29" t="inlineStr">
+      <c r="I80" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="29" t="inlineStr">
+      <c r="J80" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="29" t="inlineStr">
+      <c r="K80" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="29" t="inlineStr">
+      <c r="L80" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="29" t="inlineStr">
+      <c r="M80" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="29" t="inlineStr">
+      <c r="N80" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="29" t="inlineStr">
+      <c r="O80" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="29" t="inlineStr">
+      <c r="P80" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="29" t="inlineStr">
+      <c r="Q80" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>5.157</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>5.467</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J78" s="32" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>3.923</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B79" s="31" t="n">
-        <v>8.811999999999999</v>
-      </c>
-      <c r="C79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="31" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P79" s="31" t="n">
-        <v>7.312</v>
-      </c>
-      <c r="Q79" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="30" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B80" s="31" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="C80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="31" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P80" s="31" t="n">
-        <v>1.062</v>
-      </c>
-      <c r="Q80" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>9.708</v>
-      </c>
-      <c r="C81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.157</v>
+      </c>
+      <c r="C81" s="31" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="D81" s="31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J81" s="32" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L81" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M81" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="N81" s="31" t="n">
+        <v>4.95</v>
       </c>
       <c r="O81" s="31" t="n">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>8.561999999999999</v>
+        <v>3.923</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>8.811999999999999</v>
+      </c>
+      <c r="C82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>7.312</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B83" s="31" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="C83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O83" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P83" s="31" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="Q83" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B84" s="31" t="n">
+        <v>9.708</v>
+      </c>
+      <c r="C84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="31" t="inlineStr"/>
+      <c r="J84" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O84" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="P84" s="31" t="n">
+        <v>8.561999999999999</v>
+      </c>
+      <c r="Q84" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="31" t="n">
+      <c r="B85" s="31" t="n">
         <v>0.538</v>
       </c>
-      <c r="C82" s="31" t="n">
+      <c r="C85" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="D82" s="31" t="n">
+      <c r="D85" s="31" t="n">
         <v>0.35</v>
       </c>
-      <c r="E82" s="31" t="n">
+      <c r="E85" s="31" t="n">
         <v>0.267</v>
       </c>
-      <c r="F82" s="31" t="n">
+      <c r="F85" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="G82" s="31" t="n">
+      <c r="G85" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="H82" s="32" t="inlineStr">
+      <c r="H85" s="32" t="inlineStr">
         <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
+      <c r="I85" s="31" t="inlineStr"/>
+      <c r="J85" s="35" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="K82" s="31" t="n">
+      <c r="K85" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="L82" s="31" t="n">
+      <c r="L85" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="M82" s="31" t="n">
+      <c r="M85" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="N82" s="31" t="n">
+      <c r="N85" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="O82" s="31" t="n">
+      <c r="O85" s="31" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="P82" s="31" t="n">
+      <c r="P85" s="31" t="n">
         <v>0.553</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q85" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5769,7 +5769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5786,911 +5786,911 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="28" t="inlineStr">
         <is>
           <t>Houston Astros offense vs Washington Nationals defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B72" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C72" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D72" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E72" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F72" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G72" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H72" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I72" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="29" t="inlineStr">
+      <c r="J72" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K72" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L72" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr">
+      <c r="M72" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="29" t="inlineStr">
+      <c r="N72" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O72" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="29" t="inlineStr">
+      <c r="P72" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="29" t="inlineStr">
+      <c r="Q72" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>4.914</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="32" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>5.268</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B71" s="31" t="n">
-        <v>8.083</v>
-      </c>
-      <c r="C71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="31" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B72" s="31" t="n">
-        <v>1.417</v>
-      </c>
-      <c r="C72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="31" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q72" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>7.729</v>
-      </c>
-      <c r="C73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.914</v>
+      </c>
+      <c r="C73" s="31" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J73" s="32" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O73" s="31" t="n">
+        <v>5</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>8.199999999999999</v>
+        <v>5.268</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>8.083</v>
+      </c>
+      <c r="C74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="C75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B76" s="31" t="n">
+        <v>7.729</v>
+      </c>
+      <c r="C76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="31" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P76" s="31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B77" s="31" t="n">
         <v>0.696</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C77" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D77" s="31" t="n">
         <v>0.45</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E77" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F77" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G77" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="H74" s="35" t="inlineStr">
+      <c r="H77" s="35" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
         <is>
           <t>6th</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K77" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L77" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M77" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N77" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O77" s="31" t="n">
         <v>0.433</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P77" s="31" t="n">
         <v>0.412</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q77" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="28" t="inlineStr">
         <is>
           <t>Washington Nationals offense vs Houston Astros defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B80" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C80" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D80" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E80" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="29" t="inlineStr">
+      <c r="F80" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="29" t="inlineStr">
+      <c r="G80" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H80" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="29" t="inlineStr">
+      <c r="I80" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="29" t="inlineStr">
+      <c r="J80" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="29" t="inlineStr">
+      <c r="K80" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="29" t="inlineStr">
+      <c r="L80" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="29" t="inlineStr">
+      <c r="M80" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="29" t="inlineStr">
+      <c r="N80" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="29" t="inlineStr">
+      <c r="O80" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="29" t="inlineStr">
+      <c r="P80" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="29" t="inlineStr">
+      <c r="Q80" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>5.354</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>5.567</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J78" s="32" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B79" s="31" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="C79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P79" s="31" t="n">
-        <v>7.625</v>
-      </c>
-      <c r="Q79" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="30" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B80" s="31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="C80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="31" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P80" s="31" t="n">
-        <v>1.292</v>
-      </c>
-      <c r="Q80" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="C81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.354</v>
+      </c>
+      <c r="C81" s="31" t="n">
+        <v>5.567</v>
+      </c>
+      <c r="D81" s="31" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J81" s="32" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L81" s="31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M81" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N81" s="31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O81" s="31" t="n">
+        <v>4.867</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>8.417</v>
+        <v>5</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="C82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>7.625</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B83" s="31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P83" s="31" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="Q83" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B84" s="31" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="C84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="31" t="inlineStr"/>
+      <c r="J84" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P84" s="31" t="n">
+        <v>8.417</v>
+      </c>
+      <c r="Q84" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="31" t="n">
+      <c r="B85" s="31" t="n">
         <v>0.825</v>
       </c>
-      <c r="C82" s="31" t="n">
+      <c r="C85" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="D82" s="31" t="n">
+      <c r="D85" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="E82" s="31" t="n">
+      <c r="E85" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="F82" s="31" t="n">
+      <c r="F85" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="G82" s="31" t="n">
+      <c r="G85" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H82" s="33" t="inlineStr">
+      <c r="H85" s="33" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="I82" s="31" t="inlineStr">
+      <c r="I85" s="31" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="J82" s="35" t="inlineStr">
+      <c r="J85" s="35" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="K82" s="31" t="n">
+      <c r="K85" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="L82" s="31" t="n">
+      <c r="L85" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="M82" s="31" t="n">
+      <c r="M85" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="N82" s="31" t="n">
+      <c r="N85" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="O82" s="31" t="n">
+      <c r="O85" s="31" t="n">
         <v>0.667</v>
       </c>
-      <c r="P82" s="31" t="n">
+      <c r="P85" s="31" t="n">
         <v>0.646</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q85" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6862937062937062</v>
+        <v>0.6795104895104894</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-219</v>
+        <v>-212</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>186</v>
@@ -8821,7 +8821,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 68.6% (fair -219). Your call.</t>
+          <t>Model 68.0% (fair -212). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8857,13 +8857,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6392657342657342</v>
+        <v>0.6392361111111111</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-177</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8923,10 +8923,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6328623188405799</v>
+        <v>0.6291666666666667</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-172</v>
+        <v>-170</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>176</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 63.3% (fair -172). Your call.</t>
+          <t>Model 62.9% (fair -170). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5876119402985075</v>
+        <v>0.593037037037037</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-142</v>
+        <v>-146</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -142). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9055,10 +9055,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5720149253731344</v>
+        <v>0.5679104477611941</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-134</v>
+        <v>-131</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>168</v>
@@ -9085,7 +9085,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9121,13 +9121,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5546666666666666</v>
+        <v>0.5734600760456274</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-125</v>
+        <v>-134</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9187,10 +9187,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5148888888888888</v>
+        <v>0.5175925925925925</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>170</v>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.7350906976744187</v>
+        <v>0.7345558139534885</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-277</v>
@@ -9319,10 +9319,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4851111111111111</v>
+        <v>0.4824074074074074</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>170</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9381,17 +9381,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4453454545454545</v>
+        <v>0.6438395348837209</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>125</v>
+        <v>-181</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>175</v>
+        <v>-115</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9432,12 +9432,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9447,17 +9447,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.6550186046511628</v>
+        <v>0.5242358078602619</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-190</v>
+        <v>-110</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-115</v>
+        <v>129</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 65.5% (fair -190). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9513,17 +9513,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6135291866028708</v>
+        <v>0.4265357142857143</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-159</v>
+        <v>134</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-109</v>
+        <v>180</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 42.7% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5983096153846152</v>
+        <v>0.5990884615384615</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>-149</v>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9625,17 +9625,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9645,17 +9645,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.428</v>
+        <v>0.6087676056338028</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>134</v>
+        <v>-156</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>165</v>
+        <v>-113</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9696,12 +9696,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9711,17 +9711,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4123880597014926</v>
+        <v>0.4321132075471698</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9745,7 +9745,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +142). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -9772,22 +9772,22 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves +1.5</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5678753623188406</v>
+        <v>0.3634983498349835</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-131</v>
+        <v>175</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-107</v>
+        <v>203</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 36.3% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9823,37 +9823,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.3684121621621622</v>
+        <v>0.4069629629629629</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 36.8% (fair +171). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9894,32 +9894,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Atlanta Braves +1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5557882352941176</v>
+        <v>0.569025</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-125</v>
+        <v>-132</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9955,7 +9955,7 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
@@ -9979,13 +9979,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5707826291079813</v>
+        <v>0.5270588235294117</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-133</v>
+        <v>-111</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-113</v>
+        <v>104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10021,17 +10021,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4321544715447154</v>
+        <v>0.3952222222222222</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +131). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10092,32 +10092,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5433365853658536</v>
+        <v>0.5734078341013824</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-119</v>
+        <v>-134</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-105</v>
+        <v>-117</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -10168,22 +10168,22 @@
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4793212669683258</v>
+        <v>0.4310162601626016</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10219,17 +10219,17 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -10239,17 +10239,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5134803921568628</v>
+        <v>0.4764864864864866</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-106</v>
+        <v>110</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -106). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10290,32 +10290,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.3965530303030304</v>
+        <v>0.5071634615384615</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>152</v>
+        <v>-103</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10375,13 +10375,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5535408450704226</v>
+        <v>0.543063768115942</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-124</v>
+        <v>-119</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-113</v>
+        <v>-107</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10582,10 +10582,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6149</v>
+        <v>0.6122</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-160</v>
+        <v>-158</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>-110</v>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -160). Your call.</t>
+          <t>Model 61.2% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3851</v>
+        <v>0.3878</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>203</v>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 38.5% (fair +160). Your call.</t>
+          <t>Model 38.8% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5689</v>
+        <v>0.5516</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-132</v>
+        <v>-123</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>141</v>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10780,10 +10780,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4311</v>
+        <v>0.4484</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>100</v>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10846,10 +10846,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.2648928571428572</v>
+        <v>0.2654642857142858</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>180</v>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 26.5% (fair +278). Your call.</t>
+          <t>Model 26.5% (fair +277). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.7350906976744187</v>
+        <v>0.7345558139534885</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>-277</v>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5291</v>
+        <v>0.5182</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>-110</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11044,10 +11044,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4709</v>
+        <v>0.4818</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>203</v>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.6603</v>
+        <v>0.6528</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-194</v>
+        <v>-188</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>141</v>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 66.0% (fair -194). Your call.</t>
+          <t>Model 65.3% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11176,10 +11176,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.3397</v>
+        <v>0.3472</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>100</v>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 34.0% (fair +194). Your call.</t>
+          <t>Model 34.7% (fair +188). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11242,10 +11242,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.345</v>
+        <v>0.3561428571428571</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>180</v>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 34.5% (fair +190). Your call.</t>
+          <t>Model 35.6% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6550186046511628</v>
+        <v>0.6438395348837209</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-190</v>
+        <v>-181</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-115</v>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 65.5% (fair -190). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11374,13 +11374,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4898334975369458</v>
+        <v>0.4882671641791045</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-103</v>
+        <v>-101</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5101470588235294</v>
+        <v>0.5117647058823529</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>104</v>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11506,13 +11506,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4728</v>
+        <v>0.468</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11572,10 +11572,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5272</v>
+        <v>0.532</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-112</v>
+        <v>-114</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>100</v>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11638,13 +11638,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.3684121621621622</v>
+        <v>0.3634983498349835</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 36.8% (fair +171). Your call.</t>
+          <t>Model 36.3% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11704,13 +11704,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6315421404682274</v>
+        <v>0.6364686468646864</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-171</v>
+        <v>-175</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-199</v>
+        <v>-203</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 63.2% (fair -171). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11770,13 +11770,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.617</v>
+        <v>0.6103</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-161</v>
+        <v>-157</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11800,7 +11800,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 61.0% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11836,13 +11836,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.383</v>
+        <v>0.3897</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 39.0% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11902,13 +11902,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4464150943396226</v>
+        <v>0.4569607843137255</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11968,13 +11968,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5535408450704226</v>
+        <v>0.543063768115942</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-124</v>
+        <v>-119</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-113</v>
+        <v>-107</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12034,10 +12034,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4241452991452992</v>
+        <v>0.4251282051282051</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>134</v>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12100,13 +12100,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5758468085106383</v>
+        <v>0.5748682403433477</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-136</v>
+        <v>-135</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-135</v>
+        <v>-133</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12166,10 +12166,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5583</v>
+        <v>0.5147549019607843</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-126</v>
+        <v>-106</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>104</v>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12232,13 +12232,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4417</v>
+        <v>0.4852669950738916</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>130</v>
+        <v>-103</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4321544715447154</v>
+        <v>0.4310162601626016</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>146</v>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +131). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12364,13 +12364,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5678753623188406</v>
+        <v>0.569025</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-131</v>
+        <v>-132</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12430,13 +12430,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4606542056074767</v>
+        <v>0.4583870967741936</v>
       </c>
       <c r="G33" s="14" t="n">
+        <v>118</v>
+      </c>
+      <c r="H33" s="15" t="n">
         <v>117</v>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>114</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12496,10 +12496,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5393322580645161</v>
+        <v>0.5415967741935483</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-117</v>
+        <v>-118</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>-117</v>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12568,7 +12568,7 @@
         <v>109</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12634,7 +12634,7 @@
         <v>-109</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12760,13 +12760,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.6392657342657342</v>
+        <v>0.6392361111111111</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>-177</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12826,13 +12826,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4793212669683258</v>
+        <v>0.4764864864864866</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12892,13 +12892,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5206769585253456</v>
+        <v>0.5235009009009008</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-117</v>
+        <v>-122</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12954,17 +12954,17 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5322</v>
+        <v>0.5414</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-114</v>
+        <v>-118</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12988,7 +12988,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13020,17 +13020,17 @@
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4678</v>
+        <v>0.4586</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.313705035971223</v>
+        <v>0.3205035971223021</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>178</v>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 31.4% (fair +219). Your call.</t>
+          <t>Model 32.1% (fair +212). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13156,10 +13156,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.6862937062937062</v>
+        <v>0.6795104895104894</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-219</v>
+        <v>-212</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>186</v>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 68.6% (fair -219). Your call.</t>
+          <t>Model 68.0% (fair -212). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13222,13 +13222,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4016666666666667</v>
+        <v>0.4009004739336492</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>149</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5983096153846152</v>
+        <v>0.5990884615384615</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>-149</v>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13350,17 +13350,17 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.5100980392156863</v>
+        <v>0.4606</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>-104</v>
+        <v>117</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13384,7 +13384,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13416,17 +13416,17 @@
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.4899</v>
+        <v>0.5394</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>104</v>
+        <v>-117</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13486,10 +13486,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4851111111111111</v>
+        <v>0.4824074074074074</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>170</v>
@@ -13516,7 +13516,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13552,10 +13552,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5148888888888888</v>
+        <v>0.5175925925925925</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>170</v>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13618,13 +13618,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4267659574468085</v>
+        <v>0.4236554621848739</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13684,13 +13684,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5732218487394958</v>
+        <v>0.5763638297872341</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-134</v>
+        <v>-136</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-138</v>
+        <v>-135</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13746,17 +13746,17 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.3904</v>
+        <v>0.4843</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 48.4% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13812,17 +13812,17 @@
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.6095999999999999</v>
+        <v>0.5157</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-156</v>
+        <v>-106</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-104</v>
+        <v>117</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 51.6% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13882,10 +13882,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.38644</v>
+        <v>0.39124</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>150</v>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 39.1% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13948,13 +13948,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.6135291866028708</v>
+        <v>0.6087676056338028</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-159</v>
+        <v>-156</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-109</v>
+        <v>-113</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14014,13 +14014,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.628671653543307</v>
+        <v>0.6278444444444444</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>-169</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>-154</v>
+        <v>-152</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -169). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.3713671875</v>
+        <v>0.3721484375</v>
       </c>
       <c r="G58" s="14" t="n">
         <v>169</v>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 37.1% (fair +169). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14146,13 +14146,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5079</v>
+        <v>0.4718</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-103</v>
+        <v>112</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14212,10 +14212,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4921</v>
+        <v>0.5282</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>103</v>
+        <v>-112</v>
       </c>
       <c r="H60" s="15" t="n">
         <v>120</v>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14278,10 +14278,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4941529411764706</v>
+        <v>0.4757490196078431</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>-104</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5058415841584158</v>
+        <v>0.5242358078602619</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14410,13 +14410,13 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.4441666666666667</v>
+        <v>0.47295</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -14440,7 +14440,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14476,13 +14476,13 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5557882352941176</v>
+        <v>0.5270588235294117</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-125</v>
+        <v>-111</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14538,17 +14538,17 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4342</v>
+        <v>0.5009333333333333</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>130</v>
+        <v>-100</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>117</v>
+        <v>-104</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14604,17 +14604,17 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5658000000000001</v>
+        <v>0.4990776699029126</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-130</v>
+        <v>100</v>
       </c>
       <c r="H66" s="15" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I66" s="13">
         <f>IF($H$66="","",IF($H$66&lt;0,-$H$66/(-$H$66+100),100/($H$66+100)))</f>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14674,13 +14674,13 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.4453454545454545</v>
+        <v>0.4265357142857143</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
@@ -14704,7 +14704,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 42.7% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14740,13 +14740,13 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5546666666666666</v>
+        <v>0.5734600760456274</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-125</v>
+        <v>-134</v>
       </c>
       <c r="H68" s="15" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I68" s="13">
         <f>IF($H$68="","",IF($H$68&lt;0,-$H$68/(-$H$68+100),100/($H$68+100)))</f>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14806,10 +14806,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5085</v>
+        <v>0.5105</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4915</v>
+        <v>0.4895</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +103). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14934,10 +14934,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4713</v>
+        <v>0.4594</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14998,10 +14998,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5406</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-112</v>
+        <v>-118</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15062,10 +15062,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.478</v>
+        <v>0.4649</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H73" s="15" t="n"/>
       <c r="I73" s="13">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.522</v>
+        <v>0.5351</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-109</v>
+        <v>-115</v>
       </c>
       <c r="H74" s="15" t="n"/>
       <c r="I74" s="13">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15190,10 +15190,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4332</v>
+        <v>0.4221</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H75" s="15" t="n"/>
       <c r="I75" s="13">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15254,10 +15254,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5668</v>
+        <v>0.5779</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-131</v>
+        <v>-137</v>
       </c>
       <c r="H76" s="15" t="n"/>
       <c r="I76" s="13">
@@ -15282,7 +15282,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15318,10 +15318,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.3789</v>
+        <v>0.3565</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="H77" s="15" t="n"/>
       <c r="I77" s="13">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 35.6% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15382,10 +15382,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.6211</v>
+        <v>0.6435</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-164</v>
+        <v>-181</v>
       </c>
       <c r="H78" s="15" t="n"/>
       <c r="I78" s="13">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 64.3% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15584,7 +15584,7 @@
         <v>116</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15650,7 +15650,7 @@
         <v>-116</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15710,13 +15710,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.6365298245614035</v>
+        <v>0.6372784172661871</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-175</v>
+        <v>-176</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>-185</v>
+        <v>-178</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -175). Your call.</t>
+          <t>Model 63.7% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.3634716981132076</v>
+        <v>0.3627407407407408</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +175). Your call.</t>
+          <t>Model 36.3% (fair +176). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15842,10 +15842,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4702884615384615</v>
+        <v>0.4707211538461538</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>108</v>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15908,10 +15908,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5296761904761905</v>
+        <v>0.5293095238095238</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-113</v>
+        <v>-112</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>-110</v>
@@ -15938,7 +15938,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15974,10 +15974,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.49125</v>
+        <v>0.5071634615384615</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>104</v>
+        <v>-103</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>108</v>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16040,13 +16040,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5087279069767443</v>
+        <v>0.49285</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-104</v>
+        <v>103</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-115</v>
+        <v>100</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16106,13 +16106,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.6155357142857143</v>
+        <v>0.6167851851851851</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-160</v>
+        <v>-161</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-180</v>
+        <v>-170</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16172,13 +16172,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.3844313725490196</v>
+        <v>0.3831939163498099</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +160). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.416</v>
+        <v>0.3947131147540984</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16304,10 +16304,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.584</v>
+        <v>0.6052865546218488</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-140</v>
+        <v>-153</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>-138</v>
@@ -16334,7 +16334,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 60.5% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5433365853658536</v>
+        <v>0.6012</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-119</v>
+        <v>-151</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>-105</v>
+        <v>105</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16436,13 +16436,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.4566341463414635</v>
+        <v>0.3988</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16466,7 +16466,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16502,13 +16502,13 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4328151260504202</v>
+        <v>0.4288934426229508</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16568,10 +16568,10 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5672163265306123</v>
+        <v>0.5711224489795919</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-131</v>
+        <v>-133</v>
       </c>
       <c r="H96" s="15" t="n">
         <v>-145</v>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16766,10 +16766,10 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.5068170731707318</v>
+        <v>0.5193658536585366</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-103</v>
+        <v>-108</v>
       </c>
       <c r="H99" s="15" t="n">
         <v>-105</v>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16832,13 +16832,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.4931707317073171</v>
+        <v>0.4806372549019608</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16898,10 +16898,10 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.428</v>
+        <v>0.4321132075471698</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H101" s="15" t="n">
         <v>165</v>
@@ -16928,7 +16928,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -16964,10 +16964,10 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5720149253731344</v>
+        <v>0.5679104477611941</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-134</v>
+        <v>-131</v>
       </c>
       <c r="H102" s="15" t="n">
         <v>168</v>
@@ -16994,7 +16994,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17030,13 +17030,13 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.4897</v>
+        <v>0.5394</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>104</v>
+        <v>-117</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17096,13 +17096,13 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5103</v>
+        <v>0.4606</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-104</v>
+        <v>117</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -17153,22 +17153,22 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4554377880184332</v>
+        <v>0.5214</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>120</v>
+        <v>-109</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>117</v>
+        <v>-110</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -17192,7 +17192,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="B106" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C106" s="20" t="inlineStr">
@@ -17219,22 +17219,22 @@
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5445818181818182</v>
+        <v>0.4786047619047619</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-120</v>
+        <v>109</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17275,7 +17275,7 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -17285,22 +17285,22 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Miami Marlins +1.5</t>
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.5092243902439024</v>
+        <v>0.5797040816326531</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-104</v>
+        <v>-138</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>-105</v>
+        <v>-145</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -17324,7 +17324,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17341,7 +17341,7 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C108" s="20" t="inlineStr">
@@ -17351,22 +17351,22 @@
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Seattle Mariners -1.5</t>
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4907882352941176</v>
+        <v>0.4202666666666667</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>-104</v>
+        <v>125</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -17390,7 +17390,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17417,22 +17417,22 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays -1.5</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.3671538461538462</v>
+        <v>0.4555299539170507</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="H109" s="15" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="I109" s="13">
         <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
@@ -17456,7 +17456,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 36.7% (fair +172). Your call.</t>
+          <t>Model 45.6% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17483,22 +17483,22 @@
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees +1.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.6328623188405799</v>
+        <v>0.5444727272727272</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-172</v>
+        <v>-120</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>176</v>
+        <v>-120</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -17522,7 +17522,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 63.3% (fair -172). Your call.</t>
+          <t>Model 54.4% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17539,32 +17539,32 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.4464055299539171</v>
+        <v>0.5303490196078431</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>124</v>
+        <v>-113</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>117</v>
+        <v>-104</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -17588,7 +17588,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17605,32 +17605,32 @@
       </c>
       <c r="B112" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C112" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.5536202764976959</v>
+        <v>0.469656862745098</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>-124</v>
+        <v>113</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>-117</v>
+        <v>104</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17671,32 +17671,32 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Tampa Bay Rays -1.5</t>
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.5317</v>
+        <v>0.3708518518518519</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>-114</v>
+        <v>170</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17720,7 +17720,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 37.1% (fair +170). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17737,32 +17737,32 @@
       </c>
       <c r="B114" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C114" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>New York Yankees +1.5</t>
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.4683</v>
+        <v>0.6291666666666667</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>114</v>
+        <v>-170</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17786,7 +17786,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 62.9% (fair -170). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17813,22 +17813,22 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4063008130081301</v>
+        <v>0.4433179723502304</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17879,22 +17879,22 @@
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.593688679245283</v>
+        <v>0.5566936936936936</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-146</v>
+        <v>-126</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-165</v>
+        <v>-122</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17918,7 +17918,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -17935,32 +17935,32 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.4265665236051502</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>134</v>
+        <v>-134</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18001,32 +18001,32 @@
       </c>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C118" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.5734412017167382</v>
+        <v>0.4278999999999999</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>-134</v>
+        <v>134</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>-133</v>
+        <v>122</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18067,32 +18067,32 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.5134803921568628</v>
+        <v>0.4005118110236221</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>-106</v>
+        <v>150</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -106). Your call.</t>
+          <t>Model 40.1% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18133,32 +18133,32 @@
       </c>
       <c r="B120" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C120" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.4865058823529412</v>
+        <v>0.5994703703703703</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>106</v>
+        <v>-150</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-104</v>
+        <v>-170</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +106). Your call.</t>
+          <t>Model 59.9% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18199,12 +18199,12 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
@@ -18214,17 +18214,17 @@
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.4292093023255814</v>
+        <v>0.4264806866952789</v>
       </c>
       <c r="G121" s="14" t="n">
+        <v>134</v>
+      </c>
+      <c r="H121" s="15" t="n">
         <v>133</v>
-      </c>
-      <c r="H121" s="15" t="n">
-        <v>115</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -18248,7 +18248,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 42.6% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -18265,12 +18265,12 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C122" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
@@ -18280,17 +18280,17 @@
       </c>
       <c r="E122" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.5707826291079813</v>
+        <v>0.5734982832618025</v>
       </c>
       <c r="G122" s="14" t="n">
+        <v>-134</v>
+      </c>
+      <c r="H122" s="15" t="n">
         <v>-133</v>
-      </c>
-      <c r="H122" s="15" t="n">
-        <v>-113</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -18331,32 +18331,32 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.510709756097561</v>
+        <v>0.5134803921568628</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="H123" s="15" t="n">
-        <v>-105</v>
+        <v>104</v>
       </c>
       <c r="I123" s="13">
         <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 51.3% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -18397,32 +18397,32 @@
       </c>
       <c r="B124" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C124" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.4892411214953271</v>
+        <v>0.4865058823529412</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H124" s="15" t="n">
-        <v>-114</v>
+        <v>-104</v>
       </c>
       <c r="I124" s="13">
         <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
@@ -18446,7 +18446,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 48.7% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -18473,22 +18473,22 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.3965530303030304</v>
+        <v>0.4266046511627907</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
@@ -18512,7 +18512,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 42.7% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18539,22 +18539,22 @@
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.6034245614035088</v>
+        <v>0.5734078341013824</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-152</v>
+        <v>-134</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>-185</v>
+        <v>-117</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 60.3% (fair -152). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18595,7 +18595,7 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -18605,21 +18605,23 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.4398</v>
+        <v>0.511</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>127</v>
-      </c>
-      <c r="H127" s="15" t="n"/>
+        <v>-104</v>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="I127" s="13">
         <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
         <v/>
@@ -18642,7 +18644,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18659,7 +18661,7 @@
       </c>
       <c r="B128" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C128" s="20" t="inlineStr">
@@ -18669,21 +18671,23 @@
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.5602</v>
+        <v>0.4890115384615384</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-127</v>
-      </c>
-      <c r="H128" s="15" t="n"/>
+        <v>104</v>
+      </c>
+      <c r="H128" s="15" t="n">
+        <v>-108</v>
+      </c>
       <c r="I128" s="13">
         <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
         <v/>
@@ -18706,7 +18710,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18723,7 +18727,7 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
@@ -18733,22 +18737,22 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.48895</v>
+        <v>0.3952222222222222</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="H129" s="15" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
@@ -18772,7 +18776,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18789,7 +18793,7 @@
       </c>
       <c r="B130" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C130" s="20" t="inlineStr">
@@ -18799,22 +18803,22 @@
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.5110170731707318</v>
+        <v>0.604751798561151</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>-105</v>
+        <v>-153</v>
       </c>
       <c r="H130" s="15" t="n">
-        <v>-105</v>
+        <v>-178</v>
       </c>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
@@ -18838,7 +18842,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 60.5% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -18865,23 +18869,21 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.4123880597014926</v>
+        <v>0.4484</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>142</v>
-      </c>
-      <c r="H131" s="15" t="n">
-        <v>168</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H131" s="15" t="n"/>
       <c r="I131" s="13">
         <f>IF($H$131="","",IF($H$131&lt;0,-$H$131/(-$H$131+100),100/($H$131+100)))</f>
         <v/>
@@ -18904,7 +18906,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +142). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -18931,23 +18933,21 @@
       </c>
       <c r="D132" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.5876119402985075</v>
+        <v>0.5516</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>-142</v>
-      </c>
-      <c r="H132" s="15" t="n">
-        <v>168</v>
-      </c>
+        <v>-123</v>
+      </c>
+      <c r="H132" s="15" t="n"/>
       <c r="I132" s="13">
         <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
         <v/>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -142). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -18987,31 +18987,33 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>0.5924</v>
+        <v>0.4585</v>
       </c>
       <c r="G133" s="14" t="n">
-        <v>-145</v>
-      </c>
-      <c r="H133" s="15" t="n"/>
+        <v>118</v>
+      </c>
+      <c r="H133" s="15" t="n">
+        <v>108</v>
+      </c>
       <c r="I133" s="13">
         <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
         <v/>
@@ -19034,7 +19036,7 @@
       </c>
       <c r="N133" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O133" s="15" t="n"/>
@@ -19051,31 +19053,33 @@
       </c>
       <c r="B134" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C134" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.4076</v>
+        <v>0.5415</v>
       </c>
       <c r="G134" s="14" t="n">
-        <v>145</v>
-      </c>
-      <c r="H134" s="15" t="n"/>
+        <v>-118</v>
+      </c>
+      <c r="H134" s="15" t="n">
+        <v>105</v>
+      </c>
       <c r="I134" s="13">
         <f>IF($H$134="","",IF($H$134&lt;0,-$H$134/(-$H$134+100),100/($H$134+100)))</f>
         <v/>
@@ -19098,7 +19102,7 @@
       </c>
       <c r="N134" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O134" s="15" t="n"/>
@@ -19115,32 +19119,32 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.50425</v>
+        <v>0.4069629629629629</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>-102</v>
+        <v>146</v>
       </c>
       <c r="H135" s="15" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="I135" s="13">
         <f>IF($H$135="","",IF($H$135&lt;0,-$H$135/(-$H$135+100),100/($H$135+100)))</f>
@@ -19164,7 +19168,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -19181,32 +19185,32 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C136" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E136" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.4957333333333333</v>
+        <v>0.593037037037037</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>102</v>
+        <v>-146</v>
       </c>
       <c r="H136" s="15" t="n">
-        <v>-110</v>
+        <v>170</v>
       </c>
       <c r="I136" s="13">
         <f>IF($H$136="","",IF($H$136&lt;0,-$H$136/(-$H$136+100),100/($H$136+100)))</f>
@@ -19230,7 +19234,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -19257,23 +19261,21 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.5553916666666666</v>
+        <v>0.585</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H137" s="15" t="n">
-        <v>-140</v>
-      </c>
+        <v>-141</v>
+      </c>
+      <c r="H137" s="15" t="n"/>
       <c r="I137" s="13">
         <f>IF($H$137="","",IF($H$137&lt;0,-$H$137/(-$H$137+100),100/($H$137+100)))</f>
         <v/>
@@ -19296,7 +19298,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -19323,23 +19325,21 @@
       </c>
       <c r="D138" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E138" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4446363636363636</v>
+        <v>0.415</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>125</v>
-      </c>
-      <c r="H138" s="15" t="n">
-        <v>120</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="H138" s="15" t="n"/>
       <c r="I138" s="13">
         <f>IF($H$138="","",IF($H$138&lt;0,-$H$138/(-$H$138+100),100/($H$138+100)))</f>
         <v/>
@@ -19362,7 +19362,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -19379,31 +19379,33 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.4669</v>
+        <v>0.4827</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>114</v>
-      </c>
-      <c r="H139" s="15" t="n"/>
+        <v>107</v>
+      </c>
+      <c r="H139" s="15" t="n">
+        <v>133</v>
+      </c>
       <c r="I139" s="13">
         <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
         <v/>
@@ -19426,7 +19428,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -19443,31 +19445,33 @@
       </c>
       <c r="B140" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C140" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E140" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.5331</v>
+        <v>0.5173</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H140" s="15" t="n"/>
+        <v>-107</v>
+      </c>
+      <c r="H140" s="15" t="n">
+        <v>105</v>
+      </c>
       <c r="I140" s="13">
         <f>IF($H$140="","",IF($H$140&lt;0,-$H$140/(-$H$140+100),100/($H$140+100)))</f>
         <v/>
@@ -19490,7 +19494,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -19507,32 +19511,32 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>0.5444</v>
+        <v>0.569336974789916</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>-119</v>
+        <v>-132</v>
       </c>
       <c r="H141" s="15" t="n">
-        <v>138</v>
+        <v>-138</v>
       </c>
       <c r="I141" s="13">
         <f>IF($H$141="","",IF($H$141&lt;0,-$H$141/(-$H$141+100),100/($H$141+100)))</f>
@@ -19556,7 +19560,7 @@
       </c>
       <c r="N141" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O141" s="15" t="n"/>
@@ -19573,32 +19577,32 @@
       </c>
       <c r="B142" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C142" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E142" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.4556</v>
+        <v>0.4306382978723404</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="H142" s="15" t="n">
-        <v>-105</v>
+        <v>135</v>
       </c>
       <c r="I142" s="13">
         <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
@@ -19622,7 +19626,7 @@
       </c>
       <c r="N142" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O142" s="15" t="n"/>
@@ -19649,23 +19653,21 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers -1.5</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F143" s="13" t="n">
-        <v>0.3909019607843138</v>
+        <v>0.4736</v>
       </c>
       <c r="G143" s="14" t="n">
-        <v>156</v>
-      </c>
-      <c r="H143" s="15" t="n">
-        <v>155</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="H143" s="15" t="n"/>
       <c r="I143" s="13">
         <f>IF($H$143="","",IF($H$143&lt;0,-$H$143/(-$H$143+100),100/($H$143+100)))</f>
         <v/>
@@ -19688,7 +19690,7 @@
       </c>
       <c r="N143" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +156). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O143" s="15" t="n"/>
@@ -19715,23 +19717,21 @@
       </c>
       <c r="D144" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E144" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels +1.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.6091301886792453</v>
+        <v>0.5264</v>
       </c>
       <c r="G144" s="14" t="n">
-        <v>-156</v>
-      </c>
-      <c r="H144" s="15" t="n">
-        <v>-165</v>
-      </c>
+        <v>-111</v>
+      </c>
+      <c r="H144" s="15" t="n"/>
       <c r="I144" s="13">
         <f>IF($H$144="","",IF($H$144&lt;0,-$H$144/(-$H$144+100),100/($H$144+100)))</f>
         <v/>
@@ -19754,7 +19754,7 @@
       </c>
       <c r="N144" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O144" s="15" t="n"/>
@@ -19790,7 +19790,7 @@
         </is>
       </c>
       <c r="F145" s="13" t="n">
-        <v>0.4973</v>
+        <v>0.4976</v>
       </c>
       <c r="G145" s="14" t="n">
         <v>101</v>
@@ -19818,7 +19818,7 @@
       </c>
       <c r="N145" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O145" s="15" t="n"/>
@@ -19854,7 +19854,7 @@
         </is>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.5027</v>
+        <v>0.5024</v>
       </c>
       <c r="G146" s="14" t="n">
         <v>-101</v>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="N146" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O146" s="15" t="n"/>
@@ -19918,7 +19918,7 @@
         </is>
       </c>
       <c r="F147" s="13" t="n">
-        <v>0.4293</v>
+        <v>0.4289</v>
       </c>
       <c r="G147" s="14" t="n">
         <v>133</v>
@@ -19982,7 +19982,7 @@
         </is>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.5707</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="G148" s="14" t="n">
         <v>-133</v>
@@ -20906,10 +20906,10 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2493</v>
+        <v>0.249</v>
       </c>
       <c r="D5" s="21" t="n">
         <v>241</v>
@@ -20937,10 +20937,10 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2506</v>
+        <v>0.2502</v>
       </c>
       <c r="D6" s="21" t="n">
         <v>202</v>
@@ -21041,7 +21041,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=322, ECE 0.058 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=324, ECE 0.058 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -21117,16 +21117,16 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>0.3708</v>
+        <v>0.3713</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>0.5938</v>
+        <v>0.5758</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>0.223</v>
+        <v>0.2045</v>
       </c>
     </row>
     <row r="20">
@@ -21136,16 +21136,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.4571</v>
+        <v>0.4573</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4151</v>
+        <v>0.4112</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.042</v>
+        <v>-0.0461</v>
       </c>
     </row>
     <row r="21">

--- a/data/output/workbook/2026-07-07.xlsx
+++ b/data/output/workbook/2026-07-07.xlsx
@@ -370,7 +370,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10687050"/>
+    <ext cx="10125075" cy="10544175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -430,7 +430,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10544175"/>
+    <ext cx="10125075" cy="10401300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -490,7 +490,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="11144250"/>
+    <ext cx="10125075" cy="10887075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07 18:20</t>
+          <t>2026-07-07 20:10</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1174,170 +1174,247 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t>Chicago Cubs offense vs Baltimore Orioles defense</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="28" t="inlineStr">
-        <is>
-          <t>Chicago Cubs offense vs Baltimore Orioles defense</t>
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B67" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C67" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D67" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E67" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F67" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G67" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H67" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I67" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J67" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K67" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L67" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M67" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N67" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O67" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P67" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q67" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B68" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C68" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D68" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E68" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F68" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G68" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H68" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I68" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J68" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K68" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L68" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M68" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N68" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O68" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P68" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q68" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="n">
+        <v>5.205</v>
+      </c>
+      <c r="C68" s="31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D68" s="31" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="E68" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F68" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G68" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H68" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I68" s="31" t="inlineStr"/>
+      <c r="J68" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K68" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L68" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M68" s="31" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="N68" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O68" s="31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P68" s="31" t="n">
+        <v>4.797</v>
+      </c>
+      <c r="Q68" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B69" s="31" t="n">
-        <v>5.205</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="C69" s="31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F69" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="G69" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
+        <v>4</v>
+      </c>
+      <c r="D69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I69" s="31" t="inlineStr"/>
-      <c r="J69" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>3.933</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O69" s="31" t="n">
-        <v>4.3</v>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P69" s="31" t="n">
-        <v>4.797</v>
+        <v>8.833</v>
       </c>
       <c r="Q69" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>8.438000000000001</v>
+        <v>1.104</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D70" s="31" t="inlineStr">
         <is>
@@ -1396,25 +1473,25 @@
         </is>
       </c>
       <c r="P70" s="31" t="n">
-        <v>8.833</v>
+        <v>1.062</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>1.104</v>
+        <v>8.458</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D71" s="31" t="inlineStr">
         <is>
@@ -1473,319 +1550,319 @@
         </is>
       </c>
       <c r="P71" s="31" t="n">
-        <v>1.062</v>
+        <v>8</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>8.458</v>
+        <v>0.468</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="D72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D72" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E72" s="31" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F72" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G72" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L72" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M72" s="31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N72" s="31" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O72" s="31" t="n">
+        <v>0.7</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>8</v>
+        <v>0.487</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B73" s="31" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="C73" s="31" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D73" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E73" s="31" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F73" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G73" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles offense vs Chicago Cubs defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B75" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C75" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D75" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E75" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F75" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G75" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H75" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I75" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J75" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K75" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L75" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M75" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N75" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O75" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P75" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q75" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B76" s="31" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="C76" s="31" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="D76" s="31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E76" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F76" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G76" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H76" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I76" s="31" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L73" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M73" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N73" s="31" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="O73" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P73" s="31" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="Q73" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles offense vs Chicago Cubs defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B76" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C76" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D76" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E76" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F76" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G76" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H76" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I76" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J76" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K76" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L76" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M76" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N76" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O76" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P76" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q76" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="J76" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K76" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L76" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="M76" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="N76" s="31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O76" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P76" s="31" t="n">
+        <v>4.782</v>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B77" s="31" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>4.567</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J77" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>4.75</v>
+        <v>8.208</v>
+      </c>
+      <c r="C77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O77" s="31" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="P77" s="31" t="n">
-        <v>4.782</v>
+        <v>7.896</v>
       </c>
       <c r="Q77" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>8.208</v>
+        <v>1.271</v>
       </c>
       <c r="C78" s="31" t="inlineStr">
         <is>
@@ -1844,25 +1921,25 @@
         </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>7.896</v>
+        <v>1.354</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>1.271</v>
+        <v>8.917</v>
       </c>
       <c r="C79" s="31" t="inlineStr">
         <is>
@@ -1921,148 +1998,71 @@
         </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>1.354</v>
+        <v>7.708</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.917</v>
-      </c>
-      <c r="C80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.526</v>
+      </c>
+      <c r="C80" s="31" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="D80" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E80" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F80" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G80" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I80" s="31" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J80" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K80" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L80" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M80" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N80" s="31" t="n">
+        <v>0.15</v>
       </c>
       <c r="O80" s="31" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>7.708</v>
+        <v>0.442</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B81" s="31" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="C81" s="31" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="D81" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E81" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F81" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G81" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L81" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M81" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N81" s="31" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O81" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P81" s="31" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="Q81" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3005,7 +3005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3022,174 +3022,328 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>Atlanta Braves offense vs Pittsburgh Pirates defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B70" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C70" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D70" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E70" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F70" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G70" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H70" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I70" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J70" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K70" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L70" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M70" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N70" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O70" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P70" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q70" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="71">
-      <c r="A71" s="28" t="inlineStr">
-        <is>
-          <t>Atlanta Braves offense vs Pittsburgh Pirates defense</t>
+      <c r="A71" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B71" s="31" t="n">
+        <v>4.987</v>
+      </c>
+      <c r="C71" s="31" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="O71" s="31" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="P71" s="31" t="n">
+        <v>4.771</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B72" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C72" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D72" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E72" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F72" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G72" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H72" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I72" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J72" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K72" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L72" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M72" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N72" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O72" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P72" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q72" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A72" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B72" s="31" t="n">
+        <v>8.958</v>
+      </c>
+      <c r="C72" s="31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr"/>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="31" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="Q72" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>4.987</v>
+        <v>1.333</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="D73" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E73" s="31" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="F73" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G73" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L73" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="M73" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N73" s="31" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="O73" s="31" t="n">
-        <v>5.533</v>
+        <v>1.5</v>
+      </c>
+      <c r="D73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P73" s="31" t="n">
-        <v>4.771</v>
+        <v>0.896</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>8.958</v>
+        <v>7.688</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="D74" s="31" t="inlineStr">
         <is>
@@ -3248,396 +3402,396 @@
         </is>
       </c>
       <c r="P74" s="31" t="n">
-        <v>7.792</v>
+        <v>9.292</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B75" s="31" t="n">
-        <v>1.333</v>
+        <v>0.605</v>
       </c>
       <c r="C75" s="31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.667</v>
+      </c>
+      <c r="D75" s="31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F75" s="31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G75" s="31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H75" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J75" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L75" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M75" s="31" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N75" s="31" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O75" s="31" t="n">
+        <v>0.433</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>0.896</v>
+        <v>0.41</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B76" s="31" t="n">
-        <v>7.688</v>
-      </c>
-      <c r="C76" s="31" t="n">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates offense vs Atlanta Braves defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B78" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D78" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E78" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F78" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G78" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H78" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I78" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J78" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K78" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L78" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M78" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N78" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O78" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P78" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q78" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B79" s="31" t="n">
+        <v>5.157</v>
+      </c>
+      <c r="C79" s="31" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G79" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="D76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="31" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P76" s="31" t="n">
-        <v>9.292</v>
-      </c>
-      <c r="Q76" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O77" s="31" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P77" s="31" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="28" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates offense vs Atlanta Braves defense</t>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J79" s="32" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="O79" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P79" s="31" t="n">
+        <v>3.923</v>
+      </c>
+      <c r="Q79" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B80" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C80" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D80" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E80" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F80" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G80" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H80" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I80" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J80" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K80" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L80" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M80" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N80" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O80" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P80" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q80" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A80" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B80" s="31" t="n">
+        <v>8.811999999999999</v>
+      </c>
+      <c r="C80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="31" t="inlineStr"/>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P80" s="31" t="n">
+        <v>7.312</v>
+      </c>
+      <c r="Q80" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>5.157</v>
-      </c>
-      <c r="C81" s="31" t="n">
-        <v>5.467</v>
-      </c>
-      <c r="D81" s="31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E81" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F81" s="31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G81" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="H81" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J81" s="32" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L81" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M81" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="N81" s="31" t="n">
-        <v>4.95</v>
+        <v>1.188</v>
+      </c>
+      <c r="C81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>3.923</v>
+        <v>1.062</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>8.811999999999999</v>
+        <v>9.708</v>
       </c>
       <c r="C82" s="31" t="inlineStr">
         <is>
@@ -3696,225 +3850,71 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>7.312</v>
+        <v>8.561999999999999</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B83" s="31" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="C83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.538</v>
+      </c>
+      <c r="C83" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D83" s="31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E83" s="31" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F83" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G83" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H83" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J83" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K83" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L83" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M83" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N83" s="31" t="n">
+        <v>0.6</v>
       </c>
       <c r="O83" s="31" t="n">
-        <v>1</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="P83" s="31" t="n">
-        <v>1.062</v>
+        <v>0.553</v>
       </c>
       <c r="Q83" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B84" s="31" t="n">
-        <v>9.708</v>
-      </c>
-      <c r="C84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H84" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I84" s="31" t="inlineStr"/>
-      <c r="J84" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O84" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="P84" s="31" t="n">
-        <v>8.561999999999999</v>
-      </c>
-      <c r="Q84" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B85" s="31" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="C85" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D85" s="31" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E85" s="31" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F85" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G85" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H85" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I85" s="31" t="inlineStr"/>
-      <c r="J85" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K85" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L85" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M85" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N85" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O85" s="31" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P85" s="31" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="Q85" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7645,7 +7645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7662,167 +7662,244 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies offense vs Cincinnati Reds defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="28" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies offense vs Cincinnati Reds defense</t>
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>4.519</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>5.567</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H69" s="32" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr"/>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>4.688</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>4.519</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>5.567</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="H70" s="32" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>7.234</v>
+      </c>
+      <c r="C70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>4.3</v>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O70" s="31" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>4.688</v>
+        <v>8.106</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>7.234</v>
+        <v>1.213</v>
       </c>
       <c r="C71" s="31" t="inlineStr">
         <is>
@@ -7881,25 +7958,25 @@
         </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>8.106</v>
+        <v>1.383</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>1.213</v>
+        <v>8.426</v>
       </c>
       <c r="C72" s="31" t="inlineStr">
         <is>
@@ -7958,321 +8035,321 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>1.383</v>
+        <v>7.404</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.426</v>
-      </c>
-      <c r="C73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="C73" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J73" s="32" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>0.4</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>11</v>
+        <v>0.467</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>7.404</v>
+        <v>0.553</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D74" s="31" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E74" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F74" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G74" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J74" s="32" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L74" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M74" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N74" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds offense vs Philadelphia Phillies defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="28" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds offense vs Philadelphia Phillies defense</t>
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>3.987</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H77" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="32" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>5.267</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>4.877</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>3.987</v>
+        <v>7.404</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H78" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
+        <v>4</v>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="32" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>5.267</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>5</v>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P78" s="31" t="n">
-        <v>4.877</v>
+        <v>9.319000000000001</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>7.404</v>
+        <v>1.213</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D79" s="31" t="inlineStr">
         <is>
@@ -8331,25 +8408,25 @@
         </is>
       </c>
       <c r="P79" s="31" t="n">
-        <v>9.319000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>1.213</v>
+        <v>9.532</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -8408,149 +8485,72 @@
         </is>
       </c>
       <c r="P80" s="31" t="n">
-        <v>1.17</v>
+        <v>9.276999999999999</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>9.532</v>
+        <v>0.553</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.533</v>
+      </c>
+      <c r="D81" s="31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J81" s="32" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L81" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M81" s="31" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="N81" s="31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O81" s="31" t="n">
+        <v>0.8</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>9.276999999999999</v>
+        <v>0.603</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="C82" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D82" s="31" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E82" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F82" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G82" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J82" s="32" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L82" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M82" s="31" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="N82" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O82" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P82" s="31" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6795104895104894</v>
+        <v>0.682062937062937</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-212</v>
+        <v>-215</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>186</v>
@@ -8821,7 +8821,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 68.0% (fair -212). Your call.</t>
+          <t>Model 68.2% (fair -215). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8857,10 +8857,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6392361111111111</v>
+        <v>0.6367361111111112</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-177</v>
+        <v>-175</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>188</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 63.7% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8970,12 +8970,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -8985,17 +8985,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>Chicago Cubs +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.593037037037037</v>
+        <v>0.6409885931558935</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-146</v>
+        <v>-179</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 64.1% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9051,17 +9051,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves +1.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5679104477611941</v>
+        <v>0.593037037037037</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-131</v>
+        <v>-146</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9085,7 +9085,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9097,17 +9097,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9117,17 +9117,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Atlanta Braves +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5734600760456274</v>
+        <v>0.5679104477611941</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-134</v>
+        <v>-131</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9168,12 +9168,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -9183,17 +9183,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5175925925925925</v>
+        <v>0.5734600760456274</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-107</v>
+        <v>-134</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9249,17 +9249,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.7345558139534885</v>
+        <v>0.5172962962962963</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-277</v>
+        <v>-107</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-115</v>
+        <v>170</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 73.5% (fair -277). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9300,12 +9300,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9315,17 +9315,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4824074074074074</v>
+        <v>0.7254093023255815</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>107</v>
+        <v>-264</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>170</v>
+        <v>-115</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 72.5% (fair -264). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9381,17 +9381,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6438395348837209</v>
+        <v>0.4827037037037037</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-181</v>
+        <v>107</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-115</v>
+        <v>170</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9432,12 +9432,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9447,17 +9447,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies -1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5242358078602619</v>
+        <v>0.6497767441860465</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-110</v>
+        <v>-186</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>129</v>
+        <v>-115</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 65.0% (fair -186). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9493,17 +9493,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9513,17 +9513,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4265357142857143</v>
+        <v>0.4320863309352518</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9564,32 +9564,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5990884615384615</v>
+        <v>0.4265357142857143</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-149</v>
+        <v>134</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-108</v>
+        <v>180</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 42.7% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6087676056338028</v>
+        <v>0.6103591549295775</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-156</v>
+        <v>-157</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>-113</v>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 61.0% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9691,37 +9691,37 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4321132075471698</v>
+        <v>0.601188625592417</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>131</v>
+        <v>-151</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>165</v>
+        <v>-111</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9745,7 +9745,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +131). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9781,13 +9781,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.3634983498349835</v>
+        <v>0.3588178913738019</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +175). Your call.</t>
+          <t>Model 35.9% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9913,13 +9913,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.569025</v>
+        <v>0.5648703349282296</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-132</v>
+        <v>-130</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10021,17 +10021,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.3952222222222222</v>
+        <v>0.4351417004048583</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10087,17 +10087,17 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -10107,17 +10107,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5734078341013824</v>
+        <v>0.472511013215859</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-134</v>
+        <v>112</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-117</v>
+        <v>127</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10153,37 +10153,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4310162601626016</v>
+        <v>0.5734078341013824</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>132</v>
+        <v>-134</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>146</v>
+        <v>-117</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10219,37 +10219,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4764864864864866</v>
+        <v>0.3933333333333333</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 39.3% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10285,37 +10285,37 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5071634615384615</v>
+        <v>0.5430699029126212</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-103</v>
+        <v>-119</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>108</v>
+        <v>-106</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -10366,22 +10366,22 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Athletics +1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.543063768115942</v>
+        <v>0.5142156862745098</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-119</v>
+        <v>-106</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-107</v>
+        <v>104</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10438,7 +10438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P148"/>
+  <dimension ref="A1:P146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10582,10 +10582,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6122</v>
+        <v>0.604</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-158</v>
+        <v>-153</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>-110</v>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 60.4% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3878</v>
+        <v>0.396</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>203</v>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 39.6% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5516</v>
+        <v>0.5565</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-123</v>
+        <v>-125</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>141</v>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10780,10 +10780,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4484</v>
+        <v>0.4435</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>100</v>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10846,10 +10846,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.2654642857142858</v>
+        <v>0.2746071428571429</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>180</v>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 26.5% (fair +277). Your call.</t>
+          <t>Model 27.5% (fair +264). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.7345558139534885</v>
+        <v>0.7254093023255815</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-277</v>
+        <v>-264</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>-115</v>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 73.5% (fair -277). Your call.</t>
+          <t>Model 72.5% (fair -264). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5182</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>-108</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4818</v>
+        <v>0.4814</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>108</v>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.6528</v>
+        <v>0.6462</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-188</v>
+        <v>-183</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>141</v>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -188). Your call.</t>
+          <t>Model 64.6% (fair -183). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11176,10 +11176,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.3472</v>
+        <v>0.3538</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>100</v>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 34.7% (fair +188). Your call.</t>
+          <t>Model 35.4% (fair +183). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11242,10 +11242,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3561428571428571</v>
+        <v>0.3502142857142858</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>180</v>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 35.0% (fair +186). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6438395348837209</v>
+        <v>0.6497767441860465</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-181</v>
+        <v>-186</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-115</v>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 65.0% (fair -186). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11374,13 +11374,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4882671641791045</v>
+        <v>0.4840298507462687</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-101</v>
+        <v>101</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11440,13 +11440,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5117647058823529</v>
+        <v>0.51595</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-105</v>
+        <v>-107</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11506,10 +11506,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.468</v>
+        <v>0.4595</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>117</v>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 46.0% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11572,13 +11572,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.532</v>
+        <v>0.5405</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-114</v>
+        <v>-118</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 54.0% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11638,13 +11638,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.3634983498349835</v>
+        <v>0.3588178913738019</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +175). Your call.</t>
+          <t>Model 35.9% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11704,13 +11704,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6364686468646864</v>
+        <v>0.6411532467532467</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-175</v>
+        <v>-179</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-203</v>
+        <v>-208</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 63.6% (fair -175). Your call.</t>
+          <t>Model 64.1% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11770,10 +11770,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6103</v>
+        <v>0.6004</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-157</v>
+        <v>-150</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>104</v>
@@ -11800,7 +11800,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -157). Your call.</t>
+          <t>Model 60.0% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11836,13 +11836,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.3897</v>
+        <v>0.3996</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +157). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4569607843137255</v>
+        <v>0.4569117647058824</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>119</v>
@@ -11968,13 +11968,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.543063768115942</v>
+        <v>0.5430699029126212</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>-119</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-107</v>
+        <v>-106</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12034,13 +12034,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4251282051282051</v>
+        <v>0.4214285714285714</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 42.1% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12100,13 +12100,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5748682403433477</v>
+        <v>0.5785468085106383</v>
       </c>
       <c r="G28" s="14" t="n">
+        <v>-137</v>
+      </c>
+      <c r="H28" s="15" t="n">
         <v>-135</v>
-      </c>
-      <c r="H28" s="15" t="n">
-        <v>-133</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 57.9% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5147549019607843</v>
+        <v>0.5142156862745098</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>-106</v>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4852669950738916</v>
+        <v>0.4858251231527094</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>106</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12298,13 +12298,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4310162601626016</v>
+        <v>0.4351417004048583</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12364,13 +12364,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.569025</v>
+        <v>0.5648703349282296</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-132</v>
+        <v>-130</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12430,10 +12430,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4583870967741936</v>
+        <v>0.4576497695852534</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>117</v>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 45.8% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12496,10 +12496,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5415967741935483</v>
+        <v>0.5423516129032258</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-118</v>
+        <v>-119</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>-117</v>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 54.2% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12558,17 +12558,17 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4787</v>
+        <v>0.4692</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12592,7 +12592,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12624,17 +12624,17 @@
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5213</v>
+        <v>0.5307999999999999</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-109</v>
+        <v>-113</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12694,13 +12694,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.3607342657342657</v>
+        <v>0.3632374100719424</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 36.1% (fair +177). Your call.</t>
+          <t>Model 36.3% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12760,10 +12760,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.6392361111111111</v>
+        <v>0.6367361111111112</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-177</v>
+        <v>-175</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>188</v>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 63.7% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12826,13 +12826,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4764864864864866</v>
+        <v>0.472511013215859</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12892,10 +12892,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5235009009009008</v>
+        <v>0.5275126126126126</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>-122</v>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12958,13 +12958,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5414</v>
+        <v>0.5347</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12988,7 +12988,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13024,10 +13024,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4586</v>
+        <v>0.4653</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>108</v>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.3205035971223021</v>
+        <v>0.3179496402877698</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>178</v>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 32.1% (fair +212). Your call.</t>
+          <t>Model 31.8% (fair +215). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13156,10 +13156,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.6795104895104894</v>
+        <v>0.682062937062937</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-212</v>
+        <v>-215</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>186</v>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 68.0% (fair -212). Your call.</t>
+          <t>Model 68.2% (fair -215). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13222,10 +13222,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4009004739336492</v>
+        <v>0.3988151658767772</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>111</v>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13288,13 +13288,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5990884615384615</v>
+        <v>0.601188625592417</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-149</v>
+        <v>-151</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-108</v>
+        <v>-111</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13350,17 +13350,17 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4606</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>117</v>
+        <v>-103</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13384,7 +13384,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13416,17 +13416,17 @@
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5394</v>
+        <v>0.4917</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-117</v>
+        <v>103</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-106</v>
+        <v>100</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4824074074074074</v>
+        <v>0.4827037037037037</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>107</v>
@@ -13516,7 +13516,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5175925925925925</v>
+        <v>0.5172962962962963</v>
       </c>
       <c r="G50" s="14" t="n">
         <v>-107</v>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13618,13 +13618,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4236554621848739</v>
+        <v>0.4297391304347826</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13684,13 +13684,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5763638297872341</v>
+        <v>0.5702446351931331</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-136</v>
+        <v>-133</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-135</v>
+        <v>-133</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13750,13 +13750,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4843</v>
+        <v>0.4924019607843137</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +106). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13816,13 +13816,13 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5157</v>
+        <v>0.5076117647058823</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-106</v>
+        <v>-103</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>117</v>
+        <v>-104</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -106). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13882,10 +13882,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.39124</v>
+        <v>0.38964</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>150</v>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +156). Your call.</t>
+          <t>Model 39.0% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13948,10 +13948,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.6087676056338028</v>
+        <v>0.6103591549295775</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-156</v>
+        <v>-157</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>-113</v>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 61.0% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14014,13 +14014,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.6278444444444444</v>
+        <v>0.6282675889328063</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>-169</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>-152</v>
+        <v>-153</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.3721484375</v>
+        <v>0.3717578125</v>
       </c>
       <c r="G58" s="14" t="n">
         <v>169</v>
@@ -14152,7 +14152,7 @@
         <v>112</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14218,7 +14218,7 @@
         <v>-112</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14259,32 +14259,32 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds +1.5</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4757490196078431</v>
+        <v>0.47295</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14325,32 +14325,32 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies -1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5242358078602619</v>
+        <v>0.5270588235294117</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14401,22 +14401,22 @@
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.47295</v>
+        <v>0.3804</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -14440,7 +14440,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 38.0% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14467,22 +14467,22 @@
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5270588235294117</v>
+        <v>0.6195999999999999</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-111</v>
+        <v>-163</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14533,22 +14533,22 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.5009333333333333</v>
+        <v>0.4265357142857143</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-100</v>
+        <v>134</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>-104</v>
+        <v>180</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 42.7% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14599,22 +14599,22 @@
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.4990776699029126</v>
+        <v>0.5734600760456274</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>100</v>
+        <v>-134</v>
       </c>
       <c r="H66" s="15" t="n">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="I66" s="13">
         <f>IF($H$66="","",IF($H$66&lt;0,-$H$66/(-$H$66+100),100/($H$66+100)))</f>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14655,7 +14655,7 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -14665,23 +14665,21 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.4265357142857143</v>
+        <v>0.5105</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>134</v>
-      </c>
-      <c r="H67" s="15" t="n">
-        <v>180</v>
-      </c>
+        <v>-104</v>
+      </c>
+      <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
         <v/>
@@ -14704,7 +14702,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14721,7 +14719,7 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
@@ -14731,23 +14729,21 @@
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5734600760456274</v>
+        <v>0.4895</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-134</v>
-      </c>
-      <c r="H68" s="15" t="n">
-        <v>163</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
         <f>IF($H$68="","",IF($H$68&lt;0,-$H$68/(-$H$68+100),100/($H$68+100)))</f>
         <v/>
@@ -14770,7 +14766,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14787,12 +14783,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -14802,14 +14798,14 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5105</v>
+        <v>0.4594</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>-104</v>
+        <v>118</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14834,7 +14830,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14851,12 +14847,12 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -14866,14 +14862,14 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4895</v>
+        <v>0.5406</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>104</v>
+        <v>-118</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14898,7 +14894,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14915,12 +14911,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -14930,14 +14926,14 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4594</v>
+        <v>0.4649</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -14962,7 +14958,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14979,12 +14975,12 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -14994,14 +14990,14 @@
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5406</v>
+        <v>0.5351</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15026,7 +15022,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15043,12 +15039,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -15058,14 +15054,14 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4649</v>
+        <v>0.4236</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H73" s="15" t="n"/>
       <c r="I73" s="13">
@@ -15090,7 +15086,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15107,12 +15103,12 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -15122,14 +15118,14 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5351</v>
+        <v>0.5764</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-115</v>
+        <v>-136</v>
       </c>
       <c r="H74" s="15" t="n"/>
       <c r="I74" s="13">
@@ -15154,7 +15150,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15171,12 +15167,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -15186,14 +15182,14 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4221</v>
+        <v>0.361</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="H75" s="15" t="n"/>
       <c r="I75" s="13">
@@ -15218,7 +15214,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 36.1% (fair +177). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15235,12 +15231,12 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -15250,14 +15246,14 @@
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5779</v>
+        <v>0.639</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-137</v>
+        <v>-177</v>
       </c>
       <c r="H76" s="15" t="n"/>
       <c r="I76" s="13">
@@ -15282,7 +15278,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 63.9% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15294,17 +15290,17 @@
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -15314,16 +15310,18 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.3565</v>
+        <v>0.48395</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>181</v>
-      </c>
-      <c r="H77" s="15" t="n"/>
+        <v>107</v>
+      </c>
+      <c r="H77" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
         <v/>
@@ -15346,7 +15344,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15358,17 +15356,17 @@
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -15378,16 +15376,18 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.6435</v>
+        <v>0.51605</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-181</v>
-      </c>
-      <c r="H78" s="15" t="n"/>
+        <v>-107</v>
+      </c>
+      <c r="H78" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
         <v/>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 64.3% (fair -181). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15437,22 +15437,22 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.48395</v>
+        <v>0.4633</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15503,22 +15503,22 @@
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.51605</v>
+        <v>0.5367</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-107</v>
+        <v>-116</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15569,22 +15569,22 @@
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>San Francisco Giants +1.5</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4633</v>
+        <v>0.6372784172661871</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>116</v>
+        <v>-176</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>133</v>
+        <v>-178</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 63.7% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15635,22 +15635,22 @@
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Toronto Blue Jays -1.5</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5367</v>
+        <v>0.3627407407407408</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-116</v>
+        <v>176</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 36.3% (fair +176). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15691,32 +15691,32 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants +1.5</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.6372784172661871</v>
+        <v>0.4707211538461538</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-176</v>
+        <v>112</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>-178</v>
+        <v>108</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -176). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15757,32 +15757,32 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays -1.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.3627407407407408</v>
+        <v>0.5293095238095238</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>176</v>
+        <v>-112</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>170</v>
+        <v>-110</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +176). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15833,22 +15833,22 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4707211538461538</v>
+        <v>0.5103431372549019</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>112</v>
+        <v>-104</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15899,22 +15899,22 @@
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5293095238095238</v>
+        <v>0.48965</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-112</v>
+        <v>104</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15938,7 +15938,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15965,22 +15965,22 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Baltimore Orioles -1.5</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.5071634615384615</v>
+        <v>0.359</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-103</v>
+        <v>179</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 35.9% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16031,22 +16031,22 @@
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Chicago Cubs +1.5</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.49285</v>
+        <v>0.6409885931558935</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>103</v>
+        <v>-179</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 64.1% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16087,32 +16087,32 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles +1.5</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.6167851851851851</v>
+        <v>0.3919672131147541</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-161</v>
+        <v>155</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-170</v>
+        <v>144</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16153,32 +16153,32 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.3831939163498099</v>
+        <v>0.6080459016393442</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>161</v>
+        <v>-155</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>163</v>
+        <v>-144</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16229,22 +16229,22 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.3947131147540984</v>
+        <v>0.6012</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>153</v>
+        <v>-151</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16295,22 +16295,22 @@
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.6052865546218488</v>
+        <v>0.3988</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-153</v>
+        <v>151</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>-138</v>
+        <v>115</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -16334,7 +16334,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 60.5% (fair -153). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16361,22 +16361,22 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Detroit Tigers -1.5</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.6012</v>
+        <v>0.4288934426229508</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-151</v>
+        <v>133</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -151). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16427,22 +16427,22 @@
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.3988</v>
+        <v>0.5711224489795919</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>151</v>
+        <v>-133</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>117</v>
+        <v>-145</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16466,7 +16466,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -16493,22 +16493,22 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers -1.5</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4288934426229508</v>
+        <v>0.4464055299539171</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
@@ -16559,22 +16559,22 @@
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Athletics +1.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5711224489795919</v>
+        <v>0.5536202764976959</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-133</v>
+        <v>-124</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>-145</v>
+        <v>-117</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16625,22 +16625,22 @@
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4464055299539171</v>
+        <v>0.5193658536585366</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>124</v>
+        <v>-108</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>117</v>
+        <v>-105</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16664,7 +16664,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16691,22 +16691,22 @@
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5536202764976959</v>
+        <v>0.4806372549019608</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-124</v>
+        <v>108</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>-117</v>
+        <v>104</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16757,22 +16757,22 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.5193658536585366</v>
+        <v>0.4320863309352518</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-108</v>
+        <v>131</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>-105</v>
+        <v>178</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16823,22 +16823,22 @@
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Atlanta Braves +1.5</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.4806372549019608</v>
+        <v>0.5679104477611941</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>108</v>
+        <v>-131</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -16889,22 +16889,22 @@
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4321132075471698</v>
+        <v>0.5263921658986175</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>131</v>
+        <v>-111</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>165</v>
+        <v>-117</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -16928,7 +16928,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +131). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -16945,7 +16945,7 @@
       </c>
       <c r="B102" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C102" s="20" t="inlineStr">
@@ -16955,22 +16955,22 @@
       </c>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves +1.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5679104477611941</v>
+        <v>0.4736238532110092</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-131</v>
+        <v>111</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -16994,7 +16994,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17021,19 +17021,19 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.5394</v>
+        <v>0.5377673076923077</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>-117</v>
+        <v>-116</v>
       </c>
       <c r="H103" s="15" t="n">
         <v>-108</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17087,22 +17087,22 @@
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.4606</v>
+        <v>0.4622065727699531</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17153,22 +17153,22 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Miami Marlins +1.5</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.5214</v>
+        <v>0.5797040816326531</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>-109</v>
+        <v>-138</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>-110</v>
+        <v>-145</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -17192,7 +17192,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17219,22 +17219,22 @@
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Seattle Mariners -1.5</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.4786047619047619</v>
+        <v>0.4202666666666667</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-110</v>
+        <v>125</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17275,7 +17275,7 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -17285,22 +17285,22 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins +1.5</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.5797040816326531</v>
+        <v>0.4555299539170507</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-138</v>
+        <v>120</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>-145</v>
+        <v>117</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -17324,7 +17324,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 45.6% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17341,7 +17341,7 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C108" s="20" t="inlineStr">
@@ -17351,22 +17351,22 @@
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners -1.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4202666666666667</v>
+        <v>0.5444727272727272</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>138</v>
+        <v>-120</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>125</v>
+        <v>-120</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -17390,7 +17390,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 54.4% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17417,22 +17417,22 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.4555299539170507</v>
+        <v>0.5208</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>120</v>
+        <v>-109</v>
       </c>
       <c r="H109" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I109" s="13">
         <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
@@ -17456,7 +17456,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +120). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17483,22 +17483,22 @@
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.5444727272727272</v>
+        <v>0.4792156862745097</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-120</v>
+        <v>109</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>-120</v>
+        <v>-104</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -17522,7 +17522,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -120). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17549,22 +17549,22 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Tampa Bay Rays -1.5</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.5303490196078431</v>
+        <v>0.3708633093525179</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-113</v>
+        <v>170</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>-104</v>
+        <v>178</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -17588,7 +17588,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 37.1% (fair +170). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17615,22 +17615,22 @@
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>New York Yankees +1.5</t>
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.469656862745098</v>
+        <v>0.6291666666666667</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>113</v>
+        <v>-170</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 62.9% (fair -170). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17671,32 +17671,32 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays -1.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.3708518518518519</v>
+        <v>0.4433179723502304</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>170</v>
+        <v>126</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17720,7 +17720,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 37.1% (fair +170). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17737,32 +17737,32 @@
       </c>
       <c r="B114" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C114" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees +1.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.6291666666666667</v>
+        <v>0.5566936936936936</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-170</v>
+        <v>-126</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>176</v>
+        <v>-122</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17786,7 +17786,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -170). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17813,19 +17813,19 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4433179723502304</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>126</v>
+        <v>-134</v>
       </c>
       <c r="H115" s="15" t="n">
         <v>117</v>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17879,22 +17879,22 @@
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5566936936936936</v>
+        <v>0.4278999999999999</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-126</v>
+        <v>134</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-122</v>
+        <v>122</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17918,7 +17918,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -17945,22 +17945,22 @@
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.4005118110236221</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>-134</v>
+        <v>150</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 40.1% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18011,22 +18011,22 @@
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4278999999999999</v>
+        <v>0.5994703703703703</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>134</v>
+        <v>-150</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>122</v>
+        <v>-170</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 59.9% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18067,32 +18067,32 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.4005118110236221</v>
+        <v>0.4258369098712446</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +150). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18133,32 +18133,32 @@
       </c>
       <c r="B120" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C120" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.5994703703703703</v>
+        <v>0.5741832618025752</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-150</v>
+        <v>-135</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-170</v>
+        <v>-133</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -150). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -18214,17 +18214,17 @@
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.4264806866952789</v>
+        <v>0.5134803921568628</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>134</v>
+        <v>-106</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -18248,7 +18248,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +134). Your call.</t>
+          <t>Model 51.3% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C122" s="20" t="inlineStr">
@@ -18280,17 +18280,17 @@
       </c>
       <c r="E122" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.5734982832618025</v>
+        <v>0.4865058823529412</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>-134</v>
+        <v>106</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>-133</v>
+        <v>-104</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 48.7% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -18331,12 +18331,12 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
@@ -18346,17 +18346,17 @@
       </c>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.5134803921568628</v>
+        <v>0.4266046511627907</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>-106</v>
+        <v>134</v>
       </c>
       <c r="H123" s="15" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="I123" s="13">
         <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -106). Your call.</t>
+          <t>Model 42.7% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -18397,12 +18397,12 @@
       </c>
       <c r="B124" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C124" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
@@ -18412,17 +18412,17 @@
       </c>
       <c r="E124" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.4865058823529412</v>
+        <v>0.5734078341013824</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>106</v>
+        <v>-134</v>
       </c>
       <c r="H124" s="15" t="n">
-        <v>-104</v>
+        <v>-117</v>
       </c>
       <c r="I124" s="13">
         <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
@@ -18446,7 +18446,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +106). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -18473,22 +18473,22 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.4266046511627907</v>
+        <v>0.507</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>134</v>
+        <v>-103</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
@@ -18512,7 +18512,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18539,22 +18539,22 @@
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.5734078341013824</v>
+        <v>0.4930096153846154</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-134</v>
+        <v>103</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>-117</v>
+        <v>-108</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18605,22 +18605,22 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.511</v>
+        <v>0.3933333333333333</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>-104</v>
+        <v>154</v>
       </c>
       <c r="H127" s="15" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="I127" s="13">
         <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 39.3% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18671,22 +18671,22 @@
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.4890115384615384</v>
+        <v>0.6066726618705036</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>104</v>
+        <v>-154</v>
       </c>
       <c r="H128" s="15" t="n">
-        <v>-108</v>
+        <v>-178</v>
       </c>
       <c r="I128" s="13">
         <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 60.7% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
@@ -18737,23 +18737,21 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.3952222222222222</v>
+        <v>0.4484</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>153</v>
-      </c>
-      <c r="H129" s="15" t="n">
-        <v>170</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H129" s="15" t="n"/>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
         <v/>
@@ -18776,7 +18774,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18793,7 +18791,7 @@
       </c>
       <c r="B130" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C130" s="20" t="inlineStr">
@@ -18803,23 +18801,21 @@
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.604751798561151</v>
+        <v>0.5516</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>-153</v>
-      </c>
-      <c r="H130" s="15" t="n">
-        <v>-178</v>
-      </c>
+        <v>-123</v>
+      </c>
+      <c r="H130" s="15" t="n"/>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
         <v/>
@@ -18842,7 +18838,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 60.5% (fair -153). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -18869,21 +18865,23 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.4484</v>
+        <v>0.4585</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>123</v>
-      </c>
-      <c r="H131" s="15" t="n"/>
+        <v>118</v>
+      </c>
+      <c r="H131" s="15" t="n">
+        <v>108</v>
+      </c>
       <c r="I131" s="13">
         <f>IF($H$131="","",IF($H$131&lt;0,-$H$131/(-$H$131+100),100/($H$131+100)))</f>
         <v/>
@@ -18906,7 +18904,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -18933,21 +18931,23 @@
       </c>
       <c r="D132" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.5516</v>
+        <v>0.5415</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>-123</v>
-      </c>
-      <c r="H132" s="15" t="n"/>
+        <v>-118</v>
+      </c>
+      <c r="H132" s="15" t="n">
+        <v>105</v>
+      </c>
       <c r="I132" s="13">
         <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
         <v/>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -18997,22 +18997,22 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>0.4585</v>
+        <v>0.4069629629629629</v>
       </c>
       <c r="G133" s="14" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="H133" s="15" t="n">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="I133" s="13">
         <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
@@ -19036,7 +19036,7 @@
       </c>
       <c r="N133" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O133" s="15" t="n"/>
@@ -19063,22 +19063,22 @@
       </c>
       <c r="D134" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.5415</v>
+        <v>0.593037037037037</v>
       </c>
       <c r="G134" s="14" t="n">
-        <v>-118</v>
+        <v>-146</v>
       </c>
       <c r="H134" s="15" t="n">
-        <v>105</v>
+        <v>170</v>
       </c>
       <c r="I134" s="13">
         <f>IF($H$134="","",IF($H$134&lt;0,-$H$134/(-$H$134+100),100/($H$134+100)))</f>
@@ -19102,7 +19102,7 @@
       </c>
       <c r="N134" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O134" s="15" t="n"/>
@@ -19119,33 +19119,31 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.4069629629629629</v>
+        <v>0.5831</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>146</v>
-      </c>
-      <c r="H135" s="15" t="n">
-        <v>170</v>
-      </c>
+        <v>-140</v>
+      </c>
+      <c r="H135" s="15" t="n"/>
       <c r="I135" s="13">
         <f>IF($H$135="","",IF($H$135&lt;0,-$H$135/(-$H$135+100),100/($H$135+100)))</f>
         <v/>
@@ -19168,7 +19166,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -19185,33 +19183,31 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C136" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E136" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.593037037037037</v>
+        <v>0.4169</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>-146</v>
-      </c>
-      <c r="H136" s="15" t="n">
-        <v>170</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="H136" s="15" t="n"/>
       <c r="I136" s="13">
         <f>IF($H$136="","",IF($H$136&lt;0,-$H$136/(-$H$136+100),100/($H$136+100)))</f>
         <v/>
@@ -19234,7 +19230,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -19261,21 +19257,23 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.585</v>
+        <v>0.4853</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-141</v>
-      </c>
-      <c r="H137" s="15" t="n"/>
+        <v>106</v>
+      </c>
+      <c r="H137" s="15" t="n">
+        <v>108</v>
+      </c>
       <c r="I137" s="13">
         <f>IF($H$137="","",IF($H$137&lt;0,-$H$137/(-$H$137+100),100/($H$137+100)))</f>
         <v/>
@@ -19298,7 +19296,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -19325,21 +19323,23 @@
       </c>
       <c r="D138" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E138" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.415</v>
+        <v>0.5146999999999999</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>141</v>
-      </c>
-      <c r="H138" s="15" t="n"/>
+        <v>-106</v>
+      </c>
+      <c r="H138" s="15" t="n">
+        <v>105</v>
+      </c>
       <c r="I138" s="13">
         <f>IF($H$138="","",IF($H$138&lt;0,-$H$138/(-$H$138+100),100/($H$138+100)))</f>
         <v/>
@@ -19362,7 +19362,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -19389,22 +19389,22 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.4827</v>
+        <v>0.5704386554621849</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>107</v>
+        <v>-133</v>
       </c>
       <c r="H139" s="15" t="n">
-        <v>133</v>
+        <v>-138</v>
       </c>
       <c r="I139" s="13">
         <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
@@ -19428,7 +19428,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -19455,22 +19455,22 @@
       </c>
       <c r="D140" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E140" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.5173</v>
+        <v>0.429531914893617</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>-107</v>
+        <v>133</v>
       </c>
       <c r="H140" s="15" t="n">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="I140" s="13">
         <f>IF($H$140="","",IF($H$140&lt;0,-$H$140/(-$H$140+100),100/($H$140+100)))</f>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -19511,33 +19511,31 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>0.569336974789916</v>
+        <v>0.4736</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>-132</v>
-      </c>
-      <c r="H141" s="15" t="n">
-        <v>-138</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="H141" s="15" t="n"/>
       <c r="I141" s="13">
         <f>IF($H$141="","",IF($H$141&lt;0,-$H$141/(-$H$141+100),100/($H$141+100)))</f>
         <v/>
@@ -19560,7 +19558,7 @@
       </c>
       <c r="N141" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O141" s="15" t="n"/>
@@ -19577,33 +19575,31 @@
       </c>
       <c r="B142" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C142" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E142" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.4306382978723404</v>
+        <v>0.5264</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>132</v>
-      </c>
-      <c r="H142" s="15" t="n">
-        <v>135</v>
-      </c>
+        <v>-111</v>
+      </c>
+      <c r="H142" s="15" t="n"/>
       <c r="I142" s="13">
         <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
         <v/>
@@ -19626,7 +19622,7 @@
       </c>
       <c r="N142" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O142" s="15" t="n"/>
@@ -19643,12 +19639,12 @@
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
@@ -19658,14 +19654,14 @@
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F143" s="13" t="n">
-        <v>0.4736</v>
+        <v>0.4939</v>
       </c>
       <c r="G143" s="14" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="H143" s="15" t="n"/>
       <c r="I143" s="13">
@@ -19690,7 +19686,7 @@
       </c>
       <c r="N143" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O143" s="15" t="n"/>
@@ -19707,12 +19703,12 @@
       </c>
       <c r="B144" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C144" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
@@ -19722,14 +19718,14 @@
       </c>
       <c r="E144" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.5264</v>
+        <v>0.5061</v>
       </c>
       <c r="G144" s="14" t="n">
-        <v>-111</v>
+        <v>-102</v>
       </c>
       <c r="H144" s="15" t="n"/>
       <c r="I144" s="13">
@@ -19754,7 +19750,7 @@
       </c>
       <c r="N144" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O144" s="15" t="n"/>
@@ -19771,7 +19767,7 @@
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
@@ -19786,14 +19782,14 @@
       </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F145" s="13" t="n">
-        <v>0.4976</v>
+        <v>0.4289</v>
       </c>
       <c r="G145" s="14" t="n">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="H145" s="15" t="n"/>
       <c r="I145" s="13">
@@ -19818,7 +19814,7 @@
       </c>
       <c r="N145" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O145" s="15" t="n"/>
@@ -19835,7 +19831,7 @@
       </c>
       <c r="B146" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C146" s="20" t="inlineStr">
@@ -19850,14 +19846,14 @@
       </c>
       <c r="E146" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.5024</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="G146" s="14" t="n">
-        <v>-101</v>
+        <v>-133</v>
       </c>
       <c r="H146" s="15" t="n"/>
       <c r="I146" s="13">
@@ -19882,7 +19878,7 @@
       </c>
       <c r="N146" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O146" s="15" t="n"/>
@@ -19891,137 +19887,9 @@
         <v/>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B147" s="12" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
-        </is>
-      </c>
-      <c r="C147" s="12" t="inlineStr">
-        <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="D147" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E147" s="12" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="F147" s="13" t="n">
-        <v>0.4289</v>
-      </c>
-      <c r="G147" s="14" t="n">
-        <v>133</v>
-      </c>
-      <c r="H147" s="15" t="n"/>
-      <c r="I147" s="13">
-        <f>IF($H$147="","",IF($H$147&lt;0,-$H$147/(-$H$147+100),100/($H$147+100)))</f>
-        <v/>
-      </c>
-      <c r="J147" s="16">
-        <f>IF($H$147="","",$F$147*IF($H$147&lt;0,-100/$H$147,$H$147/100)-(1-$F$147))</f>
-        <v/>
-      </c>
-      <c r="K147" s="17">
-        <f>IF($H$147="","",MAX(0,($F$147*IF($H$147&lt;0,-100/$H$147,$H$147/100)-(1-$F$147))/IF($H$147&lt;0,-100/$H$147,$H$147/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L147" s="18">
-        <f>IF($H$147="","",ROUND(MIN($K$147,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M147" s="12">
-        <f>IF($J$147="","",IF($J$147&lt;0,"Pass",IF($J$147&lt;'Settings'!$B$4,"Thin",IF($J$147&lt;0.06,"✅ Sharp band",IF($J$147&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N147" s="19" t="inlineStr">
-        <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
-        </is>
-      </c>
-      <c r="O147" s="15" t="n"/>
-      <c r="P147" s="16">
-        <f>IF(OR($H$147="",$O$147=""),"",(1+IF($H$147&lt;0,-100/$H$147,$H$147/100))/(1+IF($O$147&lt;0,-100/$O$147,$O$147/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B148" s="20" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
-        </is>
-      </c>
-      <c r="C148" s="20" t="inlineStr">
-        <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="D148" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E148" s="20" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="F148" s="13" t="n">
-        <v>0.5711000000000001</v>
-      </c>
-      <c r="G148" s="14" t="n">
-        <v>-133</v>
-      </c>
-      <c r="H148" s="15" t="n"/>
-      <c r="I148" s="13">
-        <f>IF($H$148="","",IF($H$148&lt;0,-$H$148/(-$H$148+100),100/($H$148+100)))</f>
-        <v/>
-      </c>
-      <c r="J148" s="16">
-        <f>IF($H$148="","",$F$148*IF($H$148&lt;0,-100/$H$148,$H$148/100)-(1-$F$148))</f>
-        <v/>
-      </c>
-      <c r="K148" s="17">
-        <f>IF($H$148="","",MAX(0,($F$148*IF($H$148&lt;0,-100/$H$148,$H$148/100)-(1-$F$148))/IF($H$148&lt;0,-100/$H$148,$H$148/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L148" s="18">
-        <f>IF($H$148="","",ROUND(MIN($K$148,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M148" s="12">
-        <f>IF($J$148="","",IF($J$148&lt;0,"Pass",IF($J$148&lt;'Settings'!$B$4,"Thin",IF($J$148&lt;0.06,"✅ Sharp band",IF($J$148&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N148" s="19" t="inlineStr">
-        <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
-        </is>
-      </c>
-      <c r="O148" s="15" t="n"/>
-      <c r="P148" s="16">
-        <f>IF(OR($H$148="",$O$148=""),"",(1+IF($H$148&lt;0,-100/$H$148,$H$148/100))/(1+IF($O$148&lt;0,-100/$O$148,$O$148/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J148">
+  <conditionalFormatting sqref="J5:J146">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
